--- a/results/job_matches_2026-09-23.xlsx
+++ b/results/job_matches_2026-09-23.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G90"/>
+  <dimension ref="A1:G135"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -538,25 +538,25 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Data Engineer Sr</t>
+          <t>I.T. - DevOps Engineer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Oshkosh Corporation</t>
+          <t>StorageMart</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Oshkosh, WI, US USA</t>
+          <t>Columbia, MO, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>16.7</v>
+        <v>18.8</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Data Factory, Databricks, GCP, Hadoop, HDFS, Hive</t>
+          <t>AWS, Lambda, S3, SQS, ECS, IAM, RDS, Azure, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,32 +566,32 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8b5c363397eafe5f</t>
+          <t>https://www.indeed.com/viewjob?jk=c2e972535a11a31f</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Senior AI Ops / DevOps Engineer</t>
+          <t>Applied AI Site Reliability Engineer II - PxE A&amp;A</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Hermitage, TN, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>16.7</v>
+        <v>17.4</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Splunk, MLOps, MLflow, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, Splunk, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,32 +601,32 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=040c156b15abd039</t>
+          <t>https://www.indeed.com/viewjob?jk=293a95bba31efbab</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Data Engineer 4</t>
+          <t>Applied AI Site Reliability Engineer II - PxE A&amp;A</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>16</v>
+        <v>17.4</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Redshift, RDS, Azure, Databricks, Spark, Scala, Snowflake</t>
+          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, Splunk, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,102 +636,102 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6438ee405fccd9e0</t>
+          <t>https://www.indeed.com/viewjob?jk=90798cf9ad992e58</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Data Engineer 4 (Python, AWS)</t>
+          <t>Applied AI Site Reliability Engineer II - PxE A&amp;A</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>16</v>
+        <v>17.4</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Redshift, RDS, Azure, Databricks, Spark, Scala, Snowflake</t>
+          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, Splunk, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6785ed8543590d56</t>
+          <t>https://www.indeed.com/viewjob?jk=76a0c64002bbb5c1</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Data Engineer 5</t>
+          <t>Data Engineer Sr</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>Oshkosh Corporation</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Oshkosh, WI, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>16</v>
+        <v>16.7</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Redshift, RDS, Azure, Databricks, Spark, Scala, Snowflake</t>
+          <t>AWS, Redshift, RDS, Azure, Data Factory, Databricks, GCP, Hadoop, HDFS, Hive</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=30216af3fb095a16</t>
+          <t>https://www.indeed.com/viewjob?jk=8b5c363397eafe5f</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Associate Data Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Tiger Analytics</t>
+          <t>Blue Cross and Blue Shield of Minnesota</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Eagan, MN, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>16</v>
+        <v>16.7</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Cloud Storage, Spark, PySpark, Scala, Snowflake</t>
+          <t>AWS, Glue, EMR, Lambda, S3, SQS, SNS, RDS, Databricks, Spark</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,32 +741,32 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4b2cb75552da28cb</t>
+          <t>https://www.indeed.com/viewjob?jk=31bf226ac97de61e</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Tiger Analytics</t>
+          <t>Sally Beauty</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Denton, TX, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>16</v>
+        <v>16.7</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Cloud Storage, Spark, PySpark, Scala, Snowflake</t>
+          <t>AWS, S3, RDS, Azure, Databricks, Data Lake Storage, Unity Catalog, Medallion Architecture, Delta Live Tables, Google Cloud Platform</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,32 +776,32 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4b046b29ca6b7df4</t>
+          <t>https://www.indeed.com/viewjob?jk=0864fe655aae7888</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Senior Software Developer</t>
+          <t>Enterprise Data Architect</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>NBME</t>
+          <t>Alignment Health</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Orange, CA, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>16</v>
+        <v>16.7</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Athena, Step Functions, S3, SQS, SNS, API Gateway, RDS</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Scala, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,137 +811,137 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=195d724701bfe29e</t>
+          <t>https://www.indeed.com/viewjob?jk=1611fa9de2f7504b</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Data Engineer 4 (Risk Tech)</t>
+          <t>Senior AI Ops / DevOps Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>15.3</v>
+        <v>16.7</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Redshift, RDS, Azure, Databricks, Spark, Scala, Snowflake</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Splunk, MLOps, MLflow, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6cc3d67e2533b3c1</t>
+          <t>https://www.indeed.com/viewjob?jk=040c156b15abd039</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Data Engineer - Databricks</t>
+          <t>Data Engineer 4</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Steampunk</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, Step Functions, S3, RDS, Azure, Databricks, Unity Catalog, GCP, Spark, PySpark</t>
+          <t>AWS, Glue, EMR, Redshift, RDS, Azure, Databricks, Spark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5175d58988719685</t>
+          <t>https://www.indeed.com/viewjob?jk=6438ee405fccd9e0</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Part Time Teller (20 Hours), Castro Branch</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Citi</t>
+          <t>Tiger Analytics</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Rutherford, NJ, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>14.6</v>
+        <v>16</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, Lambda, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Kafka</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Cloud Storage, Spark, PySpark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=62e481a61bf24644</t>
+          <t>https://www.indeed.com/viewjob?jk=4b2cb75552da28cb</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Agentic AI Databricks</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>LTM Limited</t>
+          <t>Tiger Analytics</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Raritan, NJ, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>14.6</v>
+        <v>16</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Unity Catalog, Delta Live Tables, Spark, PySpark, Scala</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Cloud Storage, Spark, PySpark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,172 +951,172 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=611badfabe276aeb</t>
+          <t>https://www.indeed.com/viewjob?jk=4b046b29ca6b7df4</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer</t>
+          <t>Senior Software Engineer - ai automation medical billing platform</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Seek Now</t>
+          <t>Relentless Talent</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>14.6</v>
+        <v>16</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, Scala, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=86d6727803939178</t>
+          <t>https://www.indeed.com/viewjob?jk=69d642c554413fbe</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Senior Data/Machine Learning Engineer</t>
+          <t>Senior Software Engineer - ai automation medical billing platform</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>The Coca-Cola Company</t>
+          <t>Relentless Talent</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Buffalo, NY, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>14.6</v>
+        <v>16</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, RDS, Spark, Scala, Data Modeling, ETL, dbt, MLOps, CI/CD, Docker</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3f5fae1eed697d12</t>
+          <t>https://www.indeed.com/viewjob?jk=818c7178aa0280e0</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Engineer – Application</t>
+          <t>Senior Data Platfrom Engineer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Federated Hermes</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Warrendale, PA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>13.9</v>
+        <v>15.3</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Delta Live Tables, Spark, PySpark, Scala</t>
+          <t>RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Delta Live Tables, Spark, PySpark, Scala, Data Modeling</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3249c7729c4e3bf1</t>
+          <t>https://www.indeed.com/viewjob?jk=bc974eac3e508ce6</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>SOW198 Platform Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>13.9</v>
+        <v>15.3</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Spark, PySpark, Scala, Kafka, Cassandra, NoSQL</t>
+          <t>RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Delta Live Tables, Spark, PySpark, Scala, Data Modeling</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6dbc4fb78c7362b3</t>
+          <t>https://www.indeed.com/viewjob?jk=e85b5d56e27bdfb8</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Composable Commerce Solution Architect</t>
+          <t>Cloud Engineer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Litmus7 System Consulting</t>
+          <t>Willdan</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Anaheim, CA, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>13.9</v>
+        <v>15.3</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, SQS, SNS, API Gateway, Azure, GCP, Kafka, Oracle, MySQL</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, Azure, Scala, Amazon QuickSight, CI/CD</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,32 +1126,32 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2596f5d3398a102f</t>
+          <t>https://www.indeed.com/viewjob?jk=8d1298ac76effc74</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Azure Databricks &amp; Agentic AI Architect</t>
+          <t>Senior Engineer I</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>American Express</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>13.9</v>
+        <v>15.3</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Databricks, Unity Catalog, Delta Live Tables, Spark, PySpark, Scala, Data Modeling, ETL</t>
+          <t>AWS, IAM, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Spark, Scala</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,32 +1161,32 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=02432aa1dd6c57d9</t>
+          <t>https://www.indeed.com/viewjob?jk=4ca08863d5287990</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Sr. ML Engineer</t>
+          <t>Back-end Engineer - Data Platforms</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Visa</t>
+          <t>Morgan Stanley</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>13.2</v>
+        <v>14.6</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Spark, Scala, MLOps, MLflow, CI/CD, Terraform</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Spark, PySpark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,67 +1196,67 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f84e409aaaf551e7</t>
+          <t>https://www.indeed.com/viewjob?jk=ebb387f8fd246816</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Part Time Teller (20 Hours), Castro Branch</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Imperial Brady</t>
+          <t>Citi</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Rutherford, NJ, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>13.2</v>
+        <v>14.6</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Medallion Architecture, Spark, PySpark, Scala, Data Modeling, Dimensional Modeling</t>
+          <t>AWS, Lambda, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=49e6c0c32c4bdcc7</t>
+          <t>https://www.indeed.com/viewjob?jk=62e481a61bf24644</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Agentic AI Databricks</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>WorkOS</t>
+          <t>LTM Limited</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Raritan, NJ, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>13.2</v>
+        <v>14.6</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, ECS, IAM, RDS, Scala, Snowflake, Data Modeling, ETL, dbt, CI/CD</t>
+          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Unity Catalog, Delta Live Tables, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,67 +1266,67 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=93c58ad8f77c200b</t>
+          <t>https://www.indeed.com/viewjob?jk=611badfabe276aeb</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Summer 2027 Intern: Data Engineering</t>
+          <t>Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Live Oak Bank</t>
+          <t>Seek Now</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Wilmington, NC, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>13.2</v>
+        <v>14.6</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, RDS, Databricks, Spark, Scala, Kafka, Snowflake, Data Modeling</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, Scala, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=130366fb5d7d749c</t>
+          <t>https://www.indeed.com/viewjob?jk=86d6727803939178</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Engineer – Application</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>US Tiger Securities</t>
+          <t>Federated Hermes</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Warrendale, PA, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>12.5</v>
+        <v>13.9</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, Redshift, S3, RDS, Hive, Spark, PySpark, Kafka, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Delta Live Tables, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,32 +1336,32 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=573ee0a7b1fef58d</t>
+          <t>https://www.indeed.com/viewjob?jk=3249c7729c4e3bf1</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Senior Data Engineer, Observability Engineering</t>
+          <t>SOW198 Platform Engineer</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>MA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>12.5</v>
+        <v>13.9</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Spark, PySpark, Scala, ELT, CI/CD</t>
+          <t>AWS, RDS, Azure, Databricks, Spark, PySpark, Scala, Kafka, Cassandra, NoSQL</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,32 +1371,32 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fd7165608cf370f2</t>
+          <t>https://www.indeed.com/viewjob?jk=6dbc4fb78c7362b3</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Senior Data Engineer, Observability Engineering</t>
+          <t>Software Engineer III - AI Native Development</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>PA, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>12.5</v>
+        <v>13.9</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Spark, PySpark, Scala, ELT, CI/CD</t>
+          <t>AWS, Lambda, Kinesis, S3, SQS, SNS, API Gateway, ECS, RDS, Scala</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,32 +1406,32 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7a99a75f70479356</t>
+          <t>https://www.indeed.com/viewjob?jk=ea9ef8693c4fa599</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Senior Data Engineer, Observability Engineering</t>
+          <t>Azure Databricks &amp; Agentic AI Architect</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>MI, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>12.5</v>
+        <v>13.9</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Spark, PySpark, Scala, ELT, CI/CD</t>
+          <t>Azure, Data Factory, Databricks, Unity Catalog, Delta Live Tables, Spark, PySpark, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,32 +1441,32 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0993a1ced84ff494</t>
+          <t>https://www.indeed.com/viewjob?jk=02432aa1dd6c57d9</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Senior Data Engineer, Observability Engineering</t>
+          <t>Sr. ML Engineer</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Visa</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Spark, PySpark, Scala, ELT, CI/CD</t>
+          <t>AWS, S3, IAM, RDS, Spark, Scala, MLOps, MLflow, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,32 +1476,32 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=297ea1a332be0e9f</t>
+          <t>https://www.indeed.com/viewjob?jk=f84e409aaaf551e7</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Senior Data Engineer, Observability Engineering</t>
+          <t>Integration Architect</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Penske Truck Leasing</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>IL, US USA</t>
+          <t>Reading, PA, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Spark, PySpark, Scala, ELT, CI/CD</t>
+          <t>AWS, API Gateway, RDS, Azure, GCP, Scala, Kafka, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,32 +1511,32 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=81e443465ca87ae2</t>
+          <t>https://www.indeed.com/viewjob?jk=bfceaaf0e0e2e9a5</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Senior Data Engineer, Observability Engineering</t>
+          <t>Full Stack Senior Software Engineer (Remote in CA)</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>FCT</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>CT, US USA</t>
+          <t>Santa Ana, CA, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Spark, PySpark, Scala, ELT, CI/CD</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,32 +1546,32 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e39056943f43af2b</t>
+          <t>https://www.indeed.com/viewjob?jk=70278c6707b92e9e</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Senior Data Engineer, Observability Engineering</t>
+          <t>Full Stack Senior Software Engineer (Remote in CA)</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>FCT</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>VA, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Spark, PySpark, Scala, ELT, CI/CD</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,32 +1581,32 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e363619a2524b8aa</t>
+          <t>https://www.indeed.com/viewjob?jk=a25e08cbc61c8f9c</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Senior Data Engineer, Observability Engineering</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>WorkOS</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>NY, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Spark, PySpark, Scala, ELT, CI/CD</t>
+          <t>AWS, ECS, IAM, RDS, Scala, Snowflake, Data Modeling, ETL, dbt, CI/CD</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,32 +1616,32 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=901a1050af2afd7e</t>
+          <t>https://www.indeed.com/viewjob?jk=93c58ad8f77c200b</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Senior Data Engineer, Observability Engineering</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Imperial Brady</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>MD, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Spark, PySpark, Scala, ELT, CI/CD</t>
+          <t>AWS, RDS, Azure, Databricks, Medallion Architecture, Spark, PySpark, Scala, Data Modeling, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,24 +1651,24 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=52db018588005157</t>
+          <t>https://www.indeed.com/viewjob?jk=49e6c0c32c4bdcc7</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Senior Data Engineer, Observability Engineering</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>US Tiger Securities</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>AZ, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,7 +1676,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Spark, PySpark, Scala, ELT, CI/CD</t>
+          <t>AWS, Redshift, S3, RDS, Hive, Spark, PySpark, Kafka, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,24 +1686,24 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=27c43d5e88d9c28b</t>
+          <t>https://www.indeed.com/viewjob?jk=573ee0a7b1fef58d</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Forward Deployed Engineer, Client Solutions Group</t>
+          <t>Senior Cloud / AWS Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>The Carlyle Group</t>
+          <t>Reflex Media Inc</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,34 +1711,34 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, API Gateway, ECS, RDS, Databricks, Scala, Snowflake</t>
+          <t>AWS, Lambda, Redshift, S3, ECS, IAM, RDS, PostgreSQL, MySQL, CI/CD</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3cba42b7feabaab8</t>
+          <t>https://www.indeed.com/viewjob?jk=901aac12afba9b93</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>ML Search Engineer</t>
+          <t>Senior Data Engineer, Observability Engineering</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>DEPLOY</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Birmingham, AL, US USA</t>
+          <t>MA, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,77 +1746,77 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Oracle, PostgreSQL, MySQL, MongoDB, DynamoDB</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Spark, PySpark, Scala, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a56139b7af15b128</t>
+          <t>https://www.indeed.com/viewjob?jk=fd7165608cf370f2</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Sr Software Engineer I</t>
+          <t>Senior Data Engineer, Observability Engineering</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>RWE</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>PA, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>RDS, Azure, ETL, CI/CD, Azure DevOps, Terraform, Kubernetes, AKS, Airflow, Apache Airflow</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Spark, PySpark, Scala, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f6ad43066e853c35</t>
+          <t>https://www.indeed.com/viewjob?jk=7a99a75f70479356</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Data Engineer-5</t>
+          <t>Senior Data Engineer, Observability Engineering</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>MI, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, RDS, Scala, Snowflake, Data Modeling, ETL, ELT, dbt</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Spark, PySpark, Scala, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,102 +1826,102 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bb259aa46cf4c5ed</t>
+          <t>https://www.indeed.com/viewjob?jk=0993a1ced84ff494</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Data Engineer, Observability Engineering</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Evans Transportation Services</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Delafield, WI, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Azure, Scala, Data Modeling, Dimensional Modeling, ETL, ELT, dbt, CI/CD, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Spark, PySpark, Scala, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c4cfeccf055dd0aa</t>
+          <t>https://www.indeed.com/viewjob?jk=297ea1a332be0e9f</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Data Engineer, Observability Engineering</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Community Choice Credit Union</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Jackson, MI, US USA</t>
+          <t>IL, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Scala, Snowflake, SQL Server, Data Modeling, ETL, ELT, Power BI</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Spark, PySpark, Scala, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dad209d8bad2edfe</t>
+          <t>https://www.indeed.com/viewjob?jk=81e443465ca87ae2</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Consultant, Data &amp; Analytics, NA</t>
+          <t>Senior Data Engineer, Observability Engineering</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>The Coca-Cola Company</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>CT, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Scala, ETL, ELT, Power BI, Tableau, Git</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Spark, PySpark, Scala, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,32 +1931,32 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=df7e6baa7a7dd0a0</t>
+          <t>https://www.indeed.com/viewjob?jk=e39056943f43af2b</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Sr Java MS Developer</t>
+          <t>Senior Data Engineer, Observability Engineering</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>VA, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, NoSQL, CI/CD, Jenkins, Docker</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Spark, PySpark, Scala, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,32 +1966,32 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e4991e3d38b8257d</t>
+          <t>https://www.indeed.com/viewjob?jk=e363619a2524b8aa</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Full Stack Architect – AI &amp; Intelligent Applications</t>
+          <t>Senior Data Engineer, Observability Engineering</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Excelerate Technologies</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>NY, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Vertex AI, Scala, PostgreSQL, MySQL, MongoDB, NoSQL</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Spark, PySpark, Scala, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,67 +2001,67 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5f02d3f19c8a05a4</t>
+          <t>https://www.indeed.com/viewjob?jk=901a1050af2afd7e</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Data Architect, Corporate Services</t>
+          <t>Senior Data Engineer, Observability Engineering</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>The Carlyle Group</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>MD, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Snowflake, Data Modeling, Microsoft SSIS, dbt, Power BI, CI/CD</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Spark, PySpark, Scala, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5c3007521d1e10c7</t>
+          <t>https://www.indeed.com/viewjob?jk=52db018588005157</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>Senior Data Engineer, Observability Engineering</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>SBA Communications</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Boca Raton, FL, US USA</t>
+          <t>AZ, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Dataflow, Scala, Data Modeling, dbt, Power BI, CI/CD</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Spark, PySpark, Scala, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,32 +2071,32 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=31b2e27b37e8f33d</t>
+          <t>https://www.indeed.com/viewjob?jk=27c43d5e88d9c28b</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Databricks Platform Engineer</t>
+          <t>Data Analyst - ERP &amp; Master Data</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Booz Allen Hamilton</t>
+          <t>TransTech Group</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Unity Catalog, Scala, ELT, Splunk, DataOps, MLOps, CI/CD, GitHub Actions</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Medallion Architecture, Dataflow, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,137 +2106,137 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6d89b1928ab17ec0</t>
+          <t>https://www.indeed.com/viewjob?jk=49c2343d736f4c5c</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Sr. Solutions Engineer - Games</t>
+          <t>Azure Solutions Architect - Presales</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>TTEC Digital</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Southwest, PA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, GCP, Hadoop, Spark, Kafka</t>
+          <t>Azure, Data Factory, Synapse Analytics, Databricks, Scala, ETL, Power BI, Azure DevOps, Terraform, AKS</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f26bdcd885bb50ab</t>
+          <t>https://www.indeed.com/viewjob?jk=9d1ac466d0b2792d</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Sr. Solutions Engineer - Games</t>
+          <t>Software Development Engineer II</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>GM Financial</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>Arlington, TX, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, GCP, Hadoop, Spark, Kafka</t>
+          <t>Azure, Scala, Oracle, SQL Server, NoSQL, Jenkins, Azure DevOps, Maven, Terraform, Docker</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a723ab4c325b874f</t>
+          <t>https://www.indeed.com/viewjob?jk=77c13363e54e5087</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Full-Stack Engineer 5 (Java, AWS, Kafka)</t>
+          <t>Forward Deployed Engineer, Client Solutions Group</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>The Carlyle Group</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Riverwoods, IL, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, NoSQL, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, Lambda, Step Functions, S3, API Gateway, ECS, RDS, Databricks, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=df64f895efc7335d</t>
+          <t>https://www.indeed.com/viewjob?jk=3cba42b7feabaab8</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Data Engineer - AWS, Snowflake</t>
+          <t>Sr Data Engineer II</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Regions Financial</t>
+          <t>American Express</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Hoover, AL, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, RDS, Hadoop, Hive, Impala, Spark, PySpark, Scala, Kafka, Snowflake</t>
+          <t>AWS, RDS, HBase, Spark, Scala, Kafka, Cassandra, NoSQL, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,137 +2246,137 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e3740b07510bf369</t>
+          <t>https://www.indeed.com/viewjob?jk=a9b4607cbdf4a3d4</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Integration Engineer 3 (Email/ProofPoint)</t>
+          <t>Sr Software Engineer I</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>RWE</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Splunk, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
+          <t>RDS, Azure, ETL, CI/CD, Azure DevOps, Terraform, Kubernetes, AKS, Airflow, Apache Airflow</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=957ee504301bf4ad</t>
+          <t>https://www.indeed.com/viewjob?jk=f6ad43066e853c35</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Capital One Shopping Tech, Full - stack Engineer 5 (Remote - Eligible)</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>Pika</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
+          <t>AWS, Kinesis, Redshift, GCP, BigQuery, Scala, Kafka, Snowflake, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6ad38031a1a71b92</t>
+          <t>https://www.indeed.com/viewjob?jk=126cb889e15ed9cd</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Full-stack Engineer 4</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>Hollstadt Consulting</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Cambridge, MA, US USA</t>
+          <t>MN, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
+          <t>S3, IAM, RDS, Azure, Google Cloud Platform, GCP, Cloud Storage, Scala, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9f035e4925235bc7</t>
+          <t>https://www.indeed.com/viewjob?jk=9488041a67901dc1</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Engineer-5</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Dropbox</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Kinesis, RDS, Databricks, Medallion Architecture, Spark, Scala, Kafka, Data Modeling, Airflow, Python</t>
+          <t>AWS, Lambda, S3, RDS, Scala, Snowflake, Data Modeling, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,42 +2386,42 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=43e37e262d8bc84b</t>
+          <t>https://www.indeed.com/viewjob?jk=bb259aa46cf4c5ed</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Databricks Platform Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Booz Allen Hamilton</t>
+          <t>Community Choice Credit Union</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Warren, MI, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Unity Catalog, Scala, ELT, Splunk, DataOps, MLOps, GitHub Actions, Terraform</t>
+          <t>RDS, Azure, Data Factory, Scala, Snowflake, SQL Server, Data Modeling, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d727a12d260ca4e6</t>
+          <t>https://www.indeed.com/viewjob?jk=21899fbf482a9cd2</t>
         </is>
       </c>
     </row>
@@ -2433,195 +2433,195 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>DriveTime Automotive Group</t>
+          <t>Community Choice Credit Union</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Tempe, AZ, US USA</t>
+          <t>Jackson, MI, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>RDS, Scala, Kafka, Snowflake, SQL Server, Data Modeling, ETL, ELT, dbt, Python</t>
+          <t>RDS, Azure, Data Factory, Scala, Snowflake, SQL Server, Data Modeling, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=05afa083475c5a6e</t>
+          <t>https://www.indeed.com/viewjob?jk=9457f2c72938dbd5</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Senior Software Engineer (Data Platform)</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>MIA Labs</t>
+          <t>Community Choice Credit Union</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Holland, MI, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, BigQuery, Scala, Snowflake, Data Modeling, Dimensional Modeling, ELT, dbt</t>
+          <t>RDS, Azure, Data Factory, Scala, Snowflake, SQL Server, Data Modeling, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f1a60bd31f33e718</t>
+          <t>https://www.indeed.com/viewjob?jk=6f79614628dc966f</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Senior Cloud Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Sentara</t>
+          <t>Community Choice Credit Union</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Norfolk, VA, US USA</t>
+          <t>Farmington Hills, MI, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Scala, MLOps, MLflow, CI/CD, Terraform</t>
+          <t>RDS, Azure, Data Factory, Scala, Snowflake, SQL Server, Data Modeling, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=153b2eeea635cc15</t>
+          <t>https://www.indeed.com/viewjob?jk=fc4be70d8a478d8a</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Senior Disputes Data Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Velera</t>
+          <t>Community Choice Credit Union</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Jackson, MI, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Synapse Analytics, Databricks, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>RDS, Azure, Data Factory, Scala, Snowflake, SQL Server, Data Modeling, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a8ade8cb2af18f57</t>
+          <t>https://www.indeed.com/viewjob?jk=dad209d8bad2edfe</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>DevSecOps Engineer</t>
+          <t>Consultant, Data &amp; Analytics, NA</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>The Coca-Cola Company</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, PostgreSQL, MongoDB, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Databricks, Scala, ETL, ELT, Power BI, Tableau, Git</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ebe326f7d1fbe7e4</t>
+          <t>https://www.indeed.com/viewjob?jk=df7e6baa7a7dd0a0</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>C# Full Stack Developer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Globant</t>
+          <t>Intentsify</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Scala, SQL Server, PostgreSQL, MySQL, CI/CD, Docker</t>
+          <t>AWS, S3, SQS, SNS, IAM, Snowflake, ETL, ELT, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,102 +2631,102 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d96c65fe6b68f304</t>
+          <t>https://www.indeed.com/viewjob?jk=6d89a533339b416c</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Berkley</t>
+          <t>SBA Communications</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Urbandale, IA, US USA</t>
+          <t>Boca Raton, FL, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Scala, SQL Server, ETL, CI/CD, Jenkins, GitHub Actions, Jenkins</t>
+          <t>RDS, Azure, Data Factory, Databricks, Dataflow, Scala, Data Modeling, dbt, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b97d1598e22dfa41</t>
+          <t>https://www.indeed.com/viewjob?jk=31b2e27b37e8f33d</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Forward Deployed AI Engineer 2026 - US, COL, UK</t>
+          <t>Data Architect, Corporate Services</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Aimpoint Digital</t>
+          <t>The Carlyle Group</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, Scala, Snowflake, ETL, ELT, MLOps, CI/CD</t>
+          <t>AWS, RDS, Azure, Databricks, Snowflake, Data Modeling, Microsoft SSIS, dbt, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=64c74cca4e3efa95</t>
+          <t>https://www.indeed.com/viewjob?jk=5c3007521d1e10c7</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Databricks Platform Engineer</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Activated Insights</t>
+          <t>Booz Allen Hamilton</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, EMR, S3, RDS, Scala, Snowflake, PostgreSQL, MySQL, ETL, CI/CD</t>
+          <t>RDS, Databricks, Unity Catalog, Scala, ELT, Splunk, DataOps, MLOps, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2736,24 +2736,24 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4c98c8e05297ceda</t>
+          <t>https://www.indeed.com/viewjob?jk=6d89b1928ab17ec0</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Data Engineer - AWS, Snowflake</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Activated Insights</t>
+          <t>Regions Financial</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Idaho Falls, ID, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2761,7 +2761,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, EMR, S3, RDS, Scala, Snowflake, PostgreSQL, MySQL, ETL, CI/CD</t>
+          <t>AWS, RDS, Hadoop, Hive, Impala, Spark, PySpark, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2771,24 +2771,24 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7382a9e2385f01a9</t>
+          <t>https://www.indeed.com/viewjob?jk=e3740b07510bf369</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Senior AI Engineer - US</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Typeform</t>
+          <t>WellSky</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Overland Park, KS, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,7 +2796,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, RDS, Spark, Scala, Kafka, Snowflake, MLflow, Terraform, Docker, Kubernetes</t>
+          <t>RDS, GCP, BigQuery, Scala, SQL Server, Data Modeling, ETL, ELT, dbt, Tableau</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,24 +2806,24 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3c765384ad0b074b</t>
+          <t>https://www.indeed.com/viewjob?jk=1d0888bf081a07cc</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Full-stack Engineer 4</t>
+          <t>Data Engineer II - AWS/PySpark/ETL</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,7 +2831,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
+          <t>AWS, RDS, Databricks, Spark, PySpark, Scala, Snowflake, ETL, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,32 +2841,32 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a6e4280958473ee4</t>
+          <t>https://www.indeed.com/viewjob?jk=aa1cc23a36ed4493</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer 4 (Python, AWS, SQL, GenAI) (Enterprise Platforms Technology)</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>Dropbox</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, CI/CD, Kubernetes, Python, SQL</t>
+          <t>Kinesis, RDS, Databricks, Medallion Architecture, Spark, Scala, Kafka, Data Modeling, Airflow, Python</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2876,32 +2876,32 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4922f7a57cfbdccb</t>
+          <t>https://www.indeed.com/viewjob?jk=43e37e262d8bc84b</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer 4 (Python, AWS, SQL, GenAI) (Enterprise Platforms Technology)</t>
+          <t>Databricks Platform Engineer</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>Booz Allen Hamilton</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, CI/CD, Kubernetes, Python, SQL</t>
+          <t>RDS, Databricks, Unity Catalog, Scala, ELT, Splunk, DataOps, MLOps, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2911,159 +2911,159 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=09348324e49b31d7</t>
+          <t>https://www.indeed.com/viewjob?jk=d727a12d260ca4e6</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Software Engineer Full Stack / Backend I (Intern) â€“ United States</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Cisco</t>
+          <t>DriveTime Automotive Group</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Tempe, AZ, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes, Jenkins</t>
+          <t>RDS, Scala, Kafka, Snowflake, SQL Server, Data Modeling, ETL, ELT, dbt, Python</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=12750212f2a3c980</t>
+          <t>https://www.indeed.com/viewjob?jk=05afa083475c5a6e</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Integration Engineer 4 (Email / Proofpoint)</t>
+          <t>Senior Software Engineer (Data Platform)</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>MIA Labs</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, RDS, Azure, GCP, Scala, Splunk, Jenkins, Jenkins</t>
+          <t>AWS, Azure, GCP, BigQuery, Scala, Snowflake, Data Modeling, Dimensional Modeling, ELT, dbt</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9efe526fa2eec9b7</t>
+          <t>https://www.indeed.com/viewjob?jk=f1a60bd31f33e718</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Full Stack Engineer 4- People Tech- GenAI &amp; Agentic Systems (LangChain, LangGraph)</t>
+          <t>Associate Solution Architect with Modernization Experience</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
+          <t>AWS, Azure, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8f4dd8ad82c941e3</t>
+          <t>https://www.indeed.com/viewjob?jk=c343a7d6432ffeaa</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Integration Engineer 4 (MAC)</t>
+          <t>Associate Solution Architect with Modernization Experience</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Tempe, AZ, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, RDS, Azure, GCP, Scala, Splunk, Jenkins, Jenkins</t>
+          <t>AWS, Azure, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d4e76e5180e0ec43</t>
+          <t>https://www.indeed.com/viewjob?jk=e60054b9631d7895</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Integration Engineer 4 (SAM)</t>
+          <t>Associate Solution Architect with Modernization Experience</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -3072,186 +3072,186 @@
         </is>
       </c>
       <c r="D76" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, RDS, Azure, GCP, Scala, Splunk, Jenkins, Jenkins</t>
+          <t>AWS, Azure, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e81d19fb4dc37cf8</t>
+          <t>https://www.indeed.com/viewjob?jk=99aade9079199e44</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Cloud Platform Engineer - GCP</t>
+          <t>Associate Solution Architect with Modernization Experience</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>ASML</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Wilton, CT, US USA</t>
+          <t>Las Vegas, NV, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>IAM, RDS, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes</t>
+          <t>AWS, Azure, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e7d98e46591e0185</t>
+          <t>https://www.indeed.com/viewjob?jk=fb5a4840f3df3c6d</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Associate Solution Architect with Modernization Experience</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Ness Digital Engineering</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Morristown, NJ, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Unity Catalog, Medallion Architecture, GCP, Spark, PySpark, ELT, CI/CD</t>
+          <t>AWS, Azure, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a0412f267d3b3a64</t>
+          <t>https://www.indeed.com/viewjob?jk=55abd889581cdc48</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Data &amp; AI Engineer</t>
+          <t>Associate Solution Architect with Modernization Experience</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>The Carlyle Group</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Detroit, MI, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Spark, Scala, Snowflake, ELT, dbt, MLflow, CI/CD</t>
+          <t>AWS, Azure, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=83876c66e135b993</t>
+          <t>https://www.indeed.com/viewjob?jk=e3febde783536e21</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Data &amp; AI Engineer</t>
+          <t>Associate Solution Architect with Modernization Experience</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>The Carlyle Group</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Spark, Scala, Snowflake, ELT, dbt, MLflow, CI/CD</t>
+          <t>AWS, Azure, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f4924b3389452957</t>
+          <t>https://www.indeed.com/viewjob?jk=1be19f91eec7a842</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Technical Engineer (Production Liability Engineer)</t>
+          <t>Associate Solution Architect with Modernization Experience</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>M&amp;T Bank</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Buffalo, NY, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, REST API integration, Splunk, CI/CD, AKS, Datadog, Azure Monitor, Python</t>
+          <t>AWS, Azure, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -3261,32 +3261,32 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bef57255c79d57a0</t>
+          <t>https://www.indeed.com/viewjob?jk=7698c96689f48a9e</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Gen AI Engineer-5</t>
+          <t>Associate Solution Architect with Modernization Experience</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, API Gateway, IAM, Scala, PostgreSQL, DynamoDB, CI/CD, CloudWatch</t>
+          <t>AWS, Azure, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -3296,67 +3296,67 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4fcc298a65fe517f</t>
+          <t>https://www.indeed.com/viewjob?jk=d2e1386f9d607f38</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Senior Software Developer</t>
+          <t>Associate Solution Architect with Modernization Experience</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Trimark Associates, Inc.</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Folsom, CA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, Data Modeling, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, Azure, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=79b1c5092cba886d</t>
+          <t>https://www.indeed.com/viewjob?jk=2f2ca862816ed069</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Sr Software Engineer</t>
+          <t>Associate Solution Architect with Modernization Experience</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Resideo</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Event Hubs, Scala, NoSQL, Data Modeling, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, Azure, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -3366,32 +3366,32 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6f3ccdfade853d8f</t>
+          <t>https://www.indeed.com/viewjob?jk=a40909cafc968d82</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Full Stack (FES)</t>
+          <t>Associate Solution Architect with Modernization Experience</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Fanatics</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>AWS, SQS, SNS, IAM, RDS, Azure, GCP, Kafka, NoSQL, CI/CD</t>
+          <t>AWS, Azure, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -3401,32 +3401,32 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e95812a1a87ee87c</t>
+          <t>https://www.indeed.com/viewjob?jk=124344ebd08b7526</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Full Stack (FES)</t>
+          <t>Associate Solution Architect with Modernization Experience</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Fanatics</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>AWS, SQS, SNS, IAM, RDS, Azure, GCP, Kafka, NoSQL, CI/CD</t>
+          <t>AWS, Azure, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -3436,67 +3436,67 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f0dd1357e631ea44</t>
+          <t>https://www.indeed.com/viewjob?jk=f0ef6c1eb38b0db9</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Engineer, Performance Management</t>
+          <t>Associate Solution Architect with Modernization Experience</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>The Carlyle Group</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, SQL Server, ETL, Power BI, CI/CD, Git</t>
+          <t>AWS, Azure, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9e0346f80c455f7d</t>
+          <t>https://www.indeed.com/viewjob?jk=b780dcc242beb567</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer, JMG</t>
+          <t>Associate Solution Architect with Modernization Experience</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Keller Williams Realty</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Azure, Scala, SQL Server, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, Azure, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -3506,32 +3506,32 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2bd7eff3fbb2aa75</t>
+          <t>https://www.indeed.com/viewjob?jk=a03180188c81f9bf</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer, JMG</t>
+          <t>Associate Solution Architect with Modernization Experience</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Keller Williams Realty</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Azure, Scala, SQL Server, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, Azure, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -3541,42 +3541,1617 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=45f15d53aceb441c</t>
+          <t>https://www.indeed.com/viewjob?jk=8a037168850b8fe0</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>HPC Windows Server Infrastructure Engineer</t>
+          <t>Associate Solution Architect with Modernization Experience</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>KLA</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Milpitas, CA, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>AWS, Azure, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=45cd4b8d959d97ab</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>Associate Solution Architect with Modernization Experience</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>Dallas, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D91" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>AWS, Azure, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=52080037fabe4cb1</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>Associate Solution Architect with Modernization Experience</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>Cincinnati, OH, US USA</t>
+        </is>
+      </c>
+      <c r="D92" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>AWS, Azure, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=69224b4d176dd4a2</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>Associate Solution Architect with Modernization Experience</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>Kansas City, MO, US USA</t>
+        </is>
+      </c>
+      <c r="D93" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>AWS, Azure, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=5ce9dba6d19c8b82</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>Associate Solution Architect with Modernization Experience</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>Boston, MA, US USA</t>
+        </is>
+      </c>
+      <c r="D94" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>AWS, Azure, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=7c5344293aa5ed77</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>Associate Solution Architect with Modernization Experience</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>St. Louis, MO, US USA</t>
+        </is>
+      </c>
+      <c r="D95" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>AWS, Azure, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=fea3b3cc46faeb2a</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>Associate Solution Architect with Modernization Experience</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>Indianapolis, IN, US USA</t>
+        </is>
+      </c>
+      <c r="D96" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>AWS, Azure, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c3672ad48951be20</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>Associate Solution Architect with Modernization Experience</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>Raleigh, NC, US USA</t>
+        </is>
+      </c>
+      <c r="D97" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>AWS, Azure, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c45dff0f36a9a356</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>Associate Solution Architect with Modernization Experience</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D98" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>AWS, Azure, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=7e91b7a712b7a165</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>Associate Solution Architect with Modernization Experience</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>Jacksonville, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D99" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>AWS, Azure, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f3d69f9412407b80</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>Associate Solution Architect with Modernization Experience</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>Tampa, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D100" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>AWS, Azure, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=7d48fbbfaa3d0a97</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>Associate Solution Architect with Modernization Experience</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>Stamford, CT, US USA</t>
+        </is>
+      </c>
+      <c r="D101" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>AWS, Azure, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c300f1e448116fd7</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>Associate Solution Architect with Modernization Experience</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>Sacramento, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D102" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>AWS, Azure, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=316adbd72ad7e2e8</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>Associate Solution Architect with Modernization Experience</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>Costa Mesa, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D103" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>AWS, Azure, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f219232c6b6eef2b</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>Associate Solution Architect with Modernization Experience</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>San Francisco, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D104" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>AWS, Azure, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=0bb31aa937d723cd</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>Associate Solution Architect with Modernization Experience</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>Hartford, CT, US USA</t>
+        </is>
+      </c>
+      <c r="D105" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>AWS, Azure, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=884c614c785d6835</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>Associate Solution Architect with Modernization Experience</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>San Jose, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D106" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>AWS, Azure, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ecedaabbce0a0b5b</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>Associate Solution Architect with Modernization Experience</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>Denver, CO, US USA</t>
+        </is>
+      </c>
+      <c r="D107" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>AWS, Azure, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=eea12c90a4a047af</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>Associate Solution Architect with Modernization Experience</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>Chicago, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D108" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>AWS, Azure, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=28b6e9e7e6b5c6aa</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>Associate Solution Architect with Modernization Experience</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>Miami, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D109" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>AWS, Azure, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=2c0e09d9843111bd</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>Associate Solution Architect with Modernization Experience</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>Los Angeles, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D110" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>AWS, Azure, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=3b10af7d10426fa4</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>Solution Architect-Full Stack</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>Kirby Building Systems</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>Portland, TN, US USA</t>
+        </is>
+      </c>
+      <c r="D111" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Scala, SQL Server, PostgreSQL, CI/CD, Azure DevOps, Terraform, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=66ada823af164848</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>Data Scientist Associate</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>JPMorganChase</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>Wilmington, DE, US USA</t>
+        </is>
+      </c>
+      <c r="D112" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>RDS, Databricks, Scala, Snowflake, ETL, ELT, Tableau, Git, Python, SQL</t>
+        </is>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b87fe7f54c012f15</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>Sr Technical Analyst/Prog Ent App</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>Avangrid</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>Orange, CT, US USA</t>
+        </is>
+      </c>
+      <c r="D113" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, ETL, Azure DevOps, Git</t>
+        </is>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=4ea1b275b8152311</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>Full Stack Ad Tech Developer</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>The Hearst Corporation</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D114" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>AWS, Redshift, Google Cloud Platform, BigQuery, Scala, ETL, Tableau, CI/CD, Git, Python</t>
+        </is>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e8cf1f61c24a8358</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>C# Full Stack Developer</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>Globant</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>TX, US USA</t>
+        </is>
+      </c>
+      <c r="D115" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>AWS, S3, RDS, Azure, Scala, SQL Server, PostgreSQL, MySQL, CI/CD, Docker</t>
+        </is>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="G115" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d96c65fe6b68f304</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>Activated Insights</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>Dallas, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D116" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>AWS, EMR, S3, RDS, Scala, Snowflake, PostgreSQL, MySQL, ETL, CI/CD</t>
+        </is>
+      </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=4c98c8e05297ceda</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>Activated Insights</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>Idaho Falls, ID, US USA</t>
+        </is>
+      </c>
+      <c r="D117" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>AWS, EMR, S3, RDS, Scala, Snowflake, PostgreSQL, MySQL, ETL, CI/CD</t>
+        </is>
+      </c>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="G117" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=7382a9e2385f01a9</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>Forward Deployed AI Engineer 2026 - US, COL, UK</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>Aimpoint Digital</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>Atlanta, GA, US USA</t>
+        </is>
+      </c>
+      <c r="D118" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>AWS, Azure, Databricks, GCP, Scala, Snowflake, ETL, ELT, MLOps, CI/CD</t>
+        </is>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="G118" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=64c74cca4e3efa95</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>Machine Learning Engineer 4 (Python, AWS, SQL, GenAI) (Enterprise Platforms Technology)</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>Capital One</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D119" t="n">
         <v>10.4</v>
       </c>
-      <c r="E90" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Photon, Scala, CI/CD, Jenkins, Docker, Kubernetes, Jenkins</t>
-        </is>
-      </c>
-      <c r="F90" t="inlineStr">
-        <is>
-          <t>2026-09-22</t>
-        </is>
-      </c>
-      <c r="G90" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=518ee0c62a254d22</t>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, CI/CD, Kubernetes, Python, SQL</t>
+        </is>
+      </c>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="G119" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=4922f7a57cfbdccb</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>Machine Learning Engineer 4 (Python, AWS, SQL, GenAI) (Enterprise Platforms Technology)</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>Capital One</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D120" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, CI/CD, Kubernetes, Python, SQL</t>
+        </is>
+      </c>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="G120" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=09348324e49b31d7</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>Software Engineer Full Stack / Backend I (Intern) â€“ United States</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>Cisco</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>San Jose, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D121" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>AWS, Azure, GCP, Scala, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes, Jenkins</t>
+        </is>
+      </c>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="G121" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=12750212f2a3c980</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>Junior/Mid Software Engineer</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>Tampa, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D122" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>AWS, Azure, Google Cloud Platform, GCP, Hadoop, Spark, Scala, Kafka, NoSQL, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="G122" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d87ecb6d60b0f54d</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>Data Platform Engineer</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>Hubble Network</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>San Francisco, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D123" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>Kinesis, Redshift, RDS, Scala, Kafka, Dimensional Modeling, Star Schema, Fact Tables, ETL, dbt</t>
+        </is>
+      </c>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="G123" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a000c1d1d33d8b12</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>Data &amp; AI Engineer</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>The Carlyle Group</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>Washington, DC, US USA</t>
+        </is>
+      </c>
+      <c r="D124" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Databricks, Spark, Scala, Snowflake, ELT, dbt, MLflow, CI/CD</t>
+        </is>
+      </c>
+      <c r="F124" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="G124" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=83876c66e135b993</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>Data &amp; AI Engineer</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>The Carlyle Group</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D125" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Databricks, Spark, Scala, Snowflake, ELT, dbt, MLflow, CI/CD</t>
+        </is>
+      </c>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="G125" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f4924b3389452957</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>Sr. iOS Developer--Hybrid</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>Cognizant</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>Bridgewater, NJ, US USA</t>
+        </is>
+      </c>
+      <c r="D126" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>S3, RDS, Scala, PostgreSQL, MySQL, Cassandra, REST API integration, Jenkins, Jenkins, Git</t>
+        </is>
+      </c>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="G126" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a2f579d7993e4d2c</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>Sr Product Security Engineer, AI &amp; DevSecOps</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>McKesson</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>Columbus, OH, US USA</t>
+        </is>
+      </c>
+      <c r="D127" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Google Cloud Platform, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="G127" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=4b8ba8f92a1292eb</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>Sr Software Engineer</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>Resideo</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>Austin, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D128" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Event Hubs, Scala, NoSQL, Data Modeling, CI/CD, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="G128" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=6f3ccdfade853d8f</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer, Full Stack (FES)</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>Fanatics</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D129" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>AWS, SQS, SNS, IAM, RDS, Azure, GCP, Kafka, NoSQL, CI/CD</t>
+        </is>
+      </c>
+      <c r="F129" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="G129" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e95812a1a87ee87c</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer, Full Stack (FES)</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>Fanatics</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D130" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>AWS, SQS, SNS, IAM, RDS, Azure, GCP, Kafka, NoSQL, CI/CD</t>
+        </is>
+      </c>
+      <c r="F130" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="G130" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f0dd1357e631ea44</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>Data Engineer</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>Function Health</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D131" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t>RDS, Databricks, BigQuery, Spark, Kafka, Snowflake, ELT, dbt, MLOps, Terraform</t>
+        </is>
+      </c>
+      <c r="F131" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="G131" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=8d332f2047edfa45</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>Engineer, Performance Management</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>The Carlyle Group</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>Washington, DC, US USA</t>
+        </is>
+      </c>
+      <c r="D132" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Scala, Snowflake, SQL Server, ETL, Power BI, CI/CD, Git</t>
+        </is>
+      </c>
+      <c r="F132" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="G132" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=9e0346f80c455f7d</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>Sr. Software Engineer, JMG</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>Keller Williams Realty</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>Austin, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D133" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t>AWS, S3, IAM, RDS, Azure, Scala, SQL Server, CI/CD, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F133" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="G133" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=2bd7eff3fbb2aa75</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>Technical Engineer (Production Liability Engineer)</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>M&amp;T Bank</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>Buffalo, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D134" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E134" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Scala, REST API integration, Splunk, CI/CD, AKS, Datadog, Azure Monitor, Python</t>
+        </is>
+      </c>
+      <c r="F134" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="G134" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=bef57255c79d57a0</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>Sr. Software Engineer, JMG</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>Keller Williams Realty</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>Austin, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D135" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E135" t="inlineStr">
+        <is>
+          <t>AWS, S3, IAM, RDS, Azure, Scala, SQL Server, CI/CD, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F135" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="G135" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=45f15d53aceb441c</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-09-23.xlsx
+++ b/results/job_matches_2026-09-23.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G135"/>
+  <dimension ref="A1:G175"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,17 +678,17 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Data Engineer Sr</t>
+          <t>Associate Data Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Oshkosh Corporation</t>
+          <t>Blue Cross and Blue Shield of Minnesota</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Oshkosh, WI, US USA</t>
+          <t>Eagan, MN, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -696,7 +696,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Data Factory, Databricks, GCP, Hadoop, HDFS, Hive</t>
+          <t>AWS, Glue, EMR, Lambda, S3, SQS, SNS, RDS, Databricks, Spark</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,24 +706,24 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8b5c363397eafe5f</t>
+          <t>https://www.indeed.com/viewjob?jk=31bf226ac97de61e</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Associate Data Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Blue Cross and Blue Shield of Minnesota</t>
+          <t>Sally Beauty</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Eagan, MN, US USA</t>
+          <t>Denton, TX, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -731,7 +731,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, S3, SQS, SNS, RDS, Databricks, Spark</t>
+          <t>AWS, S3, RDS, Azure, Databricks, Data Lake Storage, Unity Catalog, Medallion Architecture, Delta Live Tables, Google Cloud Platform</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,24 +741,24 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=31bf226ac97de61e</t>
+          <t>https://www.indeed.com/viewjob?jk=0864fe655aae7888</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Engineer Sr</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Sally Beauty</t>
+          <t>Oshkosh Corporation</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Denton, TX, US USA</t>
+          <t>Oshkosh, WI, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -766,7 +766,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Databricks, Data Lake Storage, Unity Catalog, Medallion Architecture, Delta Live Tables, Google Cloud Platform</t>
+          <t>AWS, Redshift, RDS, Azure, Data Factory, Databricks, GCP, Hadoop, HDFS, Hive</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,24 +776,24 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0864fe655aae7888</t>
+          <t>https://www.indeed.com/viewjob?jk=8b5c363397eafe5f</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Enterprise Data Architect</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Alignment Health</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Orange, CA, US USA</t>
+          <t>RI, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -801,34 +801,34 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Scala, Snowflake, Data Modeling</t>
+          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1611fa9de2f7504b</t>
+          <t>https://www.indeed.com/viewjob?jk=8dd495afc5140159</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Senior AI Ops / DevOps Engineer</t>
+          <t>Enterprise Data Architect</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Alignment Health</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Orange, CA, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -836,7 +836,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Splunk, MLOps, MLflow, CI/CD, Jenkins</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Scala, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,32 +846,32 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=040c156b15abd039</t>
+          <t>https://www.indeed.com/viewjob?jk=1611fa9de2f7504b</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Data Engineer 4</t>
+          <t>Senior AI Ops / DevOps Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>16</v>
+        <v>16.7</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Redshift, RDS, Azure, Databricks, Spark, Scala, Snowflake</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Splunk, MLOps, MLflow, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,24 +881,24 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6438ee405fccd9e0</t>
+          <t>https://www.indeed.com/viewjob?jk=040c156b15abd039</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Engineer 5 - Enterprise Risk Management</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Tiger Analytics</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -906,7 +906,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Cloud Storage, Spark, PySpark, Scala, Snowflake</t>
+          <t>AWS, Glue, EMR, Redshift, RDS, Azure, Databricks, Spark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,24 +916,24 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4b2cb75552da28cb</t>
+          <t>https://www.indeed.com/viewjob?jk=a45f08af4f7be5f6</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Engineer 4 - Nexus Products</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Tiger Analytics</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -941,7 +941,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Cloud Storage, Spark, PySpark, Scala, Snowflake</t>
+          <t>AWS, Glue, EMR, Redshift, RDS, Azure, Databricks, Spark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,24 +951,24 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4b046b29ca6b7df4</t>
+          <t>https://www.indeed.com/viewjob?jk=36fc31dc37d05722</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - ai automation medical billing platform</t>
+          <t>Data Engineer 4</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Relentless Talent</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -976,34 +976,34 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL</t>
+          <t>AWS, Glue, EMR, Redshift, RDS, Azure, Databricks, Spark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=69d642c554413fbe</t>
+          <t>https://www.indeed.com/viewjob?jk=45e14228c1ed2aed</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - ai automation medical billing platform</t>
+          <t>Data Engineer 4 - Payment Networks</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Relentless Talent</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Buffalo, NY, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1011,112 +1011,112 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL</t>
+          <t>AWS, Glue, EMR, Redshift, RDS, Azure, Databricks, Spark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=818c7178aa0280e0</t>
+          <t>https://www.indeed.com/viewjob?jk=f8d0c3f139798fd9</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Senior Data Platfrom Engineer</t>
+          <t>Data Engineer 4 - HR Tech</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Delta Live Tables, Spark, PySpark, Scala, Data Modeling</t>
+          <t>AWS, Glue, EMR, Redshift, RDS, Azure, Databricks, Spark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bc974eac3e508ce6</t>
+          <t>https://www.indeed.com/viewjob?jk=010f3637940ea854</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Engineer 5 (SEO/GEO, AdTech )</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Delta Live Tables, Spark, PySpark, Scala, Data Modeling</t>
+          <t>AWS, Glue, EMR, Redshift, RDS, Azure, Databricks, Spark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e85b5d56e27bdfb8</t>
+          <t>https://www.indeed.com/viewjob?jk=e9a8f6941c1a4549</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Cloud Engineer</t>
+          <t>Data Engineer 4</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Willdan</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Anaheim, CA, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, Azure, Scala, Amazon QuickSight, CI/CD</t>
+          <t>AWS, Glue, EMR, Redshift, RDS, Azure, Databricks, Spark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,32 +1126,32 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8d1298ac76effc74</t>
+          <t>https://www.indeed.com/viewjob?jk=0db4720c664a5a3f</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Senior Engineer I</t>
+          <t>Data Engineer 4</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>American Express</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Spark, Scala</t>
+          <t>AWS, Glue, EMR, Redshift, RDS, Azure, Databricks, Spark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,19 +1161,19 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4ca08863d5287990</t>
+          <t>https://www.indeed.com/viewjob?jk=d80c6adab1193eaf</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Back-end Engineer - Data Platforms</t>
+          <t>Data Engineer 5 (Enterprise Platforms Technology)</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Morgan Stanley</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1182,11 +1182,11 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>14.6</v>
+        <v>16</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Spark, PySpark, Scala, Kafka</t>
+          <t>AWS, Glue, EMR, Redshift, RDS, Azure, Databricks, Spark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,67 +1196,67 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ebb387f8fd246816</t>
+          <t>https://www.indeed.com/viewjob?jk=220dab7fe793042b</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Part Time Teller (20 Hours), Castro Branch</t>
+          <t>Data Engineer 5</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Citi</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Rutherford, NJ, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>14.6</v>
+        <v>16</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, Lambda, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Kafka</t>
+          <t>AWS, Glue, EMR, Redshift, RDS, Azure, Databricks, Spark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=62e481a61bf24644</t>
+          <t>https://www.indeed.com/viewjob?jk=3a1e95e5123a2b15</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Agentic AI Databricks</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>LTM Limited</t>
+          <t>Tiger Analytics</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Raritan, NJ, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>14.6</v>
+        <v>16</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Unity Catalog, Delta Live Tables, Spark, PySpark, Scala</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Cloud Storage, Spark, PySpark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,67 +1266,67 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=611badfabe276aeb</t>
+          <t>https://www.indeed.com/viewjob?jk=4b2cb75552da28cb</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Seek Now</t>
+          <t>Tiger Analytics</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>14.6</v>
+        <v>16</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, Scala, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Cloud Storage, Spark, PySpark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=86d6727803939178</t>
+          <t>https://www.indeed.com/viewjob?jk=4b046b29ca6b7df4</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Engineer – Application</t>
+          <t>Data Engineer 4</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Federated Hermes</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Warrendale, PA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>13.9</v>
+        <v>16</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Delta Live Tables, Spark, PySpark, Scala</t>
+          <t>AWS, Glue, EMR, Redshift, RDS, Azure, Databricks, Spark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,84 +1336,84 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3249c7729c4e3bf1</t>
+          <t>https://www.indeed.com/viewjob?jk=6438ee405fccd9e0</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>SOW198 Platform Engineer</t>
+          <t>Senior Software Engineer - ai automation medical billing platform</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Relentless Talent</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>13.9</v>
+        <v>16</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Spark, PySpark, Scala, Kafka, Cassandra, NoSQL</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6dbc4fb78c7362b3</t>
+          <t>https://www.indeed.com/viewjob?jk=69d642c554413fbe</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Software Engineer III - AI Native Development</t>
+          <t>Senior Software Engineer - ai automation medical billing platform</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Relentless Talent</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Buffalo, NY, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>13.9</v>
+        <v>16</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, S3, SQS, SNS, API Gateway, ECS, RDS, Scala</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ea9ef8693c4fa599</t>
+          <t>https://www.indeed.com/viewjob?jk=818c7178aa0280e0</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Azure Databricks &amp; Agentic AI Architect</t>
+          <t>Senior Data Platfrom Engineer</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1423,37 +1423,37 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>13.9</v>
+        <v>15.3</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Databricks, Unity Catalog, Delta Live Tables, Spark, PySpark, Scala, Data Modeling, ETL</t>
+          <t>RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Delta Live Tables, Spark, PySpark, Scala, Data Modeling</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=02432aa1dd6c57d9</t>
+          <t>https://www.indeed.com/viewjob?jk=bc974eac3e508ce6</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Sr. ML Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Visa</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -1462,46 +1462,46 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>13.2</v>
+        <v>15.3</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Spark, Scala, MLOps, MLflow, CI/CD, Terraform</t>
+          <t>RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Delta Live Tables, Spark, PySpark, Scala, Data Modeling</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f84e409aaaf551e7</t>
+          <t>https://www.indeed.com/viewjob?jk=e85b5d56e27bdfb8</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Integration Architect</t>
+          <t>Cloud Engineer</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Penske Truck Leasing</t>
+          <t>Willdan</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Reading, PA, US USA</t>
+          <t>Anaheim, CA, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>13.2</v>
+        <v>15.3</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, GCP, Scala, Kafka, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, Azure, Scala, Amazon QuickSight, CI/CD</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,32 +1511,32 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bfceaaf0e0e2e9a5</t>
+          <t>https://www.indeed.com/viewjob?jk=8d1298ac76effc74</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Full Stack Senior Software Engineer (Remote in CA)</t>
+          <t>Back-end Engineer - Data Platforms</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>FCT</t>
+          <t>Morgan Stanley</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Santa Ana, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>13.2</v>
+        <v>14.6</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Spark, PySpark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,32 +1546,32 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=70278c6707b92e9e</t>
+          <t>https://www.indeed.com/viewjob?jk=ebb387f8fd246816</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Full Stack Senior Software Engineer (Remote in CA)</t>
+          <t>Agentic AI Databricks</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>FCT</t>
+          <t>LTM Limited</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>Raritan, NJ, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>13.2</v>
+        <v>14.6</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
+          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Unity Catalog, Delta Live Tables, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,67 +1581,67 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a25e08cbc61c8f9c</t>
+          <t>https://www.indeed.com/viewjob?jk=611badfabe276aeb</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>WorkOS</t>
+          <t>Seek Now</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>13.2</v>
+        <v>14.6</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, ECS, IAM, RDS, Scala, Snowflake, Data Modeling, ETL, dbt, CI/CD</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, Scala, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=93c58ad8f77c200b</t>
+          <t>https://www.indeed.com/viewjob?jk=86d6727803939178</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Database Engineer - onsite</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Imperial Brady</t>
+          <t>Eccalon</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Detroit, MI, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>13.2</v>
+        <v>14.6</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Medallion Architecture, Spark, PySpark, Scala, Data Modeling, Dimensional Modeling</t>
+          <t>Redshift, RDS, Azure, BigQuery, Scala, Snowflake, Oracle, SQL Server, Data Modeling, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,32 +1651,32 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=49e6c0c32c4bdcc7</t>
+          <t>https://www.indeed.com/viewjob?jk=e9489350e98d48c6</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>SOW198 Platform Engineer</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>US Tiger Securities</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>12.5</v>
+        <v>13.9</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, Redshift, S3, RDS, Hive, Spark, PySpark, Kafka, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, Databricks, Spark, PySpark, Scala, Kafka, Cassandra, NoSQL</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,32 +1686,32 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=573ee0a7b1fef58d</t>
+          <t>https://www.indeed.com/viewjob?jk=6dbc4fb78c7362b3</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Senior Cloud / AWS Infrastructure Engineer</t>
+          <t>Engineer – Application</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Reflex Media Inc</t>
+          <t>Federated Hermes</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Warrendale, PA, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>12.5</v>
+        <v>13.9</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, S3, ECS, IAM, RDS, PostgreSQL, MySQL, CI/CD</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Delta Live Tables, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,32 +1721,32 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=901aac12afba9b93</t>
+          <t>https://www.indeed.com/viewjob?jk=3249c7729c4e3bf1</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Senior Data Engineer, Observability Engineering</t>
+          <t>Software Engineer III - AI Native Development</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>MA, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>12.5</v>
+        <v>13.9</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Spark, PySpark, Scala, ELT, CI/CD</t>
+          <t>AWS, Lambda, Kinesis, S3, SQS, SNS, API Gateway, ECS, RDS, Scala</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,32 +1756,32 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fd7165608cf370f2</t>
+          <t>https://www.indeed.com/viewjob?jk=ea9ef8693c4fa599</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Senior Data Engineer, Observability Engineering</t>
+          <t>Azure Databricks &amp; Agentic AI Architect</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>PA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>12.5</v>
+        <v>13.9</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Spark, PySpark, Scala, ELT, CI/CD</t>
+          <t>Azure, Data Factory, Databricks, Unity Catalog, Delta Live Tables, Spark, PySpark, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,32 +1791,32 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7a99a75f70479356</t>
+          <t>https://www.indeed.com/viewjob?jk=02432aa1dd6c57d9</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Senior Data Engineer, Observability Engineering</t>
+          <t>Sr. ML Engineer</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Visa</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>MI, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Spark, PySpark, Scala, ELT, CI/CD</t>
+          <t>AWS, S3, IAM, RDS, Spark, Scala, MLOps, MLflow, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,32 +1826,32 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0993a1ced84ff494</t>
+          <t>https://www.indeed.com/viewjob?jk=f84e409aaaf551e7</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Senior Data Engineer, Observability Engineering</t>
+          <t>Integration Architect</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Penske Truck Leasing</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Reading, PA, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Spark, PySpark, Scala, ELT, CI/CD</t>
+          <t>AWS, API Gateway, RDS, Azure, GCP, Scala, Kafka, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,32 +1861,32 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=297ea1a332be0e9f</t>
+          <t>https://www.indeed.com/viewjob?jk=bfceaaf0e0e2e9a5</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Senior Data Engineer, Observability Engineering</t>
+          <t>Full Stack Senior Software Engineer (Remote in CA)</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>FCT</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>IL, US USA</t>
+          <t>Santa Ana, CA, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Spark, PySpark, Scala, ELT, CI/CD</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,32 +1896,32 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=81e443465ca87ae2</t>
+          <t>https://www.indeed.com/viewjob?jk=70278c6707b92e9e</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Senior Data Engineer, Observability Engineering</t>
+          <t>Full Stack Senior Software Engineer (Remote in CA)</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>FCT</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>CT, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Spark, PySpark, Scala, ELT, CI/CD</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,32 +1931,32 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e39056943f43af2b</t>
+          <t>https://www.indeed.com/viewjob?jk=a25e08cbc61c8f9c</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Senior Data Engineer, Observability Engineering</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>WorkOS</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>VA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Spark, PySpark, Scala, ELT, CI/CD</t>
+          <t>AWS, ECS, IAM, RDS, Scala, Snowflake, Data Modeling, ETL, dbt, CI/CD</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,32 +1966,32 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e363619a2524b8aa</t>
+          <t>https://www.indeed.com/viewjob?jk=93c58ad8f77c200b</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Senior Data Engineer, Observability Engineering</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Imperial Brady</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>NY, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Spark, PySpark, Scala, ELT, CI/CD</t>
+          <t>AWS, RDS, Azure, Databricks, Medallion Architecture, Spark, PySpark, Scala, Data Modeling, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,24 +2001,24 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=901a1050af2afd7e</t>
+          <t>https://www.indeed.com/viewjob?jk=49e6c0c32c4bdcc7</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Senior Data Engineer, Observability Engineering</t>
+          <t>Senior Cloud / AWS Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Reflex Media Inc</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>MD, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,7 +2026,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Spark, PySpark, Scala, ELT, CI/CD</t>
+          <t>AWS, Lambda, Redshift, S3, ECS, IAM, RDS, PostgreSQL, MySQL, CI/CD</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,24 +2036,24 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=52db018588005157</t>
+          <t>https://www.indeed.com/viewjob?jk=901aac12afba9b93</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Senior Data Engineer, Observability Engineering</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>US Tiger Securities</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>AZ, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2061,7 +2061,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Spark, PySpark, Scala, ELT, CI/CD</t>
+          <t>AWS, Redshift, S3, RDS, Hive, Spark, PySpark, Kafka, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,24 +2071,24 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=27c43d5e88d9c28b</t>
+          <t>https://www.indeed.com/viewjob?jk=573ee0a7b1fef58d</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Data Analyst - ERP &amp; Master Data</t>
+          <t>Sr Implementation Consultant</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>TransTech Group</t>
+          <t>Cotiviti</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2096,7 +2096,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Medallion Architecture, Dataflow, Spark, PySpark, Scala</t>
+          <t>AWS, Glue, ECS, RDS, Azure, Oracle, SQL Server, Data Modeling, ETL, Talend</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,24 +2106,24 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=49c2343d736f4c5c</t>
+          <t>https://www.indeed.com/viewjob?jk=feec9157e828c7c5</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Azure Solutions Architect - Presales</t>
+          <t>Data Analyst - ERP &amp; Master Data</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>TTEC Digital</t>
+          <t>TransTech Group</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,7 +2131,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Synapse Analytics, Databricks, Scala, ETL, Power BI, Azure DevOps, Terraform, AKS</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Medallion Architecture, Dataflow, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,24 +2141,24 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9d1ac466d0b2792d</t>
+          <t>https://www.indeed.com/viewjob?jk=49c2343d736f4c5c</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Software Development Engineer II</t>
+          <t>Azure Solutions Architect - Presales</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>GM Financial</t>
+          <t>TTEC Digital</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Arlington, TX, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,7 +2166,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Azure, Scala, Oracle, SQL Server, NoSQL, Jenkins, Azure DevOps, Maven, Terraform, Docker</t>
+          <t>Azure, Data Factory, Synapse Analytics, Databricks, Scala, ETL, Power BI, Azure DevOps, Terraform, AKS</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,24 +2176,24 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=77c13363e54e5087</t>
+          <t>https://www.indeed.com/viewjob?jk=9d1ac466d0b2792d</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Forward Deployed Engineer, Client Solutions Group</t>
+          <t>Software Development Engineer II</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>The Carlyle Group</t>
+          <t>GM Financial</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Arlington, TX, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,69 +2201,69 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, API Gateway, ECS, RDS, Databricks, Scala, Snowflake</t>
+          <t>Azure, Scala, Oracle, SQL Server, NoSQL, Jenkins, Azure DevOps, Maven, Terraform, Docker</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3cba42b7feabaab8</t>
+          <t>https://www.indeed.com/viewjob?jk=77c13363e54e5087</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Sr Data Engineer II</t>
+          <t>Forward Deployed Engineer, Client Solutions Group</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>American Express</t>
+          <t>The Carlyle Group</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, RDS, HBase, Spark, Scala, Kafka, Cassandra, NoSQL, MLOps, CI/CD</t>
+          <t>AWS, Lambda, Step Functions, S3, API Gateway, ECS, RDS, Databricks, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a9b4607cbdf4a3d4</t>
+          <t>https://www.indeed.com/viewjob?jk=3cba42b7feabaab8</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Sr Software Engineer I</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>RWE</t>
+          <t>Pika</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,17 +2271,17 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>RDS, Azure, ETL, CI/CD, Azure DevOps, Terraform, Kubernetes, AKS, Airflow, Apache Airflow</t>
+          <t>AWS, Kinesis, Redshift, GCP, BigQuery, Scala, Kafka, Snowflake, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f6ad43066e853c35</t>
+          <t>https://www.indeed.com/viewjob?jk=126cb889e15ed9cd</t>
         </is>
       </c>
     </row>
@@ -2293,12 +2293,12 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Pika</t>
+          <t>Hollstadt Consulting</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>MN, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,7 +2306,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, Redshift, GCP, BigQuery, Scala, Kafka, Snowflake, Data Modeling, ETL</t>
+          <t>S3, IAM, RDS, Azure, Google Cloud Platform, GCP, Cloud Storage, Scala, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,24 +2316,24 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=126cb889e15ed9cd</t>
+          <t>https://www.indeed.com/viewjob?jk=9488041a67901dc1</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Sr Data Engineer II</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Hollstadt Consulting</t>
+          <t>American Express</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>MN, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,7 +2341,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>S3, IAM, RDS, Azure, Google Cloud Platform, GCP, Cloud Storage, Scala, CI/CD, Azure DevOps</t>
+          <t>AWS, RDS, HBase, Spark, Scala, Kafka, Cassandra, NoSQL, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,7 +2351,7 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9488041a67901dc1</t>
+          <t>https://www.indeed.com/viewjob?jk=a9b4607cbdf4a3d4</t>
         </is>
       </c>
     </row>
@@ -2568,17 +2568,17 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Consultant, Data &amp; Analytics, NA</t>
+          <t>Sr Software Engineer I</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>The Coca-Cola Company</t>
+          <t>RWE</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,17 +2586,17 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Scala, ETL, ELT, Power BI, Tableau, Git</t>
+          <t>RDS, Azure, ETL, CI/CD, Azure DevOps, Terraform, Kubernetes, AKS, Airflow, Apache Airflow</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=df7e6baa7a7dd0a0</t>
+          <t>https://www.indeed.com/viewjob?jk=f6ad43066e853c35</t>
         </is>
       </c>
     </row>
@@ -2638,17 +2638,17 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>Consultant, Data &amp; Analytics, NA</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>SBA Communications</t>
+          <t>The Coca-Cola Company</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Boca Raton, FL, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,7 +2656,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Dataflow, Scala, Data Modeling, dbt, Power BI, CI/CD</t>
+          <t>AWS, RDS, Azure, Databricks, Scala, ETL, ELT, Power BI, Tableau, Git</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2666,24 +2666,24 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=31b2e27b37e8f33d</t>
+          <t>https://www.indeed.com/viewjob?jk=df7e6baa7a7dd0a0</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Data Architect, Corporate Services</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>The Carlyle Group</t>
+          <t>SBA Communications</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Boca Raton, FL, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,34 +2691,34 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Snowflake, Data Modeling, Microsoft SSIS, dbt, Power BI, CI/CD</t>
+          <t>RDS, Azure, Data Factory, Databricks, Dataflow, Scala, Data Modeling, dbt, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5c3007521d1e10c7</t>
+          <t>https://www.indeed.com/viewjob?jk=31b2e27b37e8f33d</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Databricks Platform Engineer</t>
+          <t>Data Architect, Corporate Services</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Booz Allen Hamilton</t>
+          <t>The Carlyle Group</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,42 +2726,42 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Unity Catalog, Scala, ELT, Splunk, DataOps, MLOps, CI/CD, GitHub Actions</t>
+          <t>AWS, RDS, Azure, Databricks, Snowflake, Data Modeling, Microsoft SSIS, dbt, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6d89b1928ab17ec0</t>
+          <t>https://www.indeed.com/viewjob?jk=5c3007521d1e10c7</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Data Engineer - AWS, Snowflake</t>
+          <t>Databricks Platform Engineer</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Regions Financial</t>
+          <t>Booz Allen Hamilton</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, RDS, Hadoop, Hive, Impala, Spark, PySpark, Scala, Kafka, Snowflake</t>
+          <t>RDS, Databricks, Unity Catalog, Scala, ELT, Splunk, DataOps, MLOps, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2771,24 +2771,24 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e3740b07510bf369</t>
+          <t>https://www.indeed.com/viewjob?jk=6d89b1928ab17ec0</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>WellSky</t>
+          <t>AMD</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Overland Park, KS, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,7 +2796,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>RDS, GCP, BigQuery, Scala, SQL Server, Data Modeling, ETL, ELT, dbt, Tableau</t>
+          <t>AWS, RDS, Azure, Databricks, Medallion Architecture, Spark, PySpark, Snowflake, dbt, Power BI</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,24 +2806,24 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1d0888bf081a07cc</t>
+          <t>https://www.indeed.com/viewjob?jk=9724e994419d2473</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Data Engineer II - AWS/PySpark/ETL</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>WellSky</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Overland Park, KS, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,7 +2831,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Spark, PySpark, Scala, Snowflake, ETL, CI/CD, Airflow</t>
+          <t>RDS, GCP, BigQuery, Scala, SQL Server, Data Modeling, ETL, ELT, dbt, Tableau</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,24 +2841,24 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aa1cc23a36ed4493</t>
+          <t>https://www.indeed.com/viewjob?jk=1d0888bf081a07cc</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Engineer II - AWS/PySpark/ETL</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Dropbox</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,7 +2866,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Kinesis, RDS, Databricks, Medallion Architecture, Spark, Scala, Kafka, Data Modeling, Airflow, Python</t>
+          <t>AWS, RDS, Databricks, Spark, PySpark, Scala, Snowflake, ETL, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2876,24 +2876,24 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=43e37e262d8bc84b</t>
+          <t>https://www.indeed.com/viewjob?jk=aa1cc23a36ed4493</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Databricks Platform Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Booz Allen Hamilton</t>
+          <t>Dropbox</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Unity Catalog, Scala, ELT, Splunk, DataOps, MLOps, GitHub Actions, Terraform</t>
+          <t>Kinesis, RDS, Databricks, Medallion Architecture, Spark, Scala, Kafka, Data Modeling, Airflow, Python</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2911,24 +2911,24 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d727a12d260ca4e6</t>
+          <t>https://www.indeed.com/viewjob?jk=43e37e262d8bc84b</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Databricks Platform Engineer</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>DriveTime Automotive Group</t>
+          <t>Booz Allen Hamilton</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Tempe, AZ, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,7 +2936,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>RDS, Scala, Kafka, Snowflake, SQL Server, Data Modeling, ETL, ELT, dbt, Python</t>
+          <t>RDS, Databricks, Unity Catalog, Scala, ELT, Splunk, DataOps, MLOps, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2946,24 +2946,24 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=05afa083475c5a6e</t>
+          <t>https://www.indeed.com/viewjob?jk=d727a12d260ca4e6</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Senior Software Engineer (Data Platform)</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>MIA Labs</t>
+          <t>DriveTime Automotive Group</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Tempe, AZ, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2971,7 +2971,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, BigQuery, Scala, Snowflake, Data Modeling, Dimensional Modeling, ELT, dbt</t>
+          <t>RDS, Scala, Kafka, Snowflake, SQL Server, Data Modeling, ETL, ELT, dbt, Python</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -2981,24 +2981,24 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f1a60bd31f33e718</t>
+          <t>https://www.indeed.com/viewjob?jk=05afa083475c5a6e</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Associate Solution Architect with Modernization Experience</t>
+          <t>Data Engineer - AWS, Snowflake</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Regions Financial</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Hoover, AL, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3006,7 +3006,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes</t>
+          <t>AWS, RDS, Hadoop, Hive, Impala, Spark, PySpark, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3016,24 +3016,24 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c343a7d6432ffeaa</t>
+          <t>https://www.indeed.com/viewjob?jk=e3740b07510bf369</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Associate Solution Architect with Modernization Experience</t>
+          <t>Senior Software Engineer (Data Platform)</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>MIA Labs</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Tempe, AZ, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3041,7 +3041,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes</t>
+          <t>AWS, Azure, GCP, BigQuery, Scala, Snowflake, Data Modeling, Dimensional Modeling, ELT, dbt</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3051,24 +3051,24 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e60054b9631d7895</t>
+          <t>https://www.indeed.com/viewjob?jk=f1a60bd31f33e718</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Associate Solution Architect with Modernization Experience</t>
+          <t>Full-stack Engineer 5 (Nodejs/Go/Angularjs)</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3076,7 +3076,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3086,24 +3086,24 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=99aade9079199e44</t>
+          <t>https://www.indeed.com/viewjob?jk=9813442a220867be</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Associate Solution Architect with Modernization Experience</t>
+          <t>Full-stack Engineer 4 - RiskTech</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Las Vegas, NV, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3111,7 +3111,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3121,24 +3121,24 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fb5a4840f3df3c6d</t>
+          <t>https://www.indeed.com/viewjob?jk=f2960b2498873f28</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Associate Solution Architect with Modernization Experience</t>
+          <t>Full-stack Engineer 4 (Golang, Python, Java, AWS)</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Morristown, NJ, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3146,7 +3146,7 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -3156,24 +3156,24 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=55abd889581cdc48</t>
+          <t>https://www.indeed.com/viewjob?jk=da278457dd975c3f</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Associate Solution Architect with Modernization Experience</t>
+          <t>Full-stack Engineer 4</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Detroit, MI, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3181,7 +3181,7 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -3191,24 +3191,24 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e3febde783536e21</t>
+          <t>https://www.indeed.com/viewjob?jk=18716e78985d34c6</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Associate Solution Architect with Modernization Experience</t>
+          <t>Full-stack Engineer 4 (Go, AWS)</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3216,7 +3216,7 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -3226,24 +3226,24 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1be19f91eec7a842</t>
+          <t>https://www.indeed.com/viewjob?jk=6132bb0eb6aaf86d</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Associate Solution Architect with Modernization Experience</t>
+          <t>Backend Developer</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>BRMi</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Vienna, VA, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3251,7 +3251,7 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes</t>
+          <t>RDS, Azure, Scala, Kafka, CI/CD, Jenkins, Azure DevOps, Maven, Docker, Jenkins</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -3261,24 +3261,24 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7698c96689f48a9e</t>
+          <t>https://www.indeed.com/viewjob?jk=fe1f889a04aac578</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Associate Solution Architect with Modernization Experience</t>
+          <t>Data Scientist Associate</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>Wilmington, DE, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3286,7 +3286,7 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes</t>
+          <t>RDS, Databricks, Scala, Snowflake, ETL, ELT, Tableau, Git, Python, SQL</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -3296,7 +3296,7 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d2e1386f9d607f38</t>
+          <t>https://www.indeed.com/viewjob?jk=b87fe7f54c012f15</t>
         </is>
       </c>
     </row>
@@ -3313,7 +3313,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3331,7 +3331,7 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2f2ca862816ed069</t>
+          <t>https://www.indeed.com/viewjob?jk=c343a7d6432ffeaa</t>
         </is>
       </c>
     </row>
@@ -3348,7 +3348,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Tempe, AZ, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3366,7 +3366,7 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a40909cafc968d82</t>
+          <t>https://www.indeed.com/viewjob?jk=e60054b9631d7895</t>
         </is>
       </c>
     </row>
@@ -3383,7 +3383,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3401,7 +3401,7 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=124344ebd08b7526</t>
+          <t>https://www.indeed.com/viewjob?jk=99aade9079199e44</t>
         </is>
       </c>
     </row>
@@ -3418,7 +3418,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Las Vegas, NV, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3436,7 +3436,7 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f0ef6c1eb38b0db9</t>
+          <t>https://www.indeed.com/viewjob?jk=fb5a4840f3df3c6d</t>
         </is>
       </c>
     </row>
@@ -3453,7 +3453,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Morristown, NJ, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3471,7 +3471,7 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b780dcc242beb567</t>
+          <t>https://www.indeed.com/viewjob?jk=55abd889581cdc48</t>
         </is>
       </c>
     </row>
@@ -3488,7 +3488,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Detroit, MI, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3506,7 +3506,7 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a03180188c81f9bf</t>
+          <t>https://www.indeed.com/viewjob?jk=e3febde783536e21</t>
         </is>
       </c>
     </row>
@@ -3523,7 +3523,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3541,7 +3541,7 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8a037168850b8fe0</t>
+          <t>https://www.indeed.com/viewjob?jk=1be19f91eec7a842</t>
         </is>
       </c>
     </row>
@@ -3558,7 +3558,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3576,7 +3576,7 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=45cd4b8d959d97ab</t>
+          <t>https://www.indeed.com/viewjob?jk=7698c96689f48a9e</t>
         </is>
       </c>
     </row>
@@ -3593,7 +3593,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -3611,7 +3611,7 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=52080037fabe4cb1</t>
+          <t>https://www.indeed.com/viewjob?jk=d2e1386f9d607f38</t>
         </is>
       </c>
     </row>
@@ -3628,7 +3628,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -3646,7 +3646,7 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=69224b4d176dd4a2</t>
+          <t>https://www.indeed.com/viewjob?jk=2f2ca862816ed069</t>
         </is>
       </c>
     </row>
@@ -3663,7 +3663,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Kansas City, MO, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
@@ -3681,7 +3681,7 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5ce9dba6d19c8b82</t>
+          <t>https://www.indeed.com/viewjob?jk=a40909cafc968d82</t>
         </is>
       </c>
     </row>
@@ -3698,7 +3698,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
@@ -3716,7 +3716,7 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7c5344293aa5ed77</t>
+          <t>https://www.indeed.com/viewjob?jk=124344ebd08b7526</t>
         </is>
       </c>
     </row>
@@ -3733,7 +3733,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
@@ -3751,7 +3751,7 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fea3b3cc46faeb2a</t>
+          <t>https://www.indeed.com/viewjob?jk=f0ef6c1eb38b0db9</t>
         </is>
       </c>
     </row>
@@ -3768,7 +3768,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
@@ -3786,7 +3786,7 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c3672ad48951be20</t>
+          <t>https://www.indeed.com/viewjob?jk=b780dcc242beb567</t>
         </is>
       </c>
     </row>
@@ -3803,7 +3803,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
@@ -3821,7 +3821,7 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c45dff0f36a9a356</t>
+          <t>https://www.indeed.com/viewjob?jk=a03180188c81f9bf</t>
         </is>
       </c>
     </row>
@@ -3838,7 +3838,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
@@ -3856,7 +3856,7 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7e91b7a712b7a165</t>
+          <t>https://www.indeed.com/viewjob?jk=8a037168850b8fe0</t>
         </is>
       </c>
     </row>
@@ -3873,7 +3873,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
@@ -3891,7 +3891,7 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f3d69f9412407b80</t>
+          <t>https://www.indeed.com/viewjob?jk=45cd4b8d959d97ab</t>
         </is>
       </c>
     </row>
@@ -3908,7 +3908,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D100" t="n">
@@ -3926,7 +3926,7 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7d48fbbfaa3d0a97</t>
+          <t>https://www.indeed.com/viewjob?jk=52080037fabe4cb1</t>
         </is>
       </c>
     </row>
@@ -3943,7 +3943,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Stamford, CT, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D101" t="n">
@@ -3961,7 +3961,7 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c300f1e448116fd7</t>
+          <t>https://www.indeed.com/viewjob?jk=69224b4d176dd4a2</t>
         </is>
       </c>
     </row>
@@ -3978,7 +3978,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Sacramento, CA, US USA</t>
+          <t>Kansas City, MO, US USA</t>
         </is>
       </c>
       <c r="D102" t="n">
@@ -3996,7 +3996,7 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=316adbd72ad7e2e8</t>
+          <t>https://www.indeed.com/viewjob?jk=5ce9dba6d19c8b82</t>
         </is>
       </c>
     </row>
@@ -4013,7 +4013,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Costa Mesa, CA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D103" t="n">
@@ -4031,7 +4031,7 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f219232c6b6eef2b</t>
+          <t>https://www.indeed.com/viewjob?jk=7c5344293aa5ed77</t>
         </is>
       </c>
     </row>
@@ -4048,7 +4048,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D104" t="n">
@@ -4066,7 +4066,7 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0bb31aa937d723cd</t>
+          <t>https://www.indeed.com/viewjob?jk=fea3b3cc46faeb2a</t>
         </is>
       </c>
     </row>
@@ -4083,7 +4083,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D105" t="n">
@@ -4101,7 +4101,7 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=884c614c785d6835</t>
+          <t>https://www.indeed.com/viewjob?jk=c3672ad48951be20</t>
         </is>
       </c>
     </row>
@@ -4118,7 +4118,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D106" t="n">
@@ -4136,7 +4136,7 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ecedaabbce0a0b5b</t>
+          <t>https://www.indeed.com/viewjob?jk=c45dff0f36a9a356</t>
         </is>
       </c>
     </row>
@@ -4153,7 +4153,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D107" t="n">
@@ -4171,7 +4171,7 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eea12c90a4a047af</t>
+          <t>https://www.indeed.com/viewjob?jk=7e91b7a712b7a165</t>
         </is>
       </c>
     </row>
@@ -4188,7 +4188,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D108" t="n">
@@ -4206,7 +4206,7 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=28b6e9e7e6b5c6aa</t>
+          <t>https://www.indeed.com/viewjob?jk=f3d69f9412407b80</t>
         </is>
       </c>
     </row>
@@ -4223,7 +4223,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D109" t="n">
@@ -4241,7 +4241,7 @@
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2c0e09d9843111bd</t>
+          <t>https://www.indeed.com/viewjob?jk=7d48fbbfaa3d0a97</t>
         </is>
       </c>
     </row>
@@ -4258,7 +4258,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Stamford, CT, US USA</t>
         </is>
       </c>
       <c r="D110" t="n">
@@ -4276,24 +4276,24 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3b10af7d10426fa4</t>
+          <t>https://www.indeed.com/viewjob?jk=c300f1e448116fd7</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Solution Architect-Full Stack</t>
+          <t>Associate Solution Architect with Modernization Experience</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Kirby Building Systems</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Portland, TN, US USA</t>
+          <t>Sacramento, CA, US USA</t>
         </is>
       </c>
       <c r="D111" t="n">
@@ -4301,7 +4301,7 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, SQL Server, PostgreSQL, CI/CD, Azure DevOps, Terraform, Docker, Kubernetes</t>
+          <t>AWS, Azure, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
@@ -4311,24 +4311,24 @@
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=66ada823af164848</t>
+          <t>https://www.indeed.com/viewjob?jk=316adbd72ad7e2e8</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Data Scientist Associate</t>
+          <t>Associate Solution Architect with Modernization Experience</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Wilmington, DE, US USA</t>
+          <t>Costa Mesa, CA, US USA</t>
         </is>
       </c>
       <c r="D112" t="n">
@@ -4336,7 +4336,7 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Scala, Snowflake, ETL, ELT, Tableau, Git, Python, SQL</t>
+          <t>AWS, Azure, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
@@ -4346,24 +4346,24 @@
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b87fe7f54c012f15</t>
+          <t>https://www.indeed.com/viewjob?jk=f219232c6b6eef2b</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>Sr Technical Analyst/Prog Ent App</t>
+          <t>Associate Solution Architect with Modernization Experience</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Avangrid</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Orange, CT, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D113" t="n">
@@ -4371,7 +4371,7 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, ETL, Azure DevOps, Git</t>
+          <t>AWS, Azure, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
@@ -4381,24 +4381,24 @@
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4ea1b275b8152311</t>
+          <t>https://www.indeed.com/viewjob?jk=0bb31aa937d723cd</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Full Stack Ad Tech Developer</t>
+          <t>Associate Solution Architect with Modernization Experience</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>The Hearst Corporation</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D114" t="n">
@@ -4406,7 +4406,7 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Google Cloud Platform, BigQuery, Scala, ETL, Tableau, CI/CD, Git, Python</t>
+          <t>AWS, Azure, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
@@ -4416,24 +4416,24 @@
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e8cf1f61c24a8358</t>
+          <t>https://www.indeed.com/viewjob?jk=884c614c785d6835</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>C# Full Stack Developer</t>
+          <t>Associate Solution Architect with Modernization Experience</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Globant</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D115" t="n">
@@ -4441,7 +4441,7 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Scala, SQL Server, PostgreSQL, MySQL, CI/CD, Docker</t>
+          <t>AWS, Azure, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
@@ -4451,24 +4451,24 @@
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d96c65fe6b68f304</t>
+          <t>https://www.indeed.com/viewjob?jk=ecedaabbce0a0b5b</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Associate Solution Architect with Modernization Experience</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Activated Insights</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D116" t="n">
@@ -4476,7 +4476,7 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>AWS, EMR, S3, RDS, Scala, Snowflake, PostgreSQL, MySQL, ETL, CI/CD</t>
+          <t>AWS, Azure, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
@@ -4486,24 +4486,24 @@
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4c98c8e05297ceda</t>
+          <t>https://www.indeed.com/viewjob?jk=eea12c90a4a047af</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Associate Solution Architect with Modernization Experience</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Activated Insights</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Idaho Falls, ID, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D117" t="n">
@@ -4511,7 +4511,7 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>AWS, EMR, S3, RDS, Scala, Snowflake, PostgreSQL, MySQL, ETL, CI/CD</t>
+          <t>AWS, Azure, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
@@ -4521,24 +4521,24 @@
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7382a9e2385f01a9</t>
+          <t>https://www.indeed.com/viewjob?jk=28b6e9e7e6b5c6aa</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>Forward Deployed AI Engineer 2026 - US, COL, UK</t>
+          <t>Associate Solution Architect with Modernization Experience</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Aimpoint Digital</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D118" t="n">
@@ -4546,42 +4546,42 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, Scala, Snowflake, ETL, ELT, MLOps, CI/CD</t>
+          <t>AWS, Azure, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=64c74cca4e3efa95</t>
+          <t>https://www.indeed.com/viewjob?jk=2c0e09d9843111bd</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer 4 (Python, AWS, SQL, GenAI) (Enterprise Platforms Technology)</t>
+          <t>Associate Solution Architect with Modernization Experience</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D119" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, CI/CD, Kubernetes, Python, SQL</t>
+          <t>AWS, Azure, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
@@ -4591,32 +4591,32 @@
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4922f7a57cfbdccb</t>
+          <t>https://www.indeed.com/viewjob?jk=3b10af7d10426fa4</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer 4 (Python, AWS, SQL, GenAI) (Enterprise Platforms Technology)</t>
+          <t>Solution Architect-Full Stack</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>Kirby Building Systems</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Portland, TN, US USA</t>
         </is>
       </c>
       <c r="D120" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, CI/CD, Kubernetes, Python, SQL</t>
+          <t>RDS, Azure, Scala, SQL Server, PostgreSQL, CI/CD, Azure DevOps, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
@@ -4626,102 +4626,102 @@
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=09348324e49b31d7</t>
+          <t>https://www.indeed.com/viewjob?jk=66ada823af164848</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>Software Engineer Full Stack / Backend I (Intern) â€“ United States</t>
+          <t>C# Full Stack Developer</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Cisco</t>
+          <t>Globant</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D121" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, S3, RDS, Azure, Scala, SQL Server, PostgreSQL, MySQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=12750212f2a3c980</t>
+          <t>https://www.indeed.com/viewjob?jk=d96c65fe6b68f304</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>Junior/Mid Software Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Activated Insights</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D122" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, GCP, Hadoop, Spark, Scala, Kafka, NoSQL, Kubernetes</t>
+          <t>AWS, EMR, S3, RDS, Scala, Snowflake, PostgreSQL, MySQL, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d87ecb6d60b0f54d</t>
+          <t>https://www.indeed.com/viewjob?jk=4c98c8e05297ceda</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>Data Platform Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Hubble Network</t>
+          <t>Activated Insights</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Idaho Falls, ID, US USA</t>
         </is>
       </c>
       <c r="D123" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Kinesis, Redshift, RDS, Scala, Kafka, Dimensional Modeling, Star Schema, Fact Tables, ETL, dbt</t>
+          <t>AWS, EMR, S3, RDS, Scala, Snowflake, PostgreSQL, MySQL, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
@@ -4731,102 +4731,102 @@
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a000c1d1d33d8b12</t>
+          <t>https://www.indeed.com/viewjob?jk=7382a9e2385f01a9</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>Data &amp; AI Engineer</t>
+          <t>Forward Deployed AI Engineer 2026 - US, COL, UK</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>The Carlyle Group</t>
+          <t>Aimpoint Digital</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D124" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Spark, Scala, Snowflake, ELT, dbt, MLflow, CI/CD</t>
+          <t>AWS, Azure, Databricks, GCP, Scala, Snowflake, ETL, ELT, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=83876c66e135b993</t>
+          <t>https://www.indeed.com/viewjob?jk=64c74cca4e3efa95</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>Data &amp; AI Engineer</t>
+          <t>Sr Technical Analyst/Prog Ent App</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>The Carlyle Group</t>
+          <t>Avangrid</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Orange, CT, US USA</t>
         </is>
       </c>
       <c r="D125" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Spark, Scala, Snowflake, ELT, dbt, MLflow, CI/CD</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, ETL, Azure DevOps, Git</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f4924b3389452957</t>
+          <t>https://www.indeed.com/viewjob?jk=4ea1b275b8152311</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>Sr. iOS Developer--Hybrid</t>
+          <t>Full Stack Ad Tech Developer</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>The Hearst Corporation</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Bridgewater, NJ, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D126" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>S3, RDS, Scala, PostgreSQL, MySQL, Cassandra, REST API integration, Jenkins, Jenkins, Git</t>
+          <t>AWS, Redshift, Google Cloud Platform, BigQuery, Scala, ETL, Tableau, CI/CD, Git, Python</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
@@ -4836,32 +4836,32 @@
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a2f579d7993e4d2c</t>
+          <t>https://www.indeed.com/viewjob?jk=e8cf1f61c24a8358</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>Sr Product Security Engineer, AI &amp; DevSecOps</t>
+          <t>Full-stack Engineer 5 (Go, TypeScript and Angular)</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>McKesson</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D127" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
@@ -4871,32 +4871,32 @@
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4b8ba8f92a1292eb</t>
+          <t>https://www.indeed.com/viewjob?jk=81ff3ef325447a98</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>Sr Software Engineer</t>
+          <t>Full-stack Engineer 4</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>Resideo</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D128" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Event Hubs, Scala, NoSQL, Data Modeling, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
@@ -4906,32 +4906,32 @@
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6f3ccdfade853d8f</t>
+          <t>https://www.indeed.com/viewjob?jk=70843ae9e366dd5b</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Full Stack (FES)</t>
+          <t>Full - Stack Engineer 5 (Remote - Eligible)</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>Fanatics</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D129" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>AWS, SQS, SNS, IAM, RDS, Azure, GCP, Kafka, NoSQL, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
@@ -4941,32 +4941,32 @@
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e95812a1a87ee87c</t>
+          <t>https://www.indeed.com/viewjob?jk=877ad6c20024fb1a</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Full Stack (FES)</t>
+          <t>Full-stack Engineer 4</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>Fanatics</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D130" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>AWS, SQS, SNS, IAM, RDS, Azure, GCP, Kafka, NoSQL, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
@@ -4976,32 +4976,32 @@
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f0dd1357e631ea44</t>
+          <t>https://www.indeed.com/viewjob?jk=6979868bb95d63f0</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Full Stack Engineer 5</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>Function Health</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D131" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>RDS, Databricks, BigQuery, Spark, Kafka, Snowflake, ELT, dbt, MLOps, Terraform</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
@@ -5011,67 +5011,67 @@
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8d332f2047edfa45</t>
+          <t>https://www.indeed.com/viewjob?jk=b743b91aec079a75</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>Engineer, Performance Management</t>
+          <t>Full Stack Engineer 4</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>The Carlyle Group</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D132" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, SQL Server, ETL, Power BI, CI/CD, Git</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9e0346f80c455f7d</t>
+          <t>https://www.indeed.com/viewjob?jk=3fb66ff5f4ef065f</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer, JMG</t>
+          <t>Full-stack Engineer 4 (Python, Java)</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>Keller Williams Realty</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D133" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Azure, Scala, SQL Server, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
@@ -5081,32 +5081,32 @@
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2bd7eff3fbb2aa75</t>
+          <t>https://www.indeed.com/viewjob?jk=c9046de91e154d69</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>Technical Engineer (Production Liability Engineer)</t>
+          <t>Full-stack Engineer 5 ( Python, AWS)</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>M&amp;T Bank</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Buffalo, NY, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D134" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, REST API integration, Splunk, CI/CD, AKS, Datadog, Azure Monitor, Python</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
@@ -5116,42 +5116,1442 @@
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bef57255c79d57a0</t>
+          <t>https://www.indeed.com/viewjob?jk=5e4de127a7227d81</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer, JMG</t>
+          <t>Full-stack Engineer 5 (Golang, Java, AWS)</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>Keller Williams Realty</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
+          <t>Chicago, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D135" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E135" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
+        </is>
+      </c>
+      <c r="F135" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="G135" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f3a9ee8f682a9c78</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>Full-stack Engineer 4 - Intelligent Foundations and Experiences (IFX)</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>Capital One</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>McLean, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D136" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E136" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
+        </is>
+      </c>
+      <c r="F136" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="G136" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=6faf5ca1640fcd31</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>Full-stack Engineer 4 - Intelligent Foundations and Experiences (IFX)</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>Capital One</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D137" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E137" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
+        </is>
+      </c>
+      <c r="F137" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="G137" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=42133a298638cb9b</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>Full-stack Engineer 5</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>Capital One</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>McLean, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D138" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E138" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
+        </is>
+      </c>
+      <c r="F138" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="G138" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a708182f9a1da64d</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>Full-stack Engineer 4 - Intelligent Foundations and Experiences (IFX)</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>Capital One</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D139" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E139" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
+        </is>
+      </c>
+      <c r="F139" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="G139" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=76c8a5b4fcc58505</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>Full-stack Engineer 5 - Shopping (Remote-Eligible)</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>Capital One</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>McLean, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D140" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E140" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
+        </is>
+      </c>
+      <c r="F140" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="G140" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=419688dc0cbfaf98</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>Full-stack Engineer 5 (Java, Scala, AWS)</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>Capital One</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>McLean, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D141" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E141" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
+        </is>
+      </c>
+      <c r="F141" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="G141" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c997daa05db4e0c7</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>Full Stack Engineer 4 (Go, AWS)</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>Capital One</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>McLean, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D142" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E142" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
+        </is>
+      </c>
+      <c r="F142" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="G142" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=6a9874c783fb4a03</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>Full-stack Engineer 4</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>Capital One</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>McLean, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D143" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E143" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
+        </is>
+      </c>
+      <c r="F143" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="G143" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=1f96da918db85a2a</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>Full-stack Engineer 4 (Java, Scala, AWS)</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>Capital One</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D144" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E144" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
+        </is>
+      </c>
+      <c r="F144" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="G144" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b9e0187cbe4c2e40</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>Full-stack Engineer 4</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>Capital One</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>McLean, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D145" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E145" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
+        </is>
+      </c>
+      <c r="F145" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="G145" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=900df92ddc778d5f</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>Full-stack Engineer 4 (JavaScript, React)</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>Capital One</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>Chicago, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D146" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E146" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
+        </is>
+      </c>
+      <c r="F146" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="G146" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e7c346fa6453ffb9</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>Full-stack Engineer 5 (Go/Java, Angular, AWS)</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>Capital One</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>Chicago, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D147" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E147" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
+        </is>
+      </c>
+      <c r="F147" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="G147" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c039bc465260bc95</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>Full-stack Engineer 4</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>Capital One</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>Richmond, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D148" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E148" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
+        </is>
+      </c>
+      <c r="F148" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="G148" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=54e236865193f8a0</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>Full-stack Engineer 4</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>Capital One</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>McLean, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D149" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E149" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
+        </is>
+      </c>
+      <c r="F149" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="G149" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b667ebd325202576</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>Full-stack Engineer 5 (Golang, AWS)</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>Capital One</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>McLean, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D150" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E150" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
+        </is>
+      </c>
+      <c r="F150" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="G150" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=672e371e8fd60859</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>Full-stack Engineer 4 (React, TypeScript, AWS)</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>Capital One</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>McLean, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D151" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E151" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
+        </is>
+      </c>
+      <c r="F151" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="G151" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=346a7f081a67b46c</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>Full-stack Engineer 4</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>Capital One</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>McLean, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D152" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E152" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
+        </is>
+      </c>
+      <c r="F152" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="G152" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=7b21934bf2433e6a</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>Full-stack Engineer 4 (Scala, React, AWS)</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>Capital One</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D153" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E153" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
+        </is>
+      </c>
+      <c r="F153" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="G153" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=2af3b2e528eb8c47</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>Full-stack Engineer 4 (Scala, React, AWS)</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>Capital One</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D154" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E154" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
+        </is>
+      </c>
+      <c r="F154" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="G154" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=51fd20841ca9c754</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>Full-stack Engineer 4</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>Capital One</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>McLean, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D155" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E155" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
+        </is>
+      </c>
+      <c r="F155" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="G155" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=619531dae358928f</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>Full-stack Engineer 4 (Python, AWS)</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>Capital One</t>
+        </is>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>McLean, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D156" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E156" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
+        </is>
+      </c>
+      <c r="F156" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="G156" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=8e4eaf7eaa027bbb</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>Full-stack Engineer 4 (GoLang)</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>Capital One</t>
+        </is>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>Chicago, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D157" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E157" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
+        </is>
+      </c>
+      <c r="F157" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="G157" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b7c24e0e87f3fc42</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>Full-Stack Engineer 4 (Automation Quality Engineer)</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>Capital One</t>
+        </is>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>Riverwoods, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D158" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E158" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
+        </is>
+      </c>
+      <c r="F158" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="G158" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=2acd23b24043f205</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>Full-stack Engineer 4 - Shopping (Remote-Eligible)</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>Capital One</t>
+        </is>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>McLean, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D159" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E159" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
+        </is>
+      </c>
+      <c r="F159" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="G159" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f87b328e958cbb63</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>Data Engineer</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>KeHE Distributors</t>
+        </is>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>Naperville, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D160" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E160" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, Data Modeling, Power BI, Tableau, MLOps</t>
+        </is>
+      </c>
+      <c r="F160" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="G160" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=9033c8036c6af9b3</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>Data Platform Engineer</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>Hubble Network</t>
+        </is>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>San Francisco, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D161" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E161" t="inlineStr">
+        <is>
+          <t>Kinesis, Redshift, RDS, Scala, Kafka, Dimensional Modeling, Star Schema, Fact Tables, ETL, dbt</t>
+        </is>
+      </c>
+      <c r="F161" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="G161" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a000c1d1d33d8b12</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>Data &amp; AI Engineer</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>The Carlyle Group</t>
+        </is>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>Washington, DC, US USA</t>
+        </is>
+      </c>
+      <c r="D162" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E162" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Databricks, Spark, Scala, Snowflake, ELT, dbt, MLflow, CI/CD</t>
+        </is>
+      </c>
+      <c r="F162" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="G162" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=83876c66e135b993</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>Data &amp; AI Engineer</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>The Carlyle Group</t>
+        </is>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D163" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E163" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Databricks, Spark, Scala, Snowflake, ELT, dbt, MLflow, CI/CD</t>
+        </is>
+      </c>
+      <c r="F163" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="G163" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f4924b3389452957</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>Integration Engineer 4</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>Capital One</t>
+        </is>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>McLean, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D164" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E164" t="inlineStr">
+        <is>
+          <t>AWS, Lambda, Step Functions, RDS, Azure, GCP, Scala, Splunk, Jenkins, Jenkins</t>
+        </is>
+      </c>
+      <c r="F164" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="G164" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=52d873bb7fc420f0</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>Machine Learning Engineer 4 (Python, AWS, SQL, GenAI) (Enterprise Platforms Technology)</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>Capital One</t>
+        </is>
+      </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D165" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E165" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, CI/CD, Kubernetes, Python, SQL</t>
+        </is>
+      </c>
+      <c r="F165" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="G165" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=4922f7a57cfbdccb</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>Machine Learning Engineer 4 (Python, AWS, SQL, GenAI) (Enterprise Platforms Technology)</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>Capital One</t>
+        </is>
+      </c>
+      <c r="C166" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D166" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E166" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, CI/CD, Kubernetes, Python, SQL</t>
+        </is>
+      </c>
+      <c r="F166" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="G166" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=09348324e49b31d7</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>Junior/Mid Software Engineer</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>Tampa, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D167" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E167" t="inlineStr">
+        <is>
+          <t>AWS, Azure, Google Cloud Platform, GCP, Hadoop, Spark, Scala, Kafka, NoSQL, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F167" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="G167" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d87ecb6d60b0f54d</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>Mastercard</t>
+        </is>
+      </c>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>O'Fallon, MO, US USA</t>
+        </is>
+      </c>
+      <c r="D168" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E168" t="inlineStr">
+        <is>
+          <t>AWS, API Gateway, RDS, Scala, Oracle, PostgreSQL, CI/CD, Jenkins, GitHub Actions, Jenkins</t>
+        </is>
+      </c>
+      <c r="F168" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="G168" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=0245dcafa3f48258</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>Sr Product Security Engineer, AI &amp; DevSecOps</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>McKesson</t>
+        </is>
+      </c>
+      <c r="C169" t="inlineStr">
+        <is>
+          <t>Columbus, OH, US USA</t>
+        </is>
+      </c>
+      <c r="D169" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E169" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Google Cloud Platform, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F169" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="G169" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=4b8ba8f92a1292eb</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>Sr. iOS Developer--Hybrid</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>Cognizant</t>
+        </is>
+      </c>
+      <c r="C170" t="inlineStr">
+        <is>
+          <t>Bridgewater, NJ, US USA</t>
+        </is>
+      </c>
+      <c r="D170" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E170" t="inlineStr">
+        <is>
+          <t>S3, RDS, Scala, PostgreSQL, MySQL, Cassandra, REST API integration, Jenkins, Jenkins, Git</t>
+        </is>
+      </c>
+      <c r="F170" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="G170" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a2f579d7993e4d2c</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>Sr Software Engineer</t>
+        </is>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>Resideo</t>
+        </is>
+      </c>
+      <c r="C171" t="inlineStr">
+        <is>
           <t>Austin, TX, US USA</t>
         </is>
       </c>
-      <c r="D135" t="n">
+      <c r="D171" t="n">
         <v>10.4</v>
       </c>
-      <c r="E135" t="inlineStr">
-        <is>
-          <t>AWS, S3, IAM, RDS, Azure, Scala, SQL Server, CI/CD, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F135" t="inlineStr">
-        <is>
-          <t>2026-09-22</t>
-        </is>
-      </c>
-      <c r="G135" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=45f15d53aceb441c</t>
+      <c r="E171" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Event Hubs, Scala, NoSQL, Data Modeling, CI/CD, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F171" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="G171" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=6f3ccdfade853d8f</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer, Full Stack (FES)</t>
+        </is>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>Fanatics</t>
+        </is>
+      </c>
+      <c r="C172" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D172" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E172" t="inlineStr">
+        <is>
+          <t>AWS, SQS, SNS, IAM, RDS, Azure, GCP, Kafka, NoSQL, CI/CD</t>
+        </is>
+      </c>
+      <c r="F172" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="G172" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e95812a1a87ee87c</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer, Full Stack (FES)</t>
+        </is>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>Fanatics</t>
+        </is>
+      </c>
+      <c r="C173" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D173" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E173" t="inlineStr">
+        <is>
+          <t>AWS, SQS, SNS, IAM, RDS, Azure, GCP, Kafka, NoSQL, CI/CD</t>
+        </is>
+      </c>
+      <c r="F173" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="G173" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f0dd1357e631ea44</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>Data Engineer</t>
+        </is>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>Function Health</t>
+        </is>
+      </c>
+      <c r="C174" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D174" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E174" t="inlineStr">
+        <is>
+          <t>RDS, Databricks, BigQuery, Spark, Kafka, Snowflake, ELT, dbt, MLOps, Terraform</t>
+        </is>
+      </c>
+      <c r="F174" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="G174" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=8d332f2047edfa45</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>Engineer, Performance Management</t>
+        </is>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>The Carlyle Group</t>
+        </is>
+      </c>
+      <c r="C175" t="inlineStr">
+        <is>
+          <t>Washington, DC, US USA</t>
+        </is>
+      </c>
+      <c r="D175" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E175" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Scala, Snowflake, SQL Server, ETL, Power BI, CI/CD, Git</t>
+        </is>
+      </c>
+      <c r="F175" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="G175" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=9e0346f80c455f7d</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-09-23.xlsx
+++ b/results/job_matches_2026-09-23.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G175"/>
+  <dimension ref="A1:G172"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,60 +468,60 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Databricks Data Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Gentiva</t>
+          <t>Coca Cola Southwest Beverages</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>22.2</v>
+        <v>20.1</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Databricks, Blob Storage, Unity Catalog, Medallion Architecture, Delta Live Tables, Cloud Storage, Spark, PySpark</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Snowflake, SQL Server</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=10920ada24a70c04</t>
+          <t>https://www.indeed.com/viewjob?jk=ca8f627225261b22</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>I.T. - DevOps Engineer</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Coca Cola Southwest Beverages</t>
+          <t>StorageMart</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Columbia, MO, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>20.1</v>
+        <v>18.8</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Snowflake, SQL Server</t>
+          <t>AWS, Lambda, S3, SQS, ECS, IAM, RDS, Azure, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,67 +531,67 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ca8f627225261b22</t>
+          <t>https://www.indeed.com/viewjob?jk=c2e972535a11a31f</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>I.T. - DevOps Engineer</t>
+          <t>Data Engineer 4 (Python, AWS, Kafka, Spark, SQL, Snowflake, Databricks, GenAI)</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>StorageMart</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Columbia, MO, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>18.8</v>
+        <v>16.7</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, ECS, IAM, RDS, Azure, MySQL, MongoDB</t>
+          <t>AWS, Glue, EMR, Redshift, RDS, Azure, Databricks, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c2e972535a11a31f</t>
+          <t>https://www.indeed.com/viewjob?jk=47e2de3bf66a6750</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Applied AI Site Reliability Engineer II - PxE A&amp;A</t>
+          <t>Data Engineer Sr</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Oshkosh Corporation</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Hermitage, TN, US USA</t>
+          <t>Oshkosh, WI, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>17.4</v>
+        <v>16.7</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, Splunk, MLOps, MLflow</t>
+          <t>AWS, Redshift, RDS, Azure, Data Factory, Databricks, GCP, Hadoop, HDFS, Hive</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,32 +601,32 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=293a95bba31efbab</t>
+          <t>https://www.indeed.com/viewjob?jk=8b5c363397eafe5f</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Applied AI Site Reliability Engineer II - PxE A&amp;A</t>
+          <t>Associate Data Engineer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Blue Cross and Blue Shield of Minnesota</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Eagan, MN, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>17.4</v>
+        <v>16.7</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, Splunk, MLOps, MLflow</t>
+          <t>AWS, Glue, EMR, Lambda, S3, SQS, SNS, RDS, Databricks, Spark</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,32 +636,32 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=90798cf9ad992e58</t>
+          <t>https://www.indeed.com/viewjob?jk=31bf226ac97de61e</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Applied AI Site Reliability Engineer II - PxE A&amp;A</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Sally Beauty</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Denton, TX, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>17.4</v>
+        <v>16.7</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, Splunk, MLOps, MLflow</t>
+          <t>AWS, S3, RDS, Azure, Databricks, Data Lake Storage, Unity Catalog, Medallion Architecture, Delta Live Tables, Google Cloud Platform</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,24 +671,24 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=76a0c64002bbb5c1</t>
+          <t>https://www.indeed.com/viewjob?jk=0864fe655aae7888</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Associate Data Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Blue Cross and Blue Shield of Minnesota</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Eagan, MN, US USA</t>
+          <t>RI, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -696,34 +696,34 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, S3, SQS, SNS, RDS, Databricks, Spark</t>
+          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=31bf226ac97de61e</t>
+          <t>https://www.indeed.com/viewjob?jk=8dd495afc5140159</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Enterprise Data Architect</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Sally Beauty</t>
+          <t>Alignment Health</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Denton, TX, US USA</t>
+          <t>Orange, CA, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -731,7 +731,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Databricks, Data Lake Storage, Unity Catalog, Medallion Architecture, Delta Live Tables, Google Cloud Platform</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Scala, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,24 +741,24 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0864fe655aae7888</t>
+          <t>https://www.indeed.com/viewjob?jk=1611fa9de2f7504b</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Data Engineer Sr</t>
+          <t>Senior AI Ops / DevOps Engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Oshkosh Corporation</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Oshkosh, WI, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -766,7 +766,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Data Factory, Databricks, GCP, Hadoop, HDFS, Hive</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Splunk, MLOps, MLflow, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,67 +776,67 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8b5c363397eafe5f</t>
+          <t>https://www.indeed.com/viewjob?jk=040c156b15abd039</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Data Engineer 5 - Enterprise Risk Management</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>RI, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>16.7</v>
+        <v>16</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI</t>
+          <t>AWS, Glue, EMR, Redshift, RDS, Azure, Databricks, Spark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8dd495afc5140159</t>
+          <t>https://www.indeed.com/viewjob?jk=a45f08af4f7be5f6</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Enterprise Data Architect</t>
+          <t>Data Engineer 4 - Nexus Products</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Alignment Health</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Orange, CA, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>16.7</v>
+        <v>16</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Scala, Snowflake, Data Modeling</t>
+          <t>AWS, Glue, EMR, Redshift, RDS, Azure, Databricks, Spark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,32 +846,32 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1611fa9de2f7504b</t>
+          <t>https://www.indeed.com/viewjob?jk=36fc31dc37d05722</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Senior AI Ops / DevOps Engineer</t>
+          <t>Data Engineer 4</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>16.7</v>
+        <v>16</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Splunk, MLOps, MLflow, CI/CD, Jenkins</t>
+          <t>AWS, Glue, EMR, Redshift, RDS, Azure, Databricks, Spark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,14 +881,14 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=040c156b15abd039</t>
+          <t>https://www.indeed.com/viewjob?jk=45e14228c1ed2aed</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Data Engineer 5 - Enterprise Risk Management</t>
+          <t>Data Engineer 4 - Payment Networks</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -916,14 +916,14 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a45f08af4f7be5f6</t>
+          <t>https://www.indeed.com/viewjob?jk=f8d0c3f139798fd9</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Data Engineer 4 - Nexus Products</t>
+          <t>Data Engineer 4 - HR Tech</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -951,14 +951,14 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=36fc31dc37d05722</t>
+          <t>https://www.indeed.com/viewjob?jk=010f3637940ea854</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Data Engineer 4</t>
+          <t>Data Engineer 5 (SEO/GEO, AdTech )</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -986,14 +986,14 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=45e14228c1ed2aed</t>
+          <t>https://www.indeed.com/viewjob?jk=e9a8f6941c1a4549</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Data Engineer 4 - Payment Networks</t>
+          <t>Data Engineer 4</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1021,14 +1021,14 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f8d0c3f139798fd9</t>
+          <t>https://www.indeed.com/viewjob?jk=0db4720c664a5a3f</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Data Engineer 4 - HR Tech</t>
+          <t>Data Engineer 4</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1056,14 +1056,14 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=010f3637940ea854</t>
+          <t>https://www.indeed.com/viewjob?jk=d80c6adab1193eaf</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Data Engineer 5 (SEO/GEO, AdTech )</t>
+          <t>Data Engineer 5 (Enterprise Platforms Technology)</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1073,7 +1073,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1091,14 +1091,14 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e9a8f6941c1a4549</t>
+          <t>https://www.indeed.com/viewjob?jk=220dab7fe793042b</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Data Engineer 4</t>
+          <t>Data Engineer 5</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1126,7 +1126,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0db4720c664a5a3f</t>
+          <t>https://www.indeed.com/viewjob?jk=3a1e95e5123a2b15</t>
         </is>
       </c>
     </row>
@@ -1143,7 +1143,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1161,24 +1161,24 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d80c6adab1193eaf</t>
+          <t>https://www.indeed.com/viewjob?jk=6438ee405fccd9e0</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Data Engineer 5 (Enterprise Platforms Technology)</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>Tiger Analytics</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1186,7 +1186,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Redshift, RDS, Azure, Databricks, Spark, Scala, Snowflake</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Cloud Storage, Spark, PySpark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,24 +1196,24 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=220dab7fe793042b</t>
+          <t>https://www.indeed.com/viewjob?jk=4b2cb75552da28cb</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Data Engineer 5</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>Tiger Analytics</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1221,7 +1221,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Redshift, RDS, Azure, Databricks, Spark, Scala, Snowflake</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Cloud Storage, Spark, PySpark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,24 +1231,24 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3a1e95e5123a2b15</t>
+          <t>https://www.indeed.com/viewjob?jk=4b046b29ca6b7df4</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Software Engineer - ai automation medical billing platform</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Tiger Analytics</t>
+          <t>Relentless Talent</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,34 +1256,34 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Cloud Storage, Spark, PySpark, Scala, Snowflake</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4b2cb75552da28cb</t>
+          <t>https://www.indeed.com/viewjob?jk=69d642c554413fbe</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Software Engineer - ai automation medical billing platform</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Tiger Analytics</t>
+          <t>Relentless Talent</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Buffalo, NY, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,77 +1291,77 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Cloud Storage, Spark, PySpark, Scala, Snowflake</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4b046b29ca6b7df4</t>
+          <t>https://www.indeed.com/viewjob?jk=818c7178aa0280e0</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Data Engineer 4</t>
+          <t>Senior Data Platfrom Engineer</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Redshift, RDS, Azure, Databricks, Spark, Scala, Snowflake</t>
+          <t>RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Delta Live Tables, Spark, PySpark, Scala, Data Modeling</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6438ee405fccd9e0</t>
+          <t>https://www.indeed.com/viewjob?jk=bc974eac3e508ce6</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - ai automation medical billing platform</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Relentless Talent</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL</t>
+          <t>RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Delta Live Tables, Spark, PySpark, Scala, Data Modeling</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,59 +1371,59 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=69d642c554413fbe</t>
+          <t>https://www.indeed.com/viewjob?jk=e85b5d56e27bdfb8</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - ai automation medical billing platform</t>
+          <t>Cloud Engineer</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Relentless Talent</t>
+          <t>Willdan</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Buffalo, NY, US USA</t>
+          <t>Anaheim, CA, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, Azure, Scala, Amazon QuickSight, CI/CD</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=818c7178aa0280e0</t>
+          <t>https://www.indeed.com/viewjob?jk=8d1298ac76effc74</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Senior Data Platfrom Engineer</t>
+          <t>C,C++, Python, Golang Developer</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,7 +1431,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Delta Live Tables, Spark, PySpark, Scala, Data Modeling</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, SQL Server, PostgreSQL, CI/CD</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,94 +1441,94 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bc974eac3e508ce6</t>
+          <t>https://www.indeed.com/viewjob?jk=441856af730024e8</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Back-end Engineer - Data Platforms</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Morgan Stanley</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Delta Live Tables, Spark, PySpark, Scala, Data Modeling</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Spark, PySpark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e85b5d56e27bdfb8</t>
+          <t>https://www.indeed.com/viewjob?jk=ebb387f8fd246816</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Cloud Engineer</t>
+          <t>Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Willdan</t>
+          <t>Seek Now</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Anaheim, CA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, Azure, Scala, Amazon QuickSight, CI/CD</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, Scala, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8d1298ac76effc74</t>
+          <t>https://www.indeed.com/viewjob?jk=86d6727803939178</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Back-end Engineer - Data Platforms</t>
+          <t>Database Engineer - onsite</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Morgan Stanley</t>
+          <t>Eccalon</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Detroit, MI, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Spark, PySpark, Scala, Kafka</t>
+          <t>Redshift, RDS, Azure, BigQuery, Scala, Snowflake, Oracle, SQL Server, Data Modeling, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,129 +1546,129 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ebb387f8fd246816</t>
+          <t>https://www.indeed.com/viewjob?jk=e9489350e98d48c6</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Agentic AI Databricks</t>
+          <t>Analytics and Intelligence Engineer</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>LTM Limited</t>
+          <t>Mars</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Raritan, NJ, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Unity Catalog, Delta Live Tables, Spark, PySpark, Scala</t>
+          <t>RDS, Azure, Data Factory, Databricks, Unity Catalog, Scala, Snowflake, Star Schema, dbt, Power BI</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=611badfabe276aeb</t>
+          <t>https://www.indeed.com/viewjob?jk=94ca6d53f6fb57de</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer</t>
+          <t>SOW198 Platform Engineer</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Seek Now</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, Scala, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, RDS, Azure, Databricks, Spark, PySpark, Scala, Kafka, Cassandra, NoSQL</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=86d6727803939178</t>
+          <t>https://www.indeed.com/viewjob?jk=6dbc4fb78c7362b3</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Database Engineer - onsite</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Eccalon</t>
+          <t>United Utility</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Detroit, MI, US USA</t>
+          <t>Spring, TX, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Azure, BigQuery, Scala, Snowflake, Oracle, SQL Server, Data Modeling, Dimensional Modeling</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, BigQuery, Cloud Storage, Scala, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e9489350e98d48c6</t>
+          <t>https://www.indeed.com/viewjob?jk=2c848474306799be</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>SOW198 Platform Engineer</t>
+          <t>Software Engineer III - Generative AI Technology</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Wayfair</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,77 +1676,77 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Spark, PySpark, Scala, Kafka, Cassandra, NoSQL</t>
+          <t>AWS, Azure, GCP, BigQuery, Scala, PostgreSQL, MongoDB, MLflow, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6dbc4fb78c7362b3</t>
+          <t>https://www.indeed.com/viewjob?jk=dea1b605e8c5ec18</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Engineer – Application</t>
+          <t>Product Software Engineer II</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Federated Hermes</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Warrendale, PA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Delta Live Tables, Spark, PySpark, Scala</t>
+          <t>AWS, EMR, Lambda, S3, ECS, Databricks, Spark, Scala, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3249c7729c4e3bf1</t>
+          <t>https://www.indeed.com/viewjob?jk=5fd9ded3cfb927d6</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Software Engineer III - AI Native Development</t>
+          <t>Integration Architect</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Penske Truck Leasing</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Reading, PA, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, S3, SQS, SNS, API Gateway, ECS, RDS, Scala</t>
+          <t>AWS, API Gateway, RDS, Azure, GCP, Scala, Kafka, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,32 +1756,32 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ea9ef8693c4fa599</t>
+          <t>https://www.indeed.com/viewjob?jk=bfceaaf0e0e2e9a5</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Azure Databricks &amp; Agentic AI Architect</t>
+          <t>Full Stack Senior Software Engineer (Remote in CA)</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>FCT</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Santa Ana, CA, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Databricks, Unity Catalog, Delta Live Tables, Spark, PySpark, Scala, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,24 +1791,24 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=02432aa1dd6c57d9</t>
+          <t>https://www.indeed.com/viewjob?jk=70278c6707b92e9e</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Sr. ML Engineer</t>
+          <t>Full Stack Senior Software Engineer (Remote in CA)</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Visa</t>
+          <t>FCT</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Spark, Scala, MLOps, MLflow, CI/CD, Terraform</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,24 +1826,24 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f84e409aaaf551e7</t>
+          <t>https://www.indeed.com/viewjob?jk=a25e08cbc61c8f9c</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Integration Architect</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Penske Truck Leasing</t>
+          <t>WorkOS</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Reading, PA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, GCP, Scala, Kafka, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, ECS, IAM, RDS, Scala, Snowflake, Data Modeling, ETL, dbt, CI/CD</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,24 +1861,24 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bfceaaf0e0e2e9a5</t>
+          <t>https://www.indeed.com/viewjob?jk=93c58ad8f77c200b</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Full Stack Senior Software Engineer (Remote in CA)</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>FCT</t>
+          <t>Imperial Brady</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Santa Ana, CA, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,7 +1886,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
+          <t>AWS, RDS, Azure, Databricks, Medallion Architecture, Spark, PySpark, Scala, Data Modeling, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,32 +1896,32 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=70278c6707b92e9e</t>
+          <t>https://www.indeed.com/viewjob?jk=49e6c0c32c4bdcc7</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Full Stack Senior Software Engineer (Remote in CA)</t>
+          <t>Senior Cloud / AWS Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>FCT</t>
+          <t>Reflex Media Inc</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
+          <t>AWS, Lambda, Redshift, S3, ECS, IAM, RDS, PostgreSQL, MySQL, CI/CD</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,89 +1931,89 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a25e08cbc61c8f9c</t>
+          <t>https://www.indeed.com/viewjob?jk=901aac12afba9b93</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Enterprise Architect - Data Platform</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>WorkOS</t>
+          <t>Johnson Controls</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Milwaukee, WI, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, ECS, IAM, RDS, Scala, Snowflake, Data Modeling, ETL, dbt, CI/CD</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Spark, Scala, Kafka, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=93c58ad8f77c200b</t>
+          <t>https://www.indeed.com/viewjob?jk=d42707fbe5923515</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Imperial Brady</t>
+          <t>Exostar</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Herndon, VA, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Medallion Architecture, Spark, PySpark, Scala, Data Modeling, Dimensional Modeling</t>
+          <t>AWS, S3, RDS, Azure, Scala, SQL Server, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=49e6c0c32c4bdcc7</t>
+          <t>https://www.indeed.com/viewjob?jk=ca5e90ebcac7315c</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Senior Cloud / AWS Infrastructure Engineer</t>
+          <t>Sr Implementation Consultant</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Reflex Media Inc</t>
+          <t>Cotiviti</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -2026,7 +2026,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, S3, ECS, IAM, RDS, PostgreSQL, MySQL, CI/CD</t>
+          <t>AWS, Glue, ECS, RDS, Azure, Oracle, SQL Server, Data Modeling, ETL, Talend</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,24 +2036,24 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=901aac12afba9b93</t>
+          <t>https://www.indeed.com/viewjob?jk=feec9157e828c7c5</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Analyst - ERP &amp; Master Data</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>US Tiger Securities</t>
+          <t>TransTech Group</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2061,7 +2061,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, Redshift, S3, RDS, Hive, Spark, PySpark, Kafka, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Medallion Architecture, Dataflow, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,24 +2071,24 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=573ee0a7b1fef58d</t>
+          <t>https://www.indeed.com/viewjob?jk=49c2343d736f4c5c</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Sr Implementation Consultant</t>
+          <t>Azure Solutions Architect - Presales</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Cotiviti</t>
+          <t>TTEC Digital</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2096,7 +2096,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, Glue, ECS, RDS, Azure, Oracle, SQL Server, Data Modeling, ETL, Talend</t>
+          <t>Azure, Data Factory, Synapse Analytics, Databricks, Scala, ETL, Power BI, Azure DevOps, Terraform, AKS</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,24 +2106,24 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=feec9157e828c7c5</t>
+          <t>https://www.indeed.com/viewjob?jk=9d1ac466d0b2792d</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Data Analyst - ERP &amp; Master Data</t>
+          <t>Software Development Engineer II</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>TransTech Group</t>
+          <t>GM Financial</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>Arlington, TX, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,7 +2131,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Medallion Architecture, Dataflow, Spark, PySpark, Scala</t>
+          <t>Azure, Scala, Oracle, SQL Server, NoSQL, Jenkins, Azure DevOps, Maven, Terraform, Docker</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,24 +2141,24 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=49c2343d736f4c5c</t>
+          <t>https://www.indeed.com/viewjob?jk=77c13363e54e5087</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Azure Solutions Architect - Presales</t>
+          <t>Full Stack Engineer 4 (Python, AWS, AI, Snowflake, Databricks)</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>TTEC Digital</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,34 +2166,34 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Synapse Analytics, Databricks, Scala, ETL, Power BI, Azure DevOps, Terraform, AKS</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Snowflake, NoSQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9d1ac466d0b2792d</t>
+          <t>https://www.indeed.com/viewjob?jk=2d2e1578e6815ef7</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Software Development Engineer II</t>
+          <t>Forward Deployed Engineer, Client Solutions Group</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>GM Financial</t>
+          <t>The Carlyle Group</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Arlington, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,29 +2201,29 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Azure, Scala, Oracle, SQL Server, NoSQL, Jenkins, Azure DevOps, Maven, Terraform, Docker</t>
+          <t>AWS, Lambda, Step Functions, S3, API Gateway, ECS, RDS, Databricks, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=77c13363e54e5087</t>
+          <t>https://www.indeed.com/viewjob?jk=3cba42b7feabaab8</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Forward Deployed Engineer, Client Solutions Group</t>
+          <t>Full-Stack Engineer 4 (Java, Spring, DynamoDB, S3, GraphQL, GenAI)</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>The Carlyle Group</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -2236,69 +2236,69 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, API Gateway, ECS, RDS, Databricks, Scala, Snowflake</t>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, DynamoDB, NoSQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3cba42b7feabaab8</t>
+          <t>https://www.indeed.com/viewjob?jk=30dd4b0534b4aca9</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Full-Stack Engineer 4 (Java, Spring, DynamoDB, S3, GraphQL, GenAL)</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Pika</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, Redshift, GCP, BigQuery, Scala, Kafka, Snowflake, Data Modeling, ETL</t>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, DynamoDB, NoSQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=126cb889e15ed9cd</t>
+          <t>https://www.indeed.com/viewjob?jk=3e502713d51d0a40</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Sr Data Engineer II</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Hollstadt Consulting</t>
+          <t>American Express</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>MN, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,7 +2306,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>S3, IAM, RDS, Azure, Google Cloud Platform, GCP, Cloud Storage, Scala, CI/CD, Azure DevOps</t>
+          <t>AWS, RDS, HBase, Spark, Scala, Kafka, Cassandra, NoSQL, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,24 +2316,24 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9488041a67901dc1</t>
+          <t>https://www.indeed.com/viewjob?jk=a9b4607cbdf4a3d4</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Sr Data Engineer II</t>
+          <t>Sr Software Engineer I</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>American Express</t>
+          <t>RWE</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,34 +2341,34 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, RDS, HBase, Spark, Scala, Kafka, Cassandra, NoSQL, MLOps, CI/CD</t>
+          <t>RDS, Azure, ETL, CI/CD, Azure DevOps, Terraform, Kubernetes, AKS, Airflow, Apache Airflow</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a9b4607cbdf4a3d4</t>
+          <t>https://www.indeed.com/viewjob?jk=f6ad43066e853c35</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Data Engineer-5</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>Pika</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,7 +2376,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, RDS, Scala, Snowflake, Data Modeling, ETL, ELT, dbt</t>
+          <t>AWS, Kinesis, Redshift, GCP, BigQuery, Scala, Kafka, Snowflake, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,7 +2386,7 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bb259aa46cf4c5ed</t>
+          <t>https://www.indeed.com/viewjob?jk=126cb889e15ed9cd</t>
         </is>
       </c>
     </row>
@@ -2398,12 +2398,12 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Community Choice Credit Union</t>
+          <t>Hollstadt Consulting</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Warren, MI, US USA</t>
+          <t>MN, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,17 +2411,17 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Scala, Snowflake, SQL Server, Data Modeling, ETL, ELT, Power BI</t>
+          <t>S3, IAM, RDS, Azure, Google Cloud Platform, GCP, Cloud Storage, Scala, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=21899fbf482a9cd2</t>
+          <t>https://www.indeed.com/viewjob?jk=9488041a67901dc1</t>
         </is>
       </c>
     </row>
@@ -2438,7 +2438,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Jackson, MI, US USA</t>
+          <t>Warren, MI, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2456,7 +2456,7 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9457f2c72938dbd5</t>
+          <t>https://www.indeed.com/viewjob?jk=21899fbf482a9cd2</t>
         </is>
       </c>
     </row>
@@ -2473,7 +2473,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Holland, MI, US USA</t>
+          <t>Jackson, MI, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2491,7 +2491,7 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6f79614628dc966f</t>
+          <t>https://www.indeed.com/viewjob?jk=9457f2c72938dbd5</t>
         </is>
       </c>
     </row>
@@ -2508,7 +2508,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Farmington Hills, MI, US USA</t>
+          <t>Holland, MI, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2526,7 +2526,7 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fc4be70d8a478d8a</t>
+          <t>https://www.indeed.com/viewjob?jk=6f79614628dc966f</t>
         </is>
       </c>
     </row>
@@ -2543,7 +2543,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Jackson, MI, US USA</t>
+          <t>Farmington Hills, MI, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2561,24 +2561,24 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dad209d8bad2edfe</t>
+          <t>https://www.indeed.com/viewjob?jk=fc4be70d8a478d8a</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Sr Software Engineer I</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>RWE</t>
+          <t>Community Choice Credit Union</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Jackson, MI, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,34 +2586,34 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>RDS, Azure, ETL, CI/CD, Azure DevOps, Terraform, Kubernetes, AKS, Airflow, Apache Airflow</t>
+          <t>RDS, Azure, Data Factory, Scala, Snowflake, SQL Server, Data Modeling, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f6ad43066e853c35</t>
+          <t>https://www.indeed.com/viewjob?jk=dad209d8bad2edfe</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Intentsify</t>
+          <t>SBA Communications</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Boca Raton, FL, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2621,7 +2621,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, S3, SQS, SNS, IAM, Snowflake, ETL, ELT, CI/CD, Terraform</t>
+          <t>RDS, Azure, Data Factory, Databricks, Dataflow, Scala, Data Modeling, dbt, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,24 +2631,24 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6d89a533339b416c</t>
+          <t>https://www.indeed.com/viewjob?jk=31b2e27b37e8f33d</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Consultant, Data &amp; Analytics, NA</t>
+          <t>Data Architect, Corporate Services</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>The Coca-Cola Company</t>
+          <t>The Carlyle Group</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,34 +2656,34 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Scala, ETL, ELT, Power BI, Tableau, Git</t>
+          <t>AWS, RDS, Azure, Databricks, Snowflake, Data Modeling, Microsoft SSIS, dbt, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=df7e6baa7a7dd0a0</t>
+          <t>https://www.indeed.com/viewjob?jk=5c3007521d1e10c7</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>Consultant, Data &amp; Analytics, NA</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>SBA Communications</t>
+          <t>The Coca-Cola Company</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Boca Raton, FL, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,7 +2691,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Dataflow, Scala, Data Modeling, dbt, Power BI, CI/CD</t>
+          <t>AWS, RDS, Azure, Databricks, Scala, ETL, ELT, Power BI, Tableau, Git</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2701,24 +2701,24 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=31b2e27b37e8f33d</t>
+          <t>https://www.indeed.com/viewjob?jk=df7e6baa7a7dd0a0</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Data Architect, Corporate Services</t>
+          <t>Databricks Platform Engineer</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>The Carlyle Group</t>
+          <t>Booz Allen Hamilton</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,34 +2726,34 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Snowflake, Data Modeling, Microsoft SSIS, dbt, Power BI, CI/CD</t>
+          <t>RDS, Databricks, Unity Catalog, Scala, ELT, Splunk, DataOps, MLOps, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5c3007521d1e10c7</t>
+          <t>https://www.indeed.com/viewjob?jk=6d89b1928ab17ec0</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Databricks Platform Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Booz Allen Hamilton</t>
+          <t>Intentsify</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2761,7 +2761,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Unity Catalog, Scala, ELT, Splunk, DataOps, MLOps, CI/CD, GitHub Actions</t>
+          <t>AWS, S3, SQS, SNS, IAM, Snowflake, ETL, ELT, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2771,24 +2771,24 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6d89b1928ab17ec0</t>
+          <t>https://www.indeed.com/viewjob?jk=6d89a533339b416c</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Full-stack Engineer 5 (Nodejs/Go/Angularjs)</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>AMD</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,7 +2796,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Medallion Architecture, Spark, PySpark, Snowflake, dbt, Power BI</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,24 +2806,24 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9724e994419d2473</t>
+          <t>https://www.indeed.com/viewjob?jk=9813442a220867be</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Full-stack Engineer 4 - RiskTech</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>WellSky</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Overland Park, KS, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,7 +2831,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>RDS, GCP, BigQuery, Scala, SQL Server, Data Modeling, ETL, ELT, dbt, Tableau</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,24 +2841,24 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1d0888bf081a07cc</t>
+          <t>https://www.indeed.com/viewjob?jk=f2960b2498873f28</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Data Engineer II - AWS/PySpark/ETL</t>
+          <t>Full-stack Engineer 4 (Golang, Python, Java, AWS)</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,7 +2866,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Spark, PySpark, Scala, Snowflake, ETL, CI/CD, Airflow</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2876,24 +2876,24 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aa1cc23a36ed4493</t>
+          <t>https://www.indeed.com/viewjob?jk=da278457dd975c3f</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Full-stack Engineer 4</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Dropbox</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Kinesis, RDS, Databricks, Medallion Architecture, Spark, Scala, Kafka, Data Modeling, Airflow, Python</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2911,19 +2911,19 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=43e37e262d8bc84b</t>
+          <t>https://www.indeed.com/viewjob?jk=18716e78985d34c6</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Databricks Platform Engineer</t>
+          <t>Full-stack Engineer 4 (Go, AWS)</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Booz Allen Hamilton</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -2936,7 +2936,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Unity Catalog, Scala, ELT, Splunk, DataOps, MLOps, GitHub Actions, Terraform</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2946,24 +2946,24 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d727a12d260ca4e6</t>
+          <t>https://www.indeed.com/viewjob?jk=6132bb0eb6aaf86d</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Software Engineer - Cloud Platform Engineering</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>DriveTime Automotive Group</t>
+          <t>MariaDB plc</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Tempe, AZ, US USA</t>
+          <t>VA, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2971,34 +2971,34 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>RDS, Scala, Kafka, Snowflake, SQL Server, Data Modeling, ETL, ELT, dbt, Python</t>
+          <t>AWS, RDS, Azure, GCP, Scala, MySQL, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=05afa083475c5a6e</t>
+          <t>https://www.indeed.com/viewjob?jk=e683398c349f7a6d</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Data Engineer - AWS, Snowflake</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Regions Financial</t>
+          <t>AMD</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Hoover, AL, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3006,7 +3006,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, RDS, Hadoop, Hive, Impala, Spark, PySpark, Scala, Kafka, Snowflake</t>
+          <t>AWS, RDS, Azure, Databricks, Medallion Architecture, Spark, PySpark, Snowflake, dbt, Power BI</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3016,24 +3016,24 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e3740b07510bf369</t>
+          <t>https://www.indeed.com/viewjob?jk=9724e994419d2473</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Senior Software Engineer (Data Platform)</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>MIA Labs</t>
+          <t>WellSky</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Overland Park, KS, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3041,7 +3041,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, BigQuery, Scala, Snowflake, Data Modeling, Dimensional Modeling, ELT, dbt</t>
+          <t>RDS, GCP, BigQuery, Scala, SQL Server, Data Modeling, ETL, ELT, dbt, Tableau</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3051,24 +3051,24 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f1a60bd31f33e718</t>
+          <t>https://www.indeed.com/viewjob?jk=1d0888bf081a07cc</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Full-stack Engineer 5 (Nodejs/Go/Angularjs)</t>
+          <t>Data Engineer II - AWS/PySpark/ETL</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3076,7 +3076,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
+          <t>AWS, RDS, Databricks, Spark, PySpark, Scala, Snowflake, ETL, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3086,24 +3086,24 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9813442a220867be</t>
+          <t>https://www.indeed.com/viewjob?jk=aa1cc23a36ed4493</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Full-stack Engineer 4 - RiskTech</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>Dropbox</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3111,7 +3111,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
+          <t>Kinesis, RDS, Databricks, Medallion Architecture, Spark, Scala, Kafka, Data Modeling, Airflow, Python</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3121,19 +3121,19 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f2960b2498873f28</t>
+          <t>https://www.indeed.com/viewjob?jk=43e37e262d8bc84b</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Full-stack Engineer 4 (Golang, Python, Java, AWS)</t>
+          <t>Databricks Platform Engineer</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>Booz Allen Hamilton</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -3146,7 +3146,7 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
+          <t>RDS, Databricks, Unity Catalog, Scala, ELT, Splunk, DataOps, MLOps, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -3156,24 +3156,24 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=da278457dd975c3f</t>
+          <t>https://www.indeed.com/viewjob?jk=d727a12d260ca4e6</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Full-stack Engineer 4</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>DriveTime Automotive Group</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Tempe, AZ, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3181,7 +3181,7 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
+          <t>RDS, Scala, Kafka, Snowflake, SQL Server, Data Modeling, ETL, ELT, dbt, Python</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -3191,24 +3191,24 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=18716e78985d34c6</t>
+          <t>https://www.indeed.com/viewjob?jk=05afa083475c5a6e</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Full-stack Engineer 4 (Go, AWS)</t>
+          <t>Senior Software Engineer (Data Platform)</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>MIA Labs</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3216,7 +3216,7 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
+          <t>AWS, Azure, GCP, BigQuery, Scala, Snowflake, Data Modeling, Dimensional Modeling, ELT, dbt</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -3226,24 +3226,24 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6132bb0eb6aaf86d</t>
+          <t>https://www.indeed.com/viewjob?jk=f1a60bd31f33e718</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Backend Developer</t>
+          <t>Associate Solution Architect with Modernization Experience</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>BRMi</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Vienna, VA, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3251,7 +3251,7 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Kafka, CI/CD, Jenkins, Azure DevOps, Maven, Docker, Jenkins</t>
+          <t>AWS, Azure, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -3261,24 +3261,24 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fe1f889a04aac578</t>
+          <t>https://www.indeed.com/viewjob?jk=c343a7d6432ffeaa</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Data Scientist Associate</t>
+          <t>Associate Solution Architect with Modernization Experience</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Wilmington, DE, US USA</t>
+          <t>Tempe, AZ, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3286,7 +3286,7 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Scala, Snowflake, ETL, ELT, Tableau, Git, Python, SQL</t>
+          <t>AWS, Azure, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -3296,7 +3296,7 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b87fe7f54c012f15</t>
+          <t>https://www.indeed.com/viewjob?jk=e60054b9631d7895</t>
         </is>
       </c>
     </row>
@@ -3313,7 +3313,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3331,7 +3331,7 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c343a7d6432ffeaa</t>
+          <t>https://www.indeed.com/viewjob?jk=99aade9079199e44</t>
         </is>
       </c>
     </row>
@@ -3348,7 +3348,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Tempe, AZ, US USA</t>
+          <t>Las Vegas, NV, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3366,7 +3366,7 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e60054b9631d7895</t>
+          <t>https://www.indeed.com/viewjob?jk=fb5a4840f3df3c6d</t>
         </is>
       </c>
     </row>
@@ -3383,7 +3383,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Morristown, NJ, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3401,7 +3401,7 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=99aade9079199e44</t>
+          <t>https://www.indeed.com/viewjob?jk=55abd889581cdc48</t>
         </is>
       </c>
     </row>
@@ -3418,7 +3418,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Las Vegas, NV, US USA</t>
+          <t>Detroit, MI, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3436,7 +3436,7 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fb5a4840f3df3c6d</t>
+          <t>https://www.indeed.com/viewjob?jk=e3febde783536e21</t>
         </is>
       </c>
     </row>
@@ -3453,7 +3453,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Morristown, NJ, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3471,7 +3471,7 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=55abd889581cdc48</t>
+          <t>https://www.indeed.com/viewjob?jk=1be19f91eec7a842</t>
         </is>
       </c>
     </row>
@@ -3488,7 +3488,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Detroit, MI, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3506,7 +3506,7 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e3febde783536e21</t>
+          <t>https://www.indeed.com/viewjob?jk=7698c96689f48a9e</t>
         </is>
       </c>
     </row>
@@ -3523,7 +3523,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3541,7 +3541,7 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1be19f91eec7a842</t>
+          <t>https://www.indeed.com/viewjob?jk=d2e1386f9d607f38</t>
         </is>
       </c>
     </row>
@@ -3558,7 +3558,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3576,7 +3576,7 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7698c96689f48a9e</t>
+          <t>https://www.indeed.com/viewjob?jk=2f2ca862816ed069</t>
         </is>
       </c>
     </row>
@@ -3593,7 +3593,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -3611,7 +3611,7 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d2e1386f9d607f38</t>
+          <t>https://www.indeed.com/viewjob?jk=a40909cafc968d82</t>
         </is>
       </c>
     </row>
@@ -3628,7 +3628,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -3646,7 +3646,7 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2f2ca862816ed069</t>
+          <t>https://www.indeed.com/viewjob?jk=124344ebd08b7526</t>
         </is>
       </c>
     </row>
@@ -3663,7 +3663,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
@@ -3681,7 +3681,7 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a40909cafc968d82</t>
+          <t>https://www.indeed.com/viewjob?jk=f0ef6c1eb38b0db9</t>
         </is>
       </c>
     </row>
@@ -3698,7 +3698,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
@@ -3716,7 +3716,7 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=124344ebd08b7526</t>
+          <t>https://www.indeed.com/viewjob?jk=b780dcc242beb567</t>
         </is>
       </c>
     </row>
@@ -3733,7 +3733,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
@@ -3751,7 +3751,7 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f0ef6c1eb38b0db9</t>
+          <t>https://www.indeed.com/viewjob?jk=a03180188c81f9bf</t>
         </is>
       </c>
     </row>
@@ -3768,7 +3768,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
@@ -3786,7 +3786,7 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b780dcc242beb567</t>
+          <t>https://www.indeed.com/viewjob?jk=8a037168850b8fe0</t>
         </is>
       </c>
     </row>
@@ -3803,7 +3803,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
@@ -3821,7 +3821,7 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a03180188c81f9bf</t>
+          <t>https://www.indeed.com/viewjob?jk=45cd4b8d959d97ab</t>
         </is>
       </c>
     </row>
@@ -3838,7 +3838,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
@@ -3856,7 +3856,7 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8a037168850b8fe0</t>
+          <t>https://www.indeed.com/viewjob?jk=52080037fabe4cb1</t>
         </is>
       </c>
     </row>
@@ -3873,7 +3873,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
@@ -3891,7 +3891,7 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=45cd4b8d959d97ab</t>
+          <t>https://www.indeed.com/viewjob?jk=69224b4d176dd4a2</t>
         </is>
       </c>
     </row>
@@ -3908,7 +3908,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Kansas City, MO, US USA</t>
         </is>
       </c>
       <c r="D100" t="n">
@@ -3926,7 +3926,7 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=52080037fabe4cb1</t>
+          <t>https://www.indeed.com/viewjob?jk=5ce9dba6d19c8b82</t>
         </is>
       </c>
     </row>
@@ -3943,7 +3943,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D101" t="n">
@@ -3961,7 +3961,7 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=69224b4d176dd4a2</t>
+          <t>https://www.indeed.com/viewjob?jk=7c5344293aa5ed77</t>
         </is>
       </c>
     </row>
@@ -3978,7 +3978,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Kansas City, MO, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D102" t="n">
@@ -3996,7 +3996,7 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5ce9dba6d19c8b82</t>
+          <t>https://www.indeed.com/viewjob?jk=fea3b3cc46faeb2a</t>
         </is>
       </c>
     </row>
@@ -4013,7 +4013,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D103" t="n">
@@ -4031,7 +4031,7 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7c5344293aa5ed77</t>
+          <t>https://www.indeed.com/viewjob?jk=c3672ad48951be20</t>
         </is>
       </c>
     </row>
@@ -4048,7 +4048,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D104" t="n">
@@ -4066,7 +4066,7 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fea3b3cc46faeb2a</t>
+          <t>https://www.indeed.com/viewjob?jk=c45dff0f36a9a356</t>
         </is>
       </c>
     </row>
@@ -4083,7 +4083,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D105" t="n">
@@ -4101,7 +4101,7 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c3672ad48951be20</t>
+          <t>https://www.indeed.com/viewjob?jk=7e91b7a712b7a165</t>
         </is>
       </c>
     </row>
@@ -4118,7 +4118,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D106" t="n">
@@ -4136,7 +4136,7 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c45dff0f36a9a356</t>
+          <t>https://www.indeed.com/viewjob?jk=f3d69f9412407b80</t>
         </is>
       </c>
     </row>
@@ -4153,7 +4153,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D107" t="n">
@@ -4171,7 +4171,7 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7e91b7a712b7a165</t>
+          <t>https://www.indeed.com/viewjob?jk=7d48fbbfaa3d0a97</t>
         </is>
       </c>
     </row>
@@ -4188,7 +4188,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, US USA</t>
+          <t>Stamford, CT, US USA</t>
         </is>
       </c>
       <c r="D108" t="n">
@@ -4206,7 +4206,7 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f3d69f9412407b80</t>
+          <t>https://www.indeed.com/viewjob?jk=c300f1e448116fd7</t>
         </is>
       </c>
     </row>
@@ -4223,7 +4223,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Sacramento, CA, US USA</t>
         </is>
       </c>
       <c r="D109" t="n">
@@ -4241,7 +4241,7 @@
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7d48fbbfaa3d0a97</t>
+          <t>https://www.indeed.com/viewjob?jk=316adbd72ad7e2e8</t>
         </is>
       </c>
     </row>
@@ -4258,7 +4258,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Stamford, CT, US USA</t>
+          <t>Costa Mesa, CA, US USA</t>
         </is>
       </c>
       <c r="D110" t="n">
@@ -4276,7 +4276,7 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c300f1e448116fd7</t>
+          <t>https://www.indeed.com/viewjob?jk=f219232c6b6eef2b</t>
         </is>
       </c>
     </row>
@@ -4293,7 +4293,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Sacramento, CA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D111" t="n">
@@ -4311,7 +4311,7 @@
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=316adbd72ad7e2e8</t>
+          <t>https://www.indeed.com/viewjob?jk=0bb31aa937d723cd</t>
         </is>
       </c>
     </row>
@@ -4328,7 +4328,7 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Costa Mesa, CA, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D112" t="n">
@@ -4346,7 +4346,7 @@
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f219232c6b6eef2b</t>
+          <t>https://www.indeed.com/viewjob?jk=884c614c785d6835</t>
         </is>
       </c>
     </row>
@@ -4363,7 +4363,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D113" t="n">
@@ -4381,7 +4381,7 @@
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0bb31aa937d723cd</t>
+          <t>https://www.indeed.com/viewjob?jk=ecedaabbce0a0b5b</t>
         </is>
       </c>
     </row>
@@ -4398,7 +4398,7 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D114" t="n">
@@ -4416,7 +4416,7 @@
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=884c614c785d6835</t>
+          <t>https://www.indeed.com/viewjob?jk=eea12c90a4a047af</t>
         </is>
       </c>
     </row>
@@ -4433,7 +4433,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D115" t="n">
@@ -4451,7 +4451,7 @@
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ecedaabbce0a0b5b</t>
+          <t>https://www.indeed.com/viewjob?jk=28b6e9e7e6b5c6aa</t>
         </is>
       </c>
     </row>
@@ -4468,7 +4468,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D116" t="n">
@@ -4486,7 +4486,7 @@
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eea12c90a4a047af</t>
+          <t>https://www.indeed.com/viewjob?jk=2c0e09d9843111bd</t>
         </is>
       </c>
     </row>
@@ -4503,7 +4503,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D117" t="n">
@@ -4521,24 +4521,24 @@
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=28b6e9e7e6b5c6aa</t>
+          <t>https://www.indeed.com/viewjob?jk=3b10af7d10426fa4</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>Associate Solution Architect with Modernization Experience</t>
+          <t>Solution Architect-Full Stack</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Kirby Building Systems</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Portland, TN, US USA</t>
         </is>
       </c>
       <c r="D118" t="n">
@@ -4546,7 +4546,7 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes</t>
+          <t>RDS, Azure, Scala, SQL Server, PostgreSQL, CI/CD, Azure DevOps, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
@@ -4556,24 +4556,24 @@
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2c0e09d9843111bd</t>
+          <t>https://www.indeed.com/viewjob?jk=66ada823af164848</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>Associate Solution Architect with Modernization Experience</t>
+          <t>C# Full Stack Developer</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Globant</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D119" t="n">
@@ -4581,7 +4581,7 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes</t>
+          <t>AWS, S3, RDS, Azure, Scala, SQL Server, PostgreSQL, MySQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
@@ -4591,24 +4591,24 @@
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3b10af7d10426fa4</t>
+          <t>https://www.indeed.com/viewjob?jk=d96c65fe6b68f304</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>Solution Architect-Full Stack</t>
+          <t>Sr Technical Analyst/Prog Ent App</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Kirby Building Systems</t>
+          <t>Avangrid</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Portland, TN, US USA</t>
+          <t>Orange, CT, US USA</t>
         </is>
       </c>
       <c r="D120" t="n">
@@ -4616,7 +4616,7 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, SQL Server, PostgreSQL, CI/CD, Azure DevOps, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, ETL, Azure DevOps, Git</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
@@ -4626,24 +4626,24 @@
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=66ada823af164848</t>
+          <t>https://www.indeed.com/viewjob?jk=4ea1b275b8152311</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>C# Full Stack Developer</t>
+          <t>Full Stack Ad Tech Developer</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Globant</t>
+          <t>The Hearst Corporation</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D121" t="n">
@@ -4651,7 +4651,7 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Scala, SQL Server, PostgreSQL, MySQL, CI/CD, Docker</t>
+          <t>AWS, Redshift, Google Cloud Platform, BigQuery, Scala, ETL, Tableau, CI/CD, Git, Python</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
@@ -4661,24 +4661,24 @@
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d96c65fe6b68f304</t>
+          <t>https://www.indeed.com/viewjob?jk=e8cf1f61c24a8358</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Forward Deployed AI Engineer 2026 - US, COL, UK</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Activated Insights</t>
+          <t>Aimpoint Digital</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D122" t="n">
@@ -4686,17 +4686,17 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>AWS, EMR, S3, RDS, Scala, Snowflake, PostgreSQL, MySQL, ETL, CI/CD</t>
+          <t>AWS, Azure, Databricks, GCP, Scala, Snowflake, ETL, ELT, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4c98c8e05297ceda</t>
+          <t>https://www.indeed.com/viewjob?jk=64c74cca4e3efa95</t>
         </is>
       </c>
     </row>
@@ -4713,7 +4713,7 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Idaho Falls, ID, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D123" t="n">
@@ -4731,24 +4731,24 @@
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7382a9e2385f01a9</t>
+          <t>https://www.indeed.com/viewjob?jk=4c98c8e05297ceda</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>Forward Deployed AI Engineer 2026 - US, COL, UK</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Aimpoint Digital</t>
+          <t>Activated Insights</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Idaho Falls, ID, US USA</t>
         </is>
       </c>
       <c r="D124" t="n">
@@ -4756,34 +4756,34 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, Scala, Snowflake, ETL, ELT, MLOps, CI/CD</t>
+          <t>AWS, EMR, S3, RDS, Scala, Snowflake, PostgreSQL, MySQL, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=64c74cca4e3efa95</t>
+          <t>https://www.indeed.com/viewjob?jk=7382a9e2385f01a9</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>Sr Technical Analyst/Prog Ent App</t>
+          <t>Full-stack Engineer 4 (IC)</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Avangrid</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Orange, CT, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D125" t="n">
@@ -4791,34 +4791,34 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, ETL, Azure DevOps, Git</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4ea1b275b8152311</t>
+          <t>https://www.indeed.com/viewjob?jk=4620494dca257198</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>Full Stack Ad Tech Developer</t>
+          <t>Full-stack Engineer 4 (IC)</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>The Hearst Corporation</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D126" t="n">
@@ -4826,24 +4826,24 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Google Cloud Platform, BigQuery, Scala, ETL, Tableau, CI/CD, Git, Python</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e8cf1f61c24a8358</t>
+          <t>https://www.indeed.com/viewjob?jk=6b1bed8feba6b917</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>Full-stack Engineer 5 (Go, TypeScript and Angular)</t>
+          <t>Full-stack Engineer 4</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -4853,7 +4853,7 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D127" t="n">
@@ -4866,19 +4866,19 @@
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=81ff3ef325447a98</t>
+          <t>https://www.indeed.com/viewjob?jk=8e194fdfb9b8dbe3</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>Full-stack Engineer 4</t>
+          <t>Full-Stack Engineer 4 (Python, AWS, Network Automation)</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -4901,19 +4901,19 @@
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=70843ae9e366dd5b</t>
+          <t>https://www.indeed.com/viewjob?jk=a77780c738e44a57</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>Full - Stack Engineer 5 (Remote - Eligible)</t>
+          <t>Full-stack Engineer 5 (Go, TypeScript and Angular)</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -4923,7 +4923,7 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D129" t="n">
@@ -4941,7 +4941,7 @@
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=877ad6c20024fb1a</t>
+          <t>https://www.indeed.com/viewjob?jk=81ff3ef325447a98</t>
         </is>
       </c>
     </row>
@@ -4958,7 +4958,7 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D130" t="n">
@@ -4976,14 +4976,14 @@
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6979868bb95d63f0</t>
+          <t>https://www.indeed.com/viewjob?jk=70843ae9e366dd5b</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>Full Stack Engineer 5</t>
+          <t>Full - Stack Engineer 5 (Remote - Eligible)</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -5011,14 +5011,14 @@
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b743b91aec079a75</t>
+          <t>https://www.indeed.com/viewjob?jk=877ad6c20024fb1a</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>Full Stack Engineer 4</t>
+          <t>Full-stack Engineer 4</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -5028,7 +5028,7 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D132" t="n">
@@ -5046,14 +5046,14 @@
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3fb66ff5f4ef065f</t>
+          <t>https://www.indeed.com/viewjob?jk=6979868bb95d63f0</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>Full-stack Engineer 4 (Python, Java)</t>
+          <t>Full Stack Engineer 5</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -5063,7 +5063,7 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D133" t="n">
@@ -5081,14 +5081,14 @@
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c9046de91e154d69</t>
+          <t>https://www.indeed.com/viewjob?jk=b743b91aec079a75</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>Full-stack Engineer 5 ( Python, AWS)</t>
+          <t>Full Stack Engineer 4</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -5116,14 +5116,14 @@
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5e4de127a7227d81</t>
+          <t>https://www.indeed.com/viewjob?jk=3fb66ff5f4ef065f</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>Full-stack Engineer 5 (Golang, Java, AWS)</t>
+          <t>Full-stack Engineer 4 (Python, Java)</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -5133,7 +5133,7 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D135" t="n">
@@ -5151,14 +5151,14 @@
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f3a9ee8f682a9c78</t>
+          <t>https://www.indeed.com/viewjob?jk=c9046de91e154d69</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>Full-stack Engineer 4 - Intelligent Foundations and Experiences (IFX)</t>
+          <t>Full-stack Engineer 5 ( Python, AWS)</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -5186,14 +5186,14 @@
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6faf5ca1640fcd31</t>
+          <t>https://www.indeed.com/viewjob?jk=5e4de127a7227d81</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>Full-stack Engineer 4 - Intelligent Foundations and Experiences (IFX)</t>
+          <t>Full-stack Engineer 5 (Golang, Java, AWS)</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -5203,7 +5203,7 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D137" t="n">
@@ -5221,14 +5221,14 @@
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=42133a298638cb9b</t>
+          <t>https://www.indeed.com/viewjob?jk=f3a9ee8f682a9c78</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>Full-stack Engineer 5</t>
+          <t>Full-stack Engineer 4 - Intelligent Foundations and Experiences (IFX)</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -5256,7 +5256,7 @@
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a708182f9a1da64d</t>
+          <t>https://www.indeed.com/viewjob?jk=6faf5ca1640fcd31</t>
         </is>
       </c>
     </row>
@@ -5291,14 +5291,14 @@
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=76c8a5b4fcc58505</t>
+          <t>https://www.indeed.com/viewjob?jk=42133a298638cb9b</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>Full-stack Engineer 5 - Shopping (Remote-Eligible)</t>
+          <t>Full-stack Engineer 5</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -5326,14 +5326,14 @@
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=419688dc0cbfaf98</t>
+          <t>https://www.indeed.com/viewjob?jk=a708182f9a1da64d</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>Full-stack Engineer 5 (Java, Scala, AWS)</t>
+          <t>Full-stack Engineer 4 - Intelligent Foundations and Experiences (IFX)</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -5343,7 +5343,7 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D141" t="n">
@@ -5361,14 +5361,14 @@
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c997daa05db4e0c7</t>
+          <t>https://www.indeed.com/viewjob?jk=76c8a5b4fcc58505</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>Full Stack Engineer 4 (Go, AWS)</t>
+          <t>Full-stack Engineer 5 - Shopping (Remote-Eligible)</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -5396,14 +5396,14 @@
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6a9874c783fb4a03</t>
+          <t>https://www.indeed.com/viewjob?jk=419688dc0cbfaf98</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>Full-stack Engineer 4</t>
+          <t>Full-stack Engineer 5 (Java, Scala, AWS)</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -5431,14 +5431,14 @@
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1f96da918db85a2a</t>
+          <t>https://www.indeed.com/viewjob?jk=c997daa05db4e0c7</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>Full-stack Engineer 4 (Java, Scala, AWS)</t>
+          <t>Full Stack Engineer 4 (Go, AWS)</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -5448,7 +5448,7 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D144" t="n">
@@ -5466,7 +5466,7 @@
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b9e0187cbe4c2e40</t>
+          <t>https://www.indeed.com/viewjob?jk=6a9874c783fb4a03</t>
         </is>
       </c>
     </row>
@@ -5501,14 +5501,14 @@
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=900df92ddc778d5f</t>
+          <t>https://www.indeed.com/viewjob?jk=1f96da918db85a2a</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>Full-stack Engineer 4 (JavaScript, React)</t>
+          <t>Full-stack Engineer 4 (Java, Scala, AWS)</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -5518,7 +5518,7 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D146" t="n">
@@ -5536,14 +5536,14 @@
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e7c346fa6453ffb9</t>
+          <t>https://www.indeed.com/viewjob?jk=b9e0187cbe4c2e40</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>Full-stack Engineer 5 (Go/Java, Angular, AWS)</t>
+          <t>Full-stack Engineer 4</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -5553,7 +5553,7 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D147" t="n">
@@ -5571,14 +5571,14 @@
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c039bc465260bc95</t>
+          <t>https://www.indeed.com/viewjob?jk=900df92ddc778d5f</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>Full-stack Engineer 4</t>
+          <t>Full-stack Engineer 4 (JavaScript, React)</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -5588,7 +5588,7 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D148" t="n">
@@ -5606,14 +5606,14 @@
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=54e236865193f8a0</t>
+          <t>https://www.indeed.com/viewjob?jk=e7c346fa6453ffb9</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>Full-stack Engineer 4</t>
+          <t>Full-stack Engineer 5 (Go/Java, Angular, AWS)</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -5623,7 +5623,7 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D149" t="n">
@@ -5641,14 +5641,14 @@
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b667ebd325202576</t>
+          <t>https://www.indeed.com/viewjob?jk=c039bc465260bc95</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>Full-stack Engineer 5 (Golang, AWS)</t>
+          <t>Full-stack Engineer 4</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -5658,7 +5658,7 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D150" t="n">
@@ -5676,14 +5676,14 @@
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=672e371e8fd60859</t>
+          <t>https://www.indeed.com/viewjob?jk=54e236865193f8a0</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>Full-stack Engineer 4 (React, TypeScript, AWS)</t>
+          <t>Full-stack Engineer 4</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -5711,14 +5711,14 @@
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=346a7f081a67b46c</t>
+          <t>https://www.indeed.com/viewjob?jk=b667ebd325202576</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>Full-stack Engineer 4</t>
+          <t>Full-stack Engineer 5 (Golang, AWS)</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -5746,14 +5746,14 @@
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7b21934bf2433e6a</t>
+          <t>https://www.indeed.com/viewjob?jk=672e371e8fd60859</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>Full-stack Engineer 4 (Scala, React, AWS)</t>
+          <t>Full-stack Engineer 4 (React, TypeScript, AWS)</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -5763,7 +5763,7 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D153" t="n">
@@ -5781,14 +5781,14 @@
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2af3b2e528eb8c47</t>
+          <t>https://www.indeed.com/viewjob?jk=346a7f081a67b46c</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>Full-stack Engineer 4 (Scala, React, AWS)</t>
+          <t>Full-stack Engineer 4</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -5798,7 +5798,7 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D154" t="n">
@@ -5816,14 +5816,14 @@
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=51fd20841ca9c754</t>
+          <t>https://www.indeed.com/viewjob?jk=7b21934bf2433e6a</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>Full-stack Engineer 4</t>
+          <t>Full-stack Engineer 4 (Scala, React, AWS)</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -5833,7 +5833,7 @@
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D155" t="n">
@@ -5851,14 +5851,14 @@
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=619531dae358928f</t>
+          <t>https://www.indeed.com/viewjob?jk=2af3b2e528eb8c47</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>Full-stack Engineer 4 (Python, AWS)</t>
+          <t>Full-stack Engineer 4 (Scala, React, AWS)</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -5868,7 +5868,7 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D156" t="n">
@@ -5886,14 +5886,14 @@
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8e4eaf7eaa027bbb</t>
+          <t>https://www.indeed.com/viewjob?jk=51fd20841ca9c754</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>Full-stack Engineer 4 (GoLang)</t>
+          <t>Full-stack Engineer 4</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -5903,7 +5903,7 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D157" t="n">
@@ -5921,14 +5921,14 @@
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b7c24e0e87f3fc42</t>
+          <t>https://www.indeed.com/viewjob?jk=619531dae358928f</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>Full-Stack Engineer 4 (Automation Quality Engineer)</t>
+          <t>Full-stack Engineer 4 (Python, AWS)</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -5938,7 +5938,7 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Riverwoods, IL, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D158" t="n">
@@ -5956,14 +5956,14 @@
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2acd23b24043f205</t>
+          <t>https://www.indeed.com/viewjob?jk=8e4eaf7eaa027bbb</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>Full-stack Engineer 4 - Shopping (Remote-Eligible)</t>
+          <t>Full-stack Engineer 4 (GoLang)</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -5973,7 +5973,7 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D159" t="n">
@@ -5991,32 +5991,32 @@
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f87b328e958cbb63</t>
+          <t>https://www.indeed.com/viewjob?jk=b7c24e0e87f3fc42</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Full-Stack Engineer 4 (Automation Quality Engineer)</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>KeHE Distributors</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Naperville, IL, US USA</t>
+          <t>Riverwoods, IL, US USA</t>
         </is>
       </c>
       <c r="D160" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, Data Modeling, Power BI, Tableau, MLOps</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
@@ -6026,32 +6026,32 @@
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9033c8036c6af9b3</t>
+          <t>https://www.indeed.com/viewjob?jk=2acd23b24043f205</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>Data Platform Engineer</t>
+          <t>Full-stack Engineer 4 - Shopping (Remote-Eligible)</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>Hubble Network</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D161" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>Kinesis, Redshift, RDS, Scala, Kafka, Dimensional Modeling, Star Schema, Fact Tables, ETL, dbt</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
@@ -6061,24 +6061,24 @@
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a000c1d1d33d8b12</t>
+          <t>https://www.indeed.com/viewjob?jk=f87b328e958cbb63</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>Data &amp; AI Engineer</t>
+          <t>Integration Engineer 4</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>The Carlyle Group</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D162" t="n">
@@ -6086,34 +6086,34 @@
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Spark, Scala, Snowflake, ELT, dbt, MLflow, CI/CD</t>
+          <t>AWS, Lambda, Step Functions, RDS, Azure, GCP, Scala, Splunk, Jenkins, Jenkins</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=83876c66e135b993</t>
+          <t>https://www.indeed.com/viewjob?jk=52d873bb7fc420f0</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>Data &amp; AI Engineer</t>
+          <t>Junior/Mid Software Engineer</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>The Carlyle Group</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D163" t="n">
@@ -6121,34 +6121,34 @@
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Spark, Scala, Snowflake, ELT, dbt, MLflow, CI/CD</t>
+          <t>AWS, Azure, Google Cloud Platform, GCP, Hadoop, Spark, Scala, Kafka, NoSQL, Kubernetes</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f4924b3389452957</t>
+          <t>https://www.indeed.com/viewjob?jk=d87ecb6d60b0f54d</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>Integration Engineer 4</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>KeHE Distributors</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Naperville, IL, US USA</t>
         </is>
       </c>
       <c r="D164" t="n">
@@ -6156,7 +6156,7 @@
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, RDS, Azure, GCP, Scala, Splunk, Jenkins, Jenkins</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, Data Modeling, Power BI, Tableau, MLOps</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
@@ -6166,24 +6166,24 @@
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=52d873bb7fc420f0</t>
+          <t>https://www.indeed.com/viewjob?jk=9033c8036c6af9b3</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer 4 (Python, AWS, SQL, GenAI) (Enterprise Platforms Technology)</t>
+          <t>Data Platform Engineer</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>Hubble Network</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D165" t="n">
@@ -6191,7 +6191,7 @@
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, CI/CD, Kubernetes, Python, SQL</t>
+          <t>Kinesis, Redshift, RDS, Scala, Kafka, Dimensional Modeling, Star Schema, Fact Tables, ETL, dbt</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
@@ -6201,24 +6201,24 @@
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4922f7a57cfbdccb</t>
+          <t>https://www.indeed.com/viewjob?jk=a000c1d1d33d8b12</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer 4 (Python, AWS, SQL, GenAI) (Enterprise Platforms Technology)</t>
+          <t>Data &amp; AI Engineer</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>The Carlyle Group</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D166" t="n">
@@ -6226,34 +6226,34 @@
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, CI/CD, Kubernetes, Python, SQL</t>
+          <t>AWS, RDS, Databricks, Spark, Scala, Snowflake, ELT, dbt, MLflow, CI/CD</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=09348324e49b31d7</t>
+          <t>https://www.indeed.com/viewjob?jk=83876c66e135b993</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>Junior/Mid Software Engineer</t>
+          <t>Data &amp; AI Engineer</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>The Carlyle Group</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D167" t="n">
@@ -6261,17 +6261,17 @@
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, GCP, Hadoop, Spark, Scala, Kafka, NoSQL, Kubernetes</t>
+          <t>AWS, RDS, Databricks, Spark, Scala, Snowflake, ELT, dbt, MLflow, CI/CD</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d87ecb6d60b0f54d</t>
+          <t>https://www.indeed.com/viewjob?jk=f4924b3389452957</t>
         </is>
       </c>
     </row>
@@ -6313,17 +6313,17 @@
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>Sr Product Security Engineer, AI &amp; DevSecOps</t>
+          <t>Healthcare Interoperability Engineer</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>McKesson</t>
+          <t>MedQuest Imaging</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D169" t="n">
@@ -6331,34 +6331,34 @@
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Kubernetes</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, CI/CD, Azure DevOps, Terraform, Git</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4b8ba8f92a1292eb</t>
+          <t>https://www.indeed.com/viewjob?jk=eeb961148c207be2</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>Sr. iOS Developer--Hybrid</t>
+          <t>Data Scientist IV</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>CareSource</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Bridgewater, NJ, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D170" t="n">
@@ -6366,34 +6366,34 @@
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>S3, RDS, Scala, PostgreSQL, MySQL, Cassandra, REST API integration, Jenkins, Jenkins, Git</t>
+          <t>AWS, EMR, RDS, Azure, Databricks, GCP, Scala, Snowflake, Data Modeling, MLOps</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a2f579d7993e4d2c</t>
+          <t>https://www.indeed.com/viewjob?jk=f79ced955268a69b</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>Sr Software Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>Resideo</t>
+          <t>Function Health</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D171" t="n">
@@ -6401,7 +6401,7 @@
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Event Hubs, Scala, NoSQL, Data Modeling, CI/CD, Docker, Kubernetes</t>
+          <t>RDS, Databricks, BigQuery, Spark, Kafka, Snowflake, ELT, dbt, MLOps, Terraform</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
@@ -6411,24 +6411,24 @@
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6f3ccdfade853d8f</t>
+          <t>https://www.indeed.com/viewjob?jk=8d332f2047edfa45</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Full Stack (FES)</t>
+          <t>Engineer, Performance Management</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>Fanatics</t>
+          <t>The Carlyle Group</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D172" t="n">
@@ -6436,120 +6436,15 @@
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>AWS, SQS, SNS, IAM, RDS, Azure, GCP, Kafka, NoSQL, CI/CD</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, SQL Server, ETL, Power BI, CI/CD, Git</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=e95812a1a87ee87c</t>
-        </is>
-      </c>
-    </row>
-    <row r="173">
-      <c r="A173" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer, Full Stack (FES)</t>
-        </is>
-      </c>
-      <c r="B173" t="inlineStr">
-        <is>
-          <t>Fanatics</t>
-        </is>
-      </c>
-      <c r="C173" t="inlineStr">
-        <is>
-          <t>New York, NY, US USA</t>
-        </is>
-      </c>
-      <c r="D173" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E173" t="inlineStr">
-        <is>
-          <t>AWS, SQS, SNS, IAM, RDS, Azure, GCP, Kafka, NoSQL, CI/CD</t>
-        </is>
-      </c>
-      <c r="F173" t="inlineStr">
-        <is>
-          <t>2026-09-22</t>
-        </is>
-      </c>
-      <c r="G173" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=f0dd1357e631ea44</t>
-        </is>
-      </c>
-    </row>
-    <row r="174">
-      <c r="A174" t="inlineStr">
-        <is>
-          <t>Data Engineer</t>
-        </is>
-      </c>
-      <c r="B174" t="inlineStr">
-        <is>
-          <t>Function Health</t>
-        </is>
-      </c>
-      <c r="C174" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D174" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E174" t="inlineStr">
-        <is>
-          <t>RDS, Databricks, BigQuery, Spark, Kafka, Snowflake, ELT, dbt, MLOps, Terraform</t>
-        </is>
-      </c>
-      <c r="F174" t="inlineStr">
-        <is>
-          <t>2026-09-22</t>
-        </is>
-      </c>
-      <c r="G174" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=8d332f2047edfa45</t>
-        </is>
-      </c>
-    </row>
-    <row r="175">
-      <c r="A175" t="inlineStr">
-        <is>
-          <t>Engineer, Performance Management</t>
-        </is>
-      </c>
-      <c r="B175" t="inlineStr">
-        <is>
-          <t>The Carlyle Group</t>
-        </is>
-      </c>
-      <c r="C175" t="inlineStr">
-        <is>
-          <t>Washington, DC, US USA</t>
-        </is>
-      </c>
-      <c r="D175" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E175" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, SQL Server, ETL, Power BI, CI/CD, Git</t>
-        </is>
-      </c>
-      <c r="F175" t="inlineStr">
-        <is>
-          <t>2026-09-15</t>
-        </is>
-      </c>
-      <c r="G175" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=9e0346f80c455f7d</t>
         </is>

--- a/results/job_matches_2026-09-23.xlsx
+++ b/results/job_matches_2026-09-23.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G172"/>
+  <dimension ref="A1:G165"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,175 +468,175 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Platform Engineer - Databricks</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Coca Cola Southwest Beverages</t>
+          <t>Changeis, Inc.</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>20.1</v>
+        <v>19.4</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Snowflake, SQL Server</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Delta Live Tables, Cloud Storage, Spark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ca8f627225261b22</t>
+          <t>https://www.indeed.com/viewjob?jk=435e38702075f0bd</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>I.T. - DevOps Engineer</t>
+          <t>Software Engineer 2 (.NET / Java Spring Boot / AWS)</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>StorageMart</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Columbia, MO, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>18.8</v>
+        <v>19.4</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, ECS, IAM, RDS, Azure, MySQL, MongoDB</t>
+          <t>AWS, Lambda, S3, API Gateway, ECS, RDS, Azure, Scala, Oracle, SQL Server</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c2e972535a11a31f</t>
+          <t>https://www.indeed.com/viewjob?jk=f36f17458475becb</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Data Engineer 4 (Python, AWS, Kafka, Spark, SQL, Snowflake, Databricks, GenAI)</t>
+          <t>I.T. - DevOps Engineer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>StorageMart</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Columbia, MO, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>16.7</v>
+        <v>18.8</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Redshift, RDS, Azure, Databricks, Spark, Scala, Kafka</t>
+          <t>AWS, Lambda, S3, SQS, ECS, IAM, RDS, Azure, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=47e2de3bf66a6750</t>
+          <t>https://www.indeed.com/viewjob?jk=c2e972535a11a31f</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Data Engineer Sr</t>
+          <t>Snowflake Platform Admin + Data Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Oshkosh Corporation</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Oshkosh, WI, US USA</t>
+          <t>Fort Mill, SC, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>16.7</v>
+        <v>18.1</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Data Factory, Databricks, GCP, Hadoop, HDFS, Hive</t>
+          <t>AWS, Glue, Lambda, S3, IAM, RDS, Azure, Scala, Snowflake, Time Travel</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8b5c363397eafe5f</t>
+          <t>https://www.indeed.com/viewjob?jk=84e09b6c27eafb1d</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Associate Data Engineer</t>
+          <t>AI Architect (Dynamics 365 Copilot) (ONSITE in Vienna, VA)</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Blue Cross and Blue Shield of Minnesota</t>
+          <t>COMPEST SOLUTIONS INDIA PRIVATE LIMITED</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Eagan, MN, US USA</t>
+          <t>Vienna, VA, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>16.7</v>
+        <v>18.1</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, S3, SQS, SNS, RDS, Databricks, Spark</t>
+          <t>AWS, S3, RDS, Azure, Blob Storage, Cloud Storage, Scala, Oracle, SQL Server, MySQL</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=31bf226ac97de61e</t>
+          <t>https://www.indeed.com/viewjob?jk=781e2cfbc6955c3b</t>
         </is>
       </c>
     </row>
@@ -648,12 +648,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Sally Beauty</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Denton, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -661,34 +661,34 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Databricks, Data Lake Storage, Unity Catalog, Medallion Architecture, Delta Live Tables, Google Cloud Platform</t>
+          <t>AWS, RDS, Databricks, GCP, Hadoop, Spark, Scala, Kafka, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0864fe655aae7888</t>
+          <t>https://www.indeed.com/viewjob?jk=3d6acf2339423ef7</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Data Engineer 4 (Python, AWS, Kafka, Spark, SQL, Snowflake, Databricks, GenAI)</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>RI, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -696,7 +696,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI</t>
+          <t>AWS, Glue, EMR, Redshift, RDS, Azure, Databricks, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,24 +706,24 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8dd495afc5140159</t>
+          <t>https://www.indeed.com/viewjob?jk=47e2de3bf66a6750</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Enterprise Data Architect</t>
+          <t>Associate Data Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Alignment Health</t>
+          <t>Blue Cross and Blue Shield of Minnesota</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Orange, CA, US USA</t>
+          <t>Eagan, MN, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -731,7 +731,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Scala, Snowflake, Data Modeling</t>
+          <t>AWS, Glue, EMR, Lambda, S3, SQS, SNS, RDS, Databricks, Spark</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,24 +741,24 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1611fa9de2f7504b</t>
+          <t>https://www.indeed.com/viewjob?jk=31bf226ac97de61e</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Senior AI Ops / DevOps Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Sally Beauty</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Denton, TX, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -766,7 +766,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Splunk, MLOps, MLflow, CI/CD, Jenkins</t>
+          <t>AWS, S3, RDS, Azure, Databricks, Data Lake Storage, Unity Catalog, Medallion Architecture, Delta Live Tables, Google Cloud Platform</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,67 +776,67 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=040c156b15abd039</t>
+          <t>https://www.indeed.com/viewjob?jk=0864fe655aae7888</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Data Engineer 5 - Enterprise Risk Management</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>RI, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>16</v>
+        <v>16.7</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Redshift, RDS, Azure, Databricks, Spark, Scala, Snowflake</t>
+          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a45f08af4f7be5f6</t>
+          <t>https://www.indeed.com/viewjob?jk=8dd495afc5140159</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Data Engineer 4 - Nexus Products</t>
+          <t>Enterprise Data Architect</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>Alignment Health</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Orange, CA, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>16</v>
+        <v>16.7</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Redshift, RDS, Azure, Databricks, Spark, Scala, Snowflake</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Scala, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,32 +846,32 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=36fc31dc37d05722</t>
+          <t>https://www.indeed.com/viewjob?jk=1611fa9de2f7504b</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Data Engineer 4</t>
+          <t>Senior AI Ops / DevOps Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>16</v>
+        <v>16.7</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Redshift, RDS, Azure, Databricks, Spark, Scala, Snowflake</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Splunk, MLOps, MLflow, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,14 +881,14 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=45e14228c1ed2aed</t>
+          <t>https://www.indeed.com/viewjob?jk=040c156b15abd039</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Data Engineer 4 - Payment Networks</t>
+          <t>Data Engineer 5 - Enterprise Risk Management</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -916,14 +916,14 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f8d0c3f139798fd9</t>
+          <t>https://www.indeed.com/viewjob?jk=a45f08af4f7be5f6</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Data Engineer 4 - HR Tech</t>
+          <t>Data Engineer 4 - Nexus Products</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -951,14 +951,14 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=010f3637940ea854</t>
+          <t>https://www.indeed.com/viewjob?jk=36fc31dc37d05722</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Data Engineer 5 (SEO/GEO, AdTech )</t>
+          <t>Data Engineer 4 - Payment Networks</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -986,14 +986,14 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e9a8f6941c1a4549</t>
+          <t>https://www.indeed.com/viewjob?jk=f8d0c3f139798fd9</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Data Engineer 4</t>
+          <t>Data Engineer 4 - HR Tech</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1021,14 +1021,14 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0db4720c664a5a3f</t>
+          <t>https://www.indeed.com/viewjob?jk=010f3637940ea854</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Data Engineer 4</t>
+          <t>Data Engineer 5 (SEO/GEO, AdTech )</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1056,14 +1056,14 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d80c6adab1193eaf</t>
+          <t>https://www.indeed.com/viewjob?jk=e9a8f6941c1a4549</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Data Engineer 5 (Enterprise Platforms Technology)</t>
+          <t>Data Engineer 4</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1073,7 +1073,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1091,14 +1091,14 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=220dab7fe793042b</t>
+          <t>https://www.indeed.com/viewjob?jk=0db4720c664a5a3f</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Data Engineer 5</t>
+          <t>Data Engineer 4</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1126,14 +1126,14 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3a1e95e5123a2b15</t>
+          <t>https://www.indeed.com/viewjob?jk=d80c6adab1193eaf</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Data Engineer 4</t>
+          <t>Data Engineer 5 (Enterprise Platforms Technology)</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1143,7 +1143,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1161,24 +1161,24 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6438ee405fccd9e0</t>
+          <t>https://www.indeed.com/viewjob?jk=220dab7fe793042b</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Engineer 5</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Tiger Analytics</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1186,7 +1186,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Cloud Storage, Spark, PySpark, Scala, Snowflake</t>
+          <t>AWS, Glue, EMR, Redshift, RDS, Azure, Databricks, Spark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,24 +1196,24 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4b2cb75552da28cb</t>
+          <t>https://www.indeed.com/viewjob?jk=3a1e95e5123a2b15</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Junior Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Tiger Analytics</t>
+          <t>Techsur Solutions</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Reston, VA, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1221,17 +1221,17 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Cloud Storage, Spark, PySpark, Scala, Snowflake</t>
+          <t>AWS, S3, IAM, RDS, Azure, Scala, Splunk, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4b046b29ca6b7df4</t>
+          <t>https://www.indeed.com/viewjob?jk=1dfb157f527b54b9</t>
         </is>
       </c>
     </row>
@@ -1308,17 +1308,17 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Senior Data Platfrom Engineer</t>
+          <t>Data Engineer I, II</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Moda Health</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Portland, OR, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,7 +1326,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Delta Live Tables, Spark, PySpark, Scala, Data Modeling</t>
+          <t>Redshift, Azure, Data Factory, BigQuery, Scala, Snowflake, SQL Server, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,24 +1336,24 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bc974eac3e508ce6</t>
+          <t>https://www.indeed.com/viewjob?jk=7db50249524e5920</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Analyst / Data Engineer – Python, Automation &amp; AI</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>iVedha Inc.</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Toronto, OH, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,7 +1361,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Delta Live Tables, Spark, PySpark, Scala, Data Modeling</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Scala, Snowflake, ETL, ELT</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,24 +1371,24 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e85b5d56e27bdfb8</t>
+          <t>https://www.indeed.com/viewjob?jk=94a37fc46cd45ada</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Cloud Engineer</t>
+          <t>Senior Data Platfrom Engineer</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Willdan</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Anaheim, CA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,34 +1396,34 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, Azure, Scala, Amazon QuickSight, CI/CD</t>
+          <t>RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Delta Live Tables, Spark, PySpark, Scala, Data Modeling</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8d1298ac76effc74</t>
+          <t>https://www.indeed.com/viewjob?jk=bc974eac3e508ce6</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>C,C++, Python, Golang Developer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,7 +1431,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, SQL Server, PostgreSQL, CI/CD</t>
+          <t>RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Delta Live Tables, Spark, PySpark, Scala, Data Modeling</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,32 +1441,32 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=441856af730024e8</t>
+          <t>https://www.indeed.com/viewjob?jk=e85b5d56e27bdfb8</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Back-end Engineer - Data Platforms</t>
+          <t>Cloud Engineer</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Morgan Stanley</t>
+          <t>Willdan</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Anaheim, CA, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Spark, PySpark, Scala, Kafka</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, Azure, Scala, Amazon QuickSight, CI/CD</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,59 +1476,59 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ebb387f8fd246816</t>
+          <t>https://www.indeed.com/viewjob?jk=8d1298ac76effc74</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer</t>
+          <t>C,C++, Python, Golang Developer</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Seek Now</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, Scala, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, SQL Server, PostgreSQL, CI/CD</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=86d6727803939178</t>
+          <t>https://www.indeed.com/viewjob?jk=441856af730024e8</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Database Engineer - onsite</t>
+          <t>Back-end Engineer - Data Platforms</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Eccalon</t>
+          <t>Morgan Stanley</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Detroit, MI, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Azure, BigQuery, Scala, Snowflake, Oracle, SQL Server, Data Modeling, Dimensional Modeling</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Spark, PySpark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,59 +1546,59 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e9489350e98d48c6</t>
+          <t>https://www.indeed.com/viewjob?jk=ebb387f8fd246816</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Analytics and Intelligence Engineer</t>
+          <t>Database Engineer - onsite</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Mars</t>
+          <t>Eccalon</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Detroit, MI, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Unity Catalog, Scala, Snowflake, Star Schema, dbt, Power BI</t>
+          <t>Redshift, RDS, Azure, BigQuery, Scala, Snowflake, Oracle, SQL Server, Data Modeling, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=94ca6d53f6fb57de</t>
+          <t>https://www.indeed.com/viewjob?jk=e9489350e98d48c6</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>SOW198 Platform Engineer</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>United Utility</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Spring, TX, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,34 +1606,34 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Spark, PySpark, Scala, Kafka, Cassandra, NoSQL</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, BigQuery, Cloud Storage, Scala, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6dbc4fb78c7362b3</t>
+          <t>https://www.indeed.com/viewjob?jk=2c848474306799be</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Software Engineer III - Generative AI Technology</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>United Utility</t>
+          <t>Wayfair</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Spring, TX, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,69 +1641,69 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, BigQuery, Cloud Storage, Scala, Snowflake, Data Modeling</t>
+          <t>AWS, Azure, GCP, BigQuery, Scala, PostgreSQL, MongoDB, MLflow, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2c848474306799be</t>
+          <t>https://www.indeed.com/viewjob?jk=dea1b605e8c5ec18</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Software Engineer III - Generative AI Technology</t>
+          <t>Data Engineer (Oracle Apps)</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Wayfair</t>
+          <t>Fidelity TalentSource</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Durham, NC, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, BigQuery, Scala, PostgreSQL, MongoDB, MLflow, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, Oracle, MongoDB, NoSQL, ETL</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dea1b605e8c5ec18</t>
+          <t>https://www.indeed.com/viewjob?jk=c788224995fc1529</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Product Software Engineer II</t>
+          <t>Senior Machine Learning Engineer (MLOPS)</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>The Coca-Cola Company</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, S3, ECS, Databricks, Spark, Scala, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, Medallion Architecture, GCP, Vertex AI, Scala, MLOps, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,24 +1721,24 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5fd9ded3cfb927d6</t>
+          <t>https://www.indeed.com/viewjob?jk=8551311899e9bc7c</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Integration Architect</t>
+          <t>Product Software Engineer II</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Penske Truck Leasing</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Reading, PA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,34 +1746,34 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, GCP, Scala, Kafka, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, EMR, Lambda, S3, ECS, Databricks, Spark, Scala, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bfceaaf0e0e2e9a5</t>
+          <t>https://www.indeed.com/viewjob?jk=5fd9ded3cfb927d6</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Full Stack Senior Software Engineer (Remote in CA)</t>
+          <t>Senior Software Engineer - LoopNet</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>FCT</t>
+          <t>CoStar Group</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Santa Ana, CA, US USA</t>
+          <t>Irvine, CA, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,34 +1781,34 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
+          <t>AWS, S3, SQS, Databricks, BigQuery, Scala, Kafka, Snowflake, MySQL, DynamoDB</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=70278c6707b92e9e</t>
+          <t>https://www.indeed.com/viewjob?jk=625a58dd59856504</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Full Stack Senior Software Engineer (Remote in CA)</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>FCT</t>
+          <t>Imperial Brady</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
+          <t>AWS, RDS, Azure, Databricks, Medallion Architecture, Spark, PySpark, Scala, Data Modeling, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,67 +1826,67 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a25e08cbc61c8f9c</t>
+          <t>https://www.indeed.com/viewjob?jk=49e6c0c32c4bdcc7</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Platform Engineer, Growth Product Engineering</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>WorkOS</t>
+          <t>Samsara</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>California City, CA, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, ECS, IAM, RDS, Scala, Snowflake, Data Modeling, ETL, dbt, CI/CD</t>
+          <t>AWS, Lambda, ECS, IAM, RDS, Databricks, CI/CD, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=93c58ad8f77c200b</t>
+          <t>https://www.indeed.com/viewjob?jk=6566d58d441eeee5</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Senior Cloud / AWS Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Imperial Brady</t>
+          <t>Reflex Media Inc</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Medallion Architecture, Spark, PySpark, Scala, Data Modeling, Dimensional Modeling</t>
+          <t>AWS, Lambda, Redshift, S3, ECS, IAM, RDS, PostgreSQL, MySQL, CI/CD</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,24 +1896,24 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=49e6c0c32c4bdcc7</t>
+          <t>https://www.indeed.com/viewjob?jk=901aac12afba9b93</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Senior Cloud / AWS Infrastructure Engineer</t>
+          <t>Specialist Solutions Architect - Cloud Infrastructure &amp; AWS Platform</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Reflex Media Inc</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,34 +1921,34 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, S3, ECS, IAM, RDS, PostgreSQL, MySQL, CI/CD</t>
+          <t>AWS, IAM, RDS, Azure, Databricks, Unity Catalog, Scala, Snowflake, Terraform, AWS CloudFormation</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=901aac12afba9b93</t>
+          <t>https://www.indeed.com/viewjob?jk=ac14888eb4824ae2</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Enterprise Architect - Data Platform</t>
+          <t>Data Platform Architect</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Johnson Controls</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Milwaukee, WI, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,7 +1956,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Spark, Scala, Kafka, Snowflake, Data Modeling</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, Unity Catalog, GCP, BigQuery, Spark, Scala</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,24 +1966,24 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d42707fbe5923515</t>
+          <t>https://www.indeed.com/viewjob?jk=d90b3504b0804f94</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Enterprise Architect - Data Platform</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Exostar</t>
+          <t>Johnson Controls</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Herndon, VA, US USA</t>
+          <t>Milwaukee, WI, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,7 +1991,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Scala, SQL Server, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Spark, Scala, Kafka, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,24 +2001,24 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ca5e90ebcac7315c</t>
+          <t>https://www.indeed.com/viewjob?jk=d42707fbe5923515</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Sr Implementation Consultant</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Cotiviti</t>
+          <t>Exostar</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Herndon, VA, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,34 +2026,34 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, Glue, ECS, RDS, Azure, Oracle, SQL Server, Data Modeling, ETL, Talend</t>
+          <t>AWS, S3, RDS, Azure, Scala, SQL Server, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=feec9157e828c7c5</t>
+          <t>https://www.indeed.com/viewjob?jk=ca5e90ebcac7315c</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Data Analyst - ERP &amp; Master Data</t>
+          <t>Sr Implementation Consultant</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>TransTech Group</t>
+          <t>Cotiviti</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2061,7 +2061,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Medallion Architecture, Dataflow, Spark, PySpark, Scala</t>
+          <t>AWS, Glue, ECS, RDS, Azure, Oracle, SQL Server, Data Modeling, ETL, Talend</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,7 +2071,7 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=49c2343d736f4c5c</t>
+          <t>https://www.indeed.com/viewjob?jk=feec9157e828c7c5</t>
         </is>
       </c>
     </row>
@@ -2113,17 +2113,17 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Software Development Engineer II</t>
+          <t>BI Engineer (Data Analyst)</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>GM Financial</t>
+          <t>Apply</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Arlington, TX, US USA</t>
+          <t>AR, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,17 +2131,17 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Azure, Scala, Oracle, SQL Server, NoSQL, Jenkins, Azure DevOps, Maven, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Scala, Snowflake, Data Modeling, dbt</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=77c13363e54e5087</t>
+          <t>https://www.indeed.com/viewjob?jk=7f4074f2837c770f</t>
         </is>
       </c>
     </row>
@@ -2183,17 +2183,17 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Forward Deployed Engineer, Client Solutions Group</t>
+          <t>Software Engineer - Remote</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>The Carlyle Group</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,34 +2201,34 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, API Gateway, ECS, RDS, Databricks, Scala, Snowflake</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Dask, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3cba42b7feabaab8</t>
+          <t>https://www.indeed.com/viewjob?jk=29fa962c43112ed2</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Full-Stack Engineer 4 (Java, Spring, DynamoDB, S3, GraphQL, GenAI)</t>
+          <t>Software Development Engineer II</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>GM Financial</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Arlington, TX, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,34 +2236,34 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, DynamoDB, NoSQL, CI/CD, Docker</t>
+          <t>Azure, Scala, Oracle, SQL Server, NoSQL, Jenkins, Azure DevOps, Maven, Terraform, Docker</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=30dd4b0534b4aca9</t>
+          <t>https://www.indeed.com/viewjob?jk=77c13363e54e5087</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Full-Stack Engineer 4 (Java, Spring, DynamoDB, S3, GraphQL, GenAL)</t>
+          <t>Data Analyst - ERP &amp; Master Data</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>TransTech Group</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,104 +2271,104 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, DynamoDB, NoSQL, CI/CD, Docker</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Medallion Architecture, Dataflow, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3e502713d51d0a40</t>
+          <t>https://www.indeed.com/viewjob?jk=49c2343d736f4c5c</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Sr Data Engineer II</t>
+          <t>Full-Stack Engineer 4 (Java, Spring, DynamoDB, S3, GraphQL, GenAI)</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>American Express</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, RDS, HBase, Spark, Scala, Kafka, Cassandra, NoSQL, MLOps, CI/CD</t>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, DynamoDB, NoSQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a9b4607cbdf4a3d4</t>
+          <t>https://www.indeed.com/viewjob?jk=30dd4b0534b4aca9</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Sr Software Engineer I</t>
+          <t>Full-Stack Engineer 4 (Java, Spring, DynamoDB, S3, GraphQL, GenAL)</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>RWE</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>RDS, Azure, ETL, CI/CD, Azure DevOps, Terraform, Kubernetes, AKS, Airflow, Apache Airflow</t>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, DynamoDB, NoSQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f6ad43066e853c35</t>
+          <t>https://www.indeed.com/viewjob?jk=3e502713d51d0a40</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>AI Data Engineer - University Students - QuantumBlack, AI by McKinsey</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Pika</t>
+          <t>McKinsey &amp; Company</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,17 +2376,17 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, Redshift, GCP, BigQuery, Scala, Kafka, Snowflake, Data Modeling, ETL</t>
+          <t>AWS, Azure, Databricks, GCP, BigQuery, Spark, Scala, Snowflake, dbt, MLOps</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=126cb889e15ed9cd</t>
+          <t>https://www.indeed.com/viewjob?jk=3c376f7a6c4f6eae</t>
         </is>
       </c>
     </row>
@@ -2398,12 +2398,12 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Hollstadt Consulting</t>
+          <t>Pika</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>MN, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,7 +2411,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>S3, IAM, RDS, Azure, Google Cloud Platform, GCP, Cloud Storage, Scala, CI/CD, Azure DevOps</t>
+          <t>AWS, Kinesis, Redshift, GCP, BigQuery, Scala, Kafka, Snowflake, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,7 +2421,7 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9488041a67901dc1</t>
+          <t>https://www.indeed.com/viewjob?jk=126cb889e15ed9cd</t>
         </is>
       </c>
     </row>
@@ -2433,12 +2433,12 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Community Choice Credit Union</t>
+          <t>Hollstadt Consulting</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Warren, MI, US USA</t>
+          <t>MN, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,34 +2446,34 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Scala, Snowflake, SQL Server, Data Modeling, ETL, ELT, Power BI</t>
+          <t>S3, IAM, RDS, Azure, Google Cloud Platform, GCP, Cloud Storage, Scala, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=21899fbf482a9cd2</t>
+          <t>https://www.indeed.com/viewjob?jk=9488041a67901dc1</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Sr Data Engineer II</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Community Choice Credit Union</t>
+          <t>American Express</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Jackson, MI, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,17 +2481,17 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Scala, Snowflake, SQL Server, Data Modeling, ETL, ELT, Power BI</t>
+          <t>AWS, RDS, HBase, Spark, Scala, Kafka, Cassandra, NoSQL, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9457f2c72938dbd5</t>
+          <t>https://www.indeed.com/viewjob?jk=a9b4607cbdf4a3d4</t>
         </is>
       </c>
     </row>
@@ -2508,7 +2508,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Holland, MI, US USA</t>
+          <t>Warren, MI, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2526,7 +2526,7 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6f79614628dc966f</t>
+          <t>https://www.indeed.com/viewjob?jk=21899fbf482a9cd2</t>
         </is>
       </c>
     </row>
@@ -2543,7 +2543,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Farmington Hills, MI, US USA</t>
+          <t>Jackson, MI, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2561,7 +2561,7 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fc4be70d8a478d8a</t>
+          <t>https://www.indeed.com/viewjob?jk=9457f2c72938dbd5</t>
         </is>
       </c>
     </row>
@@ -2578,7 +2578,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Jackson, MI, US USA</t>
+          <t>Holland, MI, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2596,24 +2596,24 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dad209d8bad2edfe</t>
+          <t>https://www.indeed.com/viewjob?jk=6f79614628dc966f</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>SBA Communications</t>
+          <t>Community Choice Credit Union</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Boca Raton, FL, US USA</t>
+          <t>Farmington Hills, MI, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2621,34 +2621,34 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Dataflow, Scala, Data Modeling, dbt, Power BI, CI/CD</t>
+          <t>RDS, Azure, Data Factory, Scala, Snowflake, SQL Server, Data Modeling, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=31b2e27b37e8f33d</t>
+          <t>https://www.indeed.com/viewjob?jk=fc4be70d8a478d8a</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Data Architect, Corporate Services</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>The Carlyle Group</t>
+          <t>Community Choice Credit Union</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Jackson, MI, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,34 +2656,34 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Snowflake, Data Modeling, Microsoft SSIS, dbt, Power BI, CI/CD</t>
+          <t>RDS, Azure, Data Factory, Scala, Snowflake, SQL Server, Data Modeling, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5c3007521d1e10c7</t>
+          <t>https://www.indeed.com/viewjob?jk=dad209d8bad2edfe</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Consultant, Data &amp; Analytics, NA</t>
+          <t>Senior DevOps Engineer</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>The Coca-Cola Company</t>
+          <t>ONTIC TECHNOLOGIES</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,34 +2691,34 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Scala, ETL, ELT, Power BI, Tableau, Git</t>
+          <t>AWS, IAM, RDS, GCP, Scala, Kafka, MongoDB, CI/CD, Jenkins, Terraform</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=df7e6baa7a7dd0a0</t>
+          <t>https://www.indeed.com/viewjob?jk=7300772b168034de</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Databricks Platform Engineer</t>
+          <t>Senior Backend Developer – Python</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Booz Allen Hamilton</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,17 +2726,17 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Unity Catalog, Scala, ELT, Splunk, DataOps, MLOps, CI/CD, GitHub Actions</t>
+          <t>AWS, Glue, S3, RDS, Scala, Oracle, SQL Server, PostgreSQL, DynamoDB, CI/CD</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6d89b1928ab17ec0</t>
+          <t>https://www.indeed.com/viewjob?jk=65b0c92c185362f0</t>
         </is>
       </c>
     </row>
@@ -2778,25 +2778,25 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Full-stack Engineer 5 (Nodejs/Go/Angularjs)</t>
+          <t>Consultant, Data &amp; Analytics, NA</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>The Coca-Cola Company</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
+          <t>AWS, RDS, Azure, Databricks, Scala, ETL, ELT, Power BI, Tableau, Git</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,24 +2806,24 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9813442a220867be</t>
+          <t>https://www.indeed.com/viewjob?jk=df7e6baa7a7dd0a0</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Full-stack Engineer 4 - RiskTech</t>
+          <t>Senior Software Engineer - Cloud Platform Engineering</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>MariaDB plc</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>VA, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,34 +2831,34 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
+          <t>AWS, RDS, Azure, GCP, Scala, MySQL, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f2960b2498873f28</t>
+          <t>https://www.indeed.com/viewjob?jk=e683398c349f7a6d</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Full-stack Engineer 4 (Golang, Python, Java, AWS)</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>AMD</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,7 +2866,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
+          <t>AWS, RDS, Azure, Databricks, Medallion Architecture, Spark, PySpark, Snowflake, dbt, Power BI</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2876,24 +2876,24 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=da278457dd975c3f</t>
+          <t>https://www.indeed.com/viewjob?jk=9724e994419d2473</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Full-stack Engineer 4</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>WellSky</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Overland Park, KS, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
+          <t>RDS, GCP, BigQuery, Scala, SQL Server, Data Modeling, ETL, ELT, dbt, Tableau</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2911,24 +2911,24 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=18716e78985d34c6</t>
+          <t>https://www.indeed.com/viewjob?jk=1d0888bf081a07cc</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Full-stack Engineer 4 (Go, AWS)</t>
+          <t>Data Engineer II - AWS/PySpark/ETL</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,7 +2936,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
+          <t>AWS, RDS, Databricks, Spark, PySpark, Scala, Snowflake, ETL, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2946,24 +2946,24 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6132bb0eb6aaf86d</t>
+          <t>https://www.indeed.com/viewjob?jk=aa1cc23a36ed4493</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Cloud Platform Engineering</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>MariaDB plc</t>
+          <t>Dropbox</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>VA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2971,34 +2971,34 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, MySQL, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>Kinesis, RDS, Databricks, Medallion Architecture, Spark, Scala, Kafka, Data Modeling, Airflow, Python</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e683398c349f7a6d</t>
+          <t>https://www.indeed.com/viewjob?jk=43e37e262d8bc84b</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Full-stack Engineer 5 (Nodejs/Go/Angularjs)</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>AMD</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3006,7 +3006,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Medallion Architecture, Spark, PySpark, Snowflake, dbt, Power BI</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3016,24 +3016,24 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9724e994419d2473</t>
+          <t>https://www.indeed.com/viewjob?jk=9813442a220867be</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Full-stack Engineer 4 - RiskTech</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>WellSky</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Overland Park, KS, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3041,7 +3041,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>RDS, GCP, BigQuery, Scala, SQL Server, Data Modeling, ETL, ELT, dbt, Tableau</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3051,24 +3051,24 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1d0888bf081a07cc</t>
+          <t>https://www.indeed.com/viewjob?jk=f2960b2498873f28</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Data Engineer II - AWS/PySpark/ETL</t>
+          <t>Full-stack Engineer 4 (Golang, Python, Java, AWS)</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3076,7 +3076,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Spark, PySpark, Scala, Snowflake, ETL, CI/CD, Airflow</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3086,24 +3086,24 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aa1cc23a36ed4493</t>
+          <t>https://www.indeed.com/viewjob?jk=da278457dd975c3f</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Full-stack Engineer 4</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Dropbox</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3111,7 +3111,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Kinesis, RDS, Databricks, Medallion Architecture, Spark, Scala, Kafka, Data Modeling, Airflow, Python</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3121,19 +3121,19 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=43e37e262d8bc84b</t>
+          <t>https://www.indeed.com/viewjob?jk=18716e78985d34c6</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Databricks Platform Engineer</t>
+          <t>Full-stack Engineer 4 (Go, AWS)</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Booz Allen Hamilton</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -3146,7 +3146,7 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Unity Catalog, Scala, ELT, Splunk, DataOps, MLOps, GitHub Actions, Terraform</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -3156,24 +3156,24 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d727a12d260ca4e6</t>
+          <t>https://www.indeed.com/viewjob?jk=6132bb0eb6aaf86d</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Backend Software Engineer</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>DriveTime Automotive Group</t>
+          <t>KorTerra</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Tempe, AZ, US USA</t>
+          <t>Chanhassen, MN, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3181,34 +3181,34 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>RDS, Scala, Kafka, Snowflake, SQL Server, Data Modeling, ETL, ELT, dbt, Python</t>
+          <t>RDS, Azure, Scala, PostgreSQL, NoSQL, CI/CD, Terraform, Docker, Kubernetes, AKS</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=05afa083475c5a6e</t>
+          <t>https://www.indeed.com/viewjob?jk=0fed605a20e912b9</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Senior Software Engineer (Data Platform)</t>
+          <t>Associate Solution Architect with Modernization Experience</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>MIA Labs</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3216,7 +3216,7 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, BigQuery, Scala, Snowflake, Data Modeling, Dimensional Modeling, ELT, dbt</t>
+          <t>AWS, Azure, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -3226,7 +3226,7 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f1a60bd31f33e718</t>
+          <t>https://www.indeed.com/viewjob?jk=c343a7d6432ffeaa</t>
         </is>
       </c>
     </row>
@@ -3243,7 +3243,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Tempe, AZ, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3261,7 +3261,7 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c343a7d6432ffeaa</t>
+          <t>https://www.indeed.com/viewjob?jk=e60054b9631d7895</t>
         </is>
       </c>
     </row>
@@ -3278,7 +3278,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Tempe, AZ, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3296,7 +3296,7 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e60054b9631d7895</t>
+          <t>https://www.indeed.com/viewjob?jk=99aade9079199e44</t>
         </is>
       </c>
     </row>
@@ -3313,7 +3313,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Las Vegas, NV, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3331,7 +3331,7 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=99aade9079199e44</t>
+          <t>https://www.indeed.com/viewjob?jk=fb5a4840f3df3c6d</t>
         </is>
       </c>
     </row>
@@ -3348,7 +3348,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Las Vegas, NV, US USA</t>
+          <t>Morristown, NJ, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3366,7 +3366,7 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fb5a4840f3df3c6d</t>
+          <t>https://www.indeed.com/viewjob?jk=55abd889581cdc48</t>
         </is>
       </c>
     </row>
@@ -3383,7 +3383,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Morristown, NJ, US USA</t>
+          <t>Detroit, MI, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3401,7 +3401,7 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=55abd889581cdc48</t>
+          <t>https://www.indeed.com/viewjob?jk=e3febde783536e21</t>
         </is>
       </c>
     </row>
@@ -3418,7 +3418,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Detroit, MI, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3436,7 +3436,7 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e3febde783536e21</t>
+          <t>https://www.indeed.com/viewjob?jk=1be19f91eec7a842</t>
         </is>
       </c>
     </row>
@@ -3453,7 +3453,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3471,7 +3471,7 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1be19f91eec7a842</t>
+          <t>https://www.indeed.com/viewjob?jk=7698c96689f48a9e</t>
         </is>
       </c>
     </row>
@@ -3488,7 +3488,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3506,7 +3506,7 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7698c96689f48a9e</t>
+          <t>https://www.indeed.com/viewjob?jk=d2e1386f9d607f38</t>
         </is>
       </c>
     </row>
@@ -3523,7 +3523,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3541,7 +3541,7 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d2e1386f9d607f38</t>
+          <t>https://www.indeed.com/viewjob?jk=2f2ca862816ed069</t>
         </is>
       </c>
     </row>
@@ -3558,7 +3558,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3576,7 +3576,7 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2f2ca862816ed069</t>
+          <t>https://www.indeed.com/viewjob?jk=a40909cafc968d82</t>
         </is>
       </c>
     </row>
@@ -3593,7 +3593,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -3611,7 +3611,7 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a40909cafc968d82</t>
+          <t>https://www.indeed.com/viewjob?jk=124344ebd08b7526</t>
         </is>
       </c>
     </row>
@@ -3628,7 +3628,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -3646,7 +3646,7 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=124344ebd08b7526</t>
+          <t>https://www.indeed.com/viewjob?jk=f0ef6c1eb38b0db9</t>
         </is>
       </c>
     </row>
@@ -3663,7 +3663,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
@@ -3681,7 +3681,7 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f0ef6c1eb38b0db9</t>
+          <t>https://www.indeed.com/viewjob?jk=b780dcc242beb567</t>
         </is>
       </c>
     </row>
@@ -3698,7 +3698,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
@@ -3716,7 +3716,7 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b780dcc242beb567</t>
+          <t>https://www.indeed.com/viewjob?jk=a03180188c81f9bf</t>
         </is>
       </c>
     </row>
@@ -3733,7 +3733,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
@@ -3751,7 +3751,7 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a03180188c81f9bf</t>
+          <t>https://www.indeed.com/viewjob?jk=8a037168850b8fe0</t>
         </is>
       </c>
     </row>
@@ -3768,7 +3768,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
@@ -3786,7 +3786,7 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8a037168850b8fe0</t>
+          <t>https://www.indeed.com/viewjob?jk=45cd4b8d959d97ab</t>
         </is>
       </c>
     </row>
@@ -3803,7 +3803,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
@@ -3821,7 +3821,7 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=45cd4b8d959d97ab</t>
+          <t>https://www.indeed.com/viewjob?jk=52080037fabe4cb1</t>
         </is>
       </c>
     </row>
@@ -3838,7 +3838,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
@@ -3856,7 +3856,7 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=52080037fabe4cb1</t>
+          <t>https://www.indeed.com/viewjob?jk=69224b4d176dd4a2</t>
         </is>
       </c>
     </row>
@@ -3873,7 +3873,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Kansas City, MO, US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
@@ -3891,7 +3891,7 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=69224b4d176dd4a2</t>
+          <t>https://www.indeed.com/viewjob?jk=5ce9dba6d19c8b82</t>
         </is>
       </c>
     </row>
@@ -3908,7 +3908,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Kansas City, MO, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D100" t="n">
@@ -3926,7 +3926,7 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5ce9dba6d19c8b82</t>
+          <t>https://www.indeed.com/viewjob?jk=7c5344293aa5ed77</t>
         </is>
       </c>
     </row>
@@ -3943,7 +3943,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D101" t="n">
@@ -3961,7 +3961,7 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7c5344293aa5ed77</t>
+          <t>https://www.indeed.com/viewjob?jk=fea3b3cc46faeb2a</t>
         </is>
       </c>
     </row>
@@ -3978,7 +3978,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D102" t="n">
@@ -3996,7 +3996,7 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fea3b3cc46faeb2a</t>
+          <t>https://www.indeed.com/viewjob?jk=c3672ad48951be20</t>
         </is>
       </c>
     </row>
@@ -4013,7 +4013,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D103" t="n">
@@ -4031,7 +4031,7 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c3672ad48951be20</t>
+          <t>https://www.indeed.com/viewjob?jk=c45dff0f36a9a356</t>
         </is>
       </c>
     </row>
@@ -4048,7 +4048,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D104" t="n">
@@ -4066,7 +4066,7 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c45dff0f36a9a356</t>
+          <t>https://www.indeed.com/viewjob?jk=7e91b7a712b7a165</t>
         </is>
       </c>
     </row>
@@ -4083,7 +4083,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D105" t="n">
@@ -4101,7 +4101,7 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7e91b7a712b7a165</t>
+          <t>https://www.indeed.com/viewjob?jk=f3d69f9412407b80</t>
         </is>
       </c>
     </row>
@@ -4118,7 +4118,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D106" t="n">
@@ -4136,7 +4136,7 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f3d69f9412407b80</t>
+          <t>https://www.indeed.com/viewjob?jk=7d48fbbfaa3d0a97</t>
         </is>
       </c>
     </row>
@@ -4153,7 +4153,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Stamford, CT, US USA</t>
         </is>
       </c>
       <c r="D107" t="n">
@@ -4171,7 +4171,7 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7d48fbbfaa3d0a97</t>
+          <t>https://www.indeed.com/viewjob?jk=c300f1e448116fd7</t>
         </is>
       </c>
     </row>
@@ -4188,7 +4188,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Stamford, CT, US USA</t>
+          <t>Sacramento, CA, US USA</t>
         </is>
       </c>
       <c r="D108" t="n">
@@ -4206,7 +4206,7 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c300f1e448116fd7</t>
+          <t>https://www.indeed.com/viewjob?jk=316adbd72ad7e2e8</t>
         </is>
       </c>
     </row>
@@ -4223,7 +4223,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Sacramento, CA, US USA</t>
+          <t>Costa Mesa, CA, US USA</t>
         </is>
       </c>
       <c r="D109" t="n">
@@ -4241,7 +4241,7 @@
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=316adbd72ad7e2e8</t>
+          <t>https://www.indeed.com/viewjob?jk=f219232c6b6eef2b</t>
         </is>
       </c>
     </row>
@@ -4258,7 +4258,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Costa Mesa, CA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D110" t="n">
@@ -4276,7 +4276,7 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f219232c6b6eef2b</t>
+          <t>https://www.indeed.com/viewjob?jk=0bb31aa937d723cd</t>
         </is>
       </c>
     </row>
@@ -4293,7 +4293,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D111" t="n">
@@ -4311,7 +4311,7 @@
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0bb31aa937d723cd</t>
+          <t>https://www.indeed.com/viewjob?jk=884c614c785d6835</t>
         </is>
       </c>
     </row>
@@ -4328,7 +4328,7 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D112" t="n">
@@ -4346,7 +4346,7 @@
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=884c614c785d6835</t>
+          <t>https://www.indeed.com/viewjob?jk=ecedaabbce0a0b5b</t>
         </is>
       </c>
     </row>
@@ -4363,7 +4363,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D113" t="n">
@@ -4381,7 +4381,7 @@
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ecedaabbce0a0b5b</t>
+          <t>https://www.indeed.com/viewjob?jk=eea12c90a4a047af</t>
         </is>
       </c>
     </row>
@@ -4398,7 +4398,7 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D114" t="n">
@@ -4416,7 +4416,7 @@
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eea12c90a4a047af</t>
+          <t>https://www.indeed.com/viewjob?jk=28b6e9e7e6b5c6aa</t>
         </is>
       </c>
     </row>
@@ -4433,7 +4433,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D115" t="n">
@@ -4451,7 +4451,7 @@
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=28b6e9e7e6b5c6aa</t>
+          <t>https://www.indeed.com/viewjob?jk=2c0e09d9843111bd</t>
         </is>
       </c>
     </row>
@@ -4468,7 +4468,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D116" t="n">
@@ -4486,24 +4486,24 @@
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2c0e09d9843111bd</t>
+          <t>https://www.indeed.com/viewjob?jk=3b10af7d10426fa4</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>Associate Solution Architect with Modernization Experience</t>
+          <t>Sr Technical Analyst/Prog Ent App</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Avangrid</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Orange, CT, US USA</t>
         </is>
       </c>
       <c r="D117" t="n">
@@ -4511,7 +4511,7 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, ETL, Azure DevOps, Git</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
@@ -4521,24 +4521,24 @@
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3b10af7d10426fa4</t>
+          <t>https://www.indeed.com/viewjob?jk=4ea1b275b8152311</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>Solution Architect-Full Stack</t>
+          <t>Full Stack Ad Tech Developer</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Kirby Building Systems</t>
+          <t>The Hearst Corporation</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Portland, TN, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D118" t="n">
@@ -4546,7 +4546,7 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, SQL Server, PostgreSQL, CI/CD, Azure DevOps, Terraform, Docker, Kubernetes</t>
+          <t>AWS, Redshift, Google Cloud Platform, BigQuery, Scala, ETL, Tableau, CI/CD, Git, Python</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
@@ -4556,24 +4556,24 @@
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=66ada823af164848</t>
+          <t>https://www.indeed.com/viewjob?jk=e8cf1f61c24a8358</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>C# Full Stack Developer</t>
+          <t>Full-stack Engineer 4 (IC)</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Globant</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D119" t="n">
@@ -4581,34 +4581,34 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Scala, SQL Server, PostgreSQL, MySQL, CI/CD, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d96c65fe6b68f304</t>
+          <t>https://www.indeed.com/viewjob?jk=4620494dca257198</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>Sr Technical Analyst/Prog Ent App</t>
+          <t>Full-stack Engineer 4 (IC)</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Avangrid</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Orange, CT, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D120" t="n">
@@ -4616,34 +4616,34 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, ETL, Azure DevOps, Git</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4ea1b275b8152311</t>
+          <t>https://www.indeed.com/viewjob?jk=6b1bed8feba6b917</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>Full Stack Ad Tech Developer</t>
+          <t>Full-stack Engineer 4</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>The Hearst Corporation</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D121" t="n">
@@ -4651,34 +4651,34 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Google Cloud Platform, BigQuery, Scala, ETL, Tableau, CI/CD, Git, Python</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e8cf1f61c24a8358</t>
+          <t>https://www.indeed.com/viewjob?jk=8e194fdfb9b8dbe3</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>Forward Deployed AI Engineer 2026 - US, COL, UK</t>
+          <t>Full-Stack Engineer 4 (Python, AWS, Network Automation)</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Aimpoint Digital</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D122" t="n">
@@ -4686,34 +4686,34 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, Scala, Snowflake, ETL, ELT, MLOps, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=64c74cca4e3efa95</t>
+          <t>https://www.indeed.com/viewjob?jk=a77780c738e44a57</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Full-stack Engineer 5 (Go, TypeScript and Angular)</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Activated Insights</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D123" t="n">
@@ -4721,7 +4721,7 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>AWS, EMR, S3, RDS, Scala, Snowflake, PostgreSQL, MySQL, ETL, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
@@ -4731,24 +4731,24 @@
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4c98c8e05297ceda</t>
+          <t>https://www.indeed.com/viewjob?jk=81ff3ef325447a98</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Full-stack Engineer 4</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Activated Insights</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Idaho Falls, ID, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D124" t="n">
@@ -4756,7 +4756,7 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>AWS, EMR, S3, RDS, Scala, Snowflake, PostgreSQL, MySQL, ETL, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
@@ -4766,14 +4766,14 @@
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7382a9e2385f01a9</t>
+          <t>https://www.indeed.com/viewjob?jk=70843ae9e366dd5b</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>Full-stack Engineer 4 (IC)</t>
+          <t>Full - Stack Engineer 5 (Remote - Eligible)</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -4783,7 +4783,7 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D125" t="n">
@@ -4796,19 +4796,19 @@
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4620494dca257198</t>
+          <t>https://www.indeed.com/viewjob?jk=877ad6c20024fb1a</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>Full-stack Engineer 4 (IC)</t>
+          <t>Full-stack Engineer 4</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -4818,7 +4818,7 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D126" t="n">
@@ -4831,19 +4831,19 @@
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6b1bed8feba6b917</t>
+          <t>https://www.indeed.com/viewjob?jk=6979868bb95d63f0</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>Full-stack Engineer 4</t>
+          <t>Full Stack Engineer 5</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -4866,19 +4866,19 @@
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8e194fdfb9b8dbe3</t>
+          <t>https://www.indeed.com/viewjob?jk=b743b91aec079a75</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>Full-Stack Engineer 4 (Python, AWS, Network Automation)</t>
+          <t>Full Stack Engineer 4</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -4901,19 +4901,19 @@
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a77780c738e44a57</t>
+          <t>https://www.indeed.com/viewjob?jk=3fb66ff5f4ef065f</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>Full-stack Engineer 5 (Go, TypeScript and Angular)</t>
+          <t>Full-stack Engineer 4 (Python, Java)</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -4923,7 +4923,7 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D129" t="n">
@@ -4941,14 +4941,14 @@
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=81ff3ef325447a98</t>
+          <t>https://www.indeed.com/viewjob?jk=c9046de91e154d69</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>Full-stack Engineer 4</t>
+          <t>Full-stack Engineer 5 ( Python, AWS)</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -4976,14 +4976,14 @@
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=70843ae9e366dd5b</t>
+          <t>https://www.indeed.com/viewjob?jk=5e4de127a7227d81</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>Full - Stack Engineer 5 (Remote - Eligible)</t>
+          <t>Full-stack Engineer 5 (Golang, Java, AWS)</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -4993,7 +4993,7 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D131" t="n">
@@ -5011,14 +5011,14 @@
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=877ad6c20024fb1a</t>
+          <t>https://www.indeed.com/viewjob?jk=f3a9ee8f682a9c78</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>Full-stack Engineer 4</t>
+          <t>Full-stack Engineer 4 - Intelligent Foundations and Experiences (IFX)</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -5028,7 +5028,7 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D132" t="n">
@@ -5046,14 +5046,14 @@
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6979868bb95d63f0</t>
+          <t>https://www.indeed.com/viewjob?jk=6faf5ca1640fcd31</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>Full Stack Engineer 5</t>
+          <t>Full-stack Engineer 4 - Intelligent Foundations and Experiences (IFX)</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -5063,7 +5063,7 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D133" t="n">
@@ -5081,14 +5081,14 @@
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b743b91aec079a75</t>
+          <t>https://www.indeed.com/viewjob?jk=42133a298638cb9b</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>Full Stack Engineer 4</t>
+          <t>Full-stack Engineer 5</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -5116,14 +5116,14 @@
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3fb66ff5f4ef065f</t>
+          <t>https://www.indeed.com/viewjob?jk=a708182f9a1da64d</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>Full-stack Engineer 4 (Python, Java)</t>
+          <t>Full-stack Engineer 4 - Intelligent Foundations and Experiences (IFX)</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -5133,7 +5133,7 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D135" t="n">
@@ -5151,14 +5151,14 @@
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c9046de91e154d69</t>
+          <t>https://www.indeed.com/viewjob?jk=76c8a5b4fcc58505</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>Full-stack Engineer 5 ( Python, AWS)</t>
+          <t>Full-stack Engineer 5 - Shopping (Remote-Eligible)</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -5186,14 +5186,14 @@
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5e4de127a7227d81</t>
+          <t>https://www.indeed.com/viewjob?jk=419688dc0cbfaf98</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>Full-stack Engineer 5 (Golang, Java, AWS)</t>
+          <t>Full-stack Engineer 5 (Java, Scala, AWS)</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -5203,7 +5203,7 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D137" t="n">
@@ -5221,14 +5221,14 @@
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f3a9ee8f682a9c78</t>
+          <t>https://www.indeed.com/viewjob?jk=c997daa05db4e0c7</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>Full-stack Engineer 4 - Intelligent Foundations and Experiences (IFX)</t>
+          <t>Full Stack Engineer 4 (Go, AWS)</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -5256,14 +5256,14 @@
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6faf5ca1640fcd31</t>
+          <t>https://www.indeed.com/viewjob?jk=6a9874c783fb4a03</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>Full-stack Engineer 4 - Intelligent Foundations and Experiences (IFX)</t>
+          <t>Full-stack Engineer 4</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -5273,7 +5273,7 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D139" t="n">
@@ -5291,14 +5291,14 @@
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=42133a298638cb9b</t>
+          <t>https://www.indeed.com/viewjob?jk=1f96da918db85a2a</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>Full-stack Engineer 5</t>
+          <t>Full-stack Engineer 4 (Java, Scala, AWS)</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -5308,7 +5308,7 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D140" t="n">
@@ -5326,14 +5326,14 @@
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a708182f9a1da64d</t>
+          <t>https://www.indeed.com/viewjob?jk=b9e0187cbe4c2e40</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>Full-stack Engineer 4 - Intelligent Foundations and Experiences (IFX)</t>
+          <t>Full-stack Engineer 4</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -5343,7 +5343,7 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D141" t="n">
@@ -5361,14 +5361,14 @@
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=76c8a5b4fcc58505</t>
+          <t>https://www.indeed.com/viewjob?jk=900df92ddc778d5f</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>Full-stack Engineer 5 - Shopping (Remote-Eligible)</t>
+          <t>Full-stack Engineer 4 (JavaScript, React)</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -5378,7 +5378,7 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D142" t="n">
@@ -5396,14 +5396,14 @@
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=419688dc0cbfaf98</t>
+          <t>https://www.indeed.com/viewjob?jk=e7c346fa6453ffb9</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>Full-stack Engineer 5 (Java, Scala, AWS)</t>
+          <t>Full-stack Engineer 5 (Go/Java, Angular, AWS)</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -5413,7 +5413,7 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D143" t="n">
@@ -5431,14 +5431,14 @@
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c997daa05db4e0c7</t>
+          <t>https://www.indeed.com/viewjob?jk=c039bc465260bc95</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>Full Stack Engineer 4 (Go, AWS)</t>
+          <t>Full-stack Engineer 4</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -5448,7 +5448,7 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D144" t="n">
@@ -5466,7 +5466,7 @@
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6a9874c783fb4a03</t>
+          <t>https://www.indeed.com/viewjob?jk=54e236865193f8a0</t>
         </is>
       </c>
     </row>
@@ -5501,14 +5501,14 @@
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1f96da918db85a2a</t>
+          <t>https://www.indeed.com/viewjob?jk=b667ebd325202576</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>Full-stack Engineer 4 (Java, Scala, AWS)</t>
+          <t>Full-stack Engineer 5 (Golang, AWS)</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -5518,7 +5518,7 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D146" t="n">
@@ -5536,14 +5536,14 @@
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b9e0187cbe4c2e40</t>
+          <t>https://www.indeed.com/viewjob?jk=672e371e8fd60859</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>Full-stack Engineer 4</t>
+          <t>Full-stack Engineer 4 (React, TypeScript, AWS)</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -5571,14 +5571,14 @@
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=900df92ddc778d5f</t>
+          <t>https://www.indeed.com/viewjob?jk=346a7f081a67b46c</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>Full-stack Engineer 4 (JavaScript, React)</t>
+          <t>Full-stack Engineer 4</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -5588,7 +5588,7 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D148" t="n">
@@ -5606,14 +5606,14 @@
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e7c346fa6453ffb9</t>
+          <t>https://www.indeed.com/viewjob?jk=7b21934bf2433e6a</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>Full-stack Engineer 5 (Go/Java, Angular, AWS)</t>
+          <t>Full-stack Engineer 4 (Scala, React, AWS)</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -5623,7 +5623,7 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D149" t="n">
@@ -5641,14 +5641,14 @@
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c039bc465260bc95</t>
+          <t>https://www.indeed.com/viewjob?jk=2af3b2e528eb8c47</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>Full-stack Engineer 4</t>
+          <t>Full-stack Engineer 4 (Scala, React, AWS)</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -5658,7 +5658,7 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D150" t="n">
@@ -5676,7 +5676,7 @@
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=54e236865193f8a0</t>
+          <t>https://www.indeed.com/viewjob?jk=51fd20841ca9c754</t>
         </is>
       </c>
     </row>
@@ -5711,14 +5711,14 @@
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b667ebd325202576</t>
+          <t>https://www.indeed.com/viewjob?jk=619531dae358928f</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>Full-stack Engineer 5 (Golang, AWS)</t>
+          <t>Full-stack Engineer 4 (Python, AWS)</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -5746,14 +5746,14 @@
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=672e371e8fd60859</t>
+          <t>https://www.indeed.com/viewjob?jk=8e4eaf7eaa027bbb</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>Full-stack Engineer 4 (React, TypeScript, AWS)</t>
+          <t>Full-stack Engineer 4 (GoLang)</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -5763,7 +5763,7 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D153" t="n">
@@ -5781,14 +5781,14 @@
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=346a7f081a67b46c</t>
+          <t>https://www.indeed.com/viewjob?jk=b7c24e0e87f3fc42</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>Full-stack Engineer 4</t>
+          <t>Full-Stack Engineer 4 (Automation Quality Engineer)</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -5798,7 +5798,7 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Riverwoods, IL, US USA</t>
         </is>
       </c>
       <c r="D154" t="n">
@@ -5816,14 +5816,14 @@
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7b21934bf2433e6a</t>
+          <t>https://www.indeed.com/viewjob?jk=2acd23b24043f205</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>Full-stack Engineer 4 (Scala, React, AWS)</t>
+          <t>Full-stack Engineer 4 - Shopping (Remote-Eligible)</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -5833,7 +5833,7 @@
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D155" t="n">
@@ -5851,32 +5851,32 @@
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2af3b2e528eb8c47</t>
+          <t>https://www.indeed.com/viewjob?jk=f87b328e958cbb63</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>Full-stack Engineer 4 (Scala, React, AWS)</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>KeHE Distributors</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Naperville, IL, US USA</t>
         </is>
       </c>
       <c r="D156" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, Data Modeling, Power BI, Tableau, MLOps</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
@@ -5886,32 +5886,32 @@
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=51fd20841ca9c754</t>
+          <t>https://www.indeed.com/viewjob?jk=9033c8036c6af9b3</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>Full-stack Engineer 4</t>
+          <t>Data Platform Engineer</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>Hubble Network</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D157" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
+          <t>Kinesis, Redshift, RDS, Scala, Kafka, Dimensional Modeling, Star Schema, Fact Tables, ETL, dbt</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
@@ -5921,49 +5921,49 @@
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=619531dae358928f</t>
+          <t>https://www.indeed.com/viewjob?jk=a000c1d1d33d8b12</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>Full-stack Engineer 4 (Python, AWS)</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>Lockheed Martin</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D158" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
+          <t>AWS, RDS, Azure, Databricks, Oracle, SQL Server, MySQL, ETL, Tableau, CI/CD</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8e4eaf7eaa027bbb</t>
+          <t>https://www.indeed.com/viewjob?jk=70671fedd9bf2e0b</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>Full-stack Engineer 4 (GoLang)</t>
+          <t>Integration Engineer 4</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -5973,15 +5973,15 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D159" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
+          <t>AWS, Lambda, Step Functions, RDS, Azure, GCP, Scala, Splunk, Jenkins, Jenkins</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
@@ -5991,94 +5991,94 @@
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b7c24e0e87f3fc42</t>
+          <t>https://www.indeed.com/viewjob?jk=52d873bb7fc420f0</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>Full-Stack Engineer 4 (Automation Quality Engineer)</t>
+          <t>Specialist Solutions Architect - Cloud Infrastructure &amp; Azure Platform</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Riverwoods, IL, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D160" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Scala, Snowflake, Terraform, Azure Monitor, Python</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2acd23b24043f205</t>
+          <t>https://www.indeed.com/viewjob?jk=24b4e0a029b86ac2</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>Full-stack Engineer 4 - Shopping (Remote-Eligible)</t>
+          <t>Senior Full Stack Software Engineer (Java)</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D161" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
+          <t>AWS, Azure, GCP, Kafka, Oracle, SQL Server, PostgreSQL, MySQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f87b328e958cbb63</t>
+          <t>https://www.indeed.com/viewjob?jk=e58be4fcea83450d</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>Integration Engineer 4</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>Mastercard</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>O'Fallon, MO, US USA</t>
         </is>
       </c>
       <c r="D162" t="n">
@@ -6086,7 +6086,7 @@
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, RDS, Azure, GCP, Scala, Splunk, Jenkins, Jenkins</t>
+          <t>AWS, API Gateway, RDS, Scala, Oracle, PostgreSQL, CI/CD, Jenkins, GitHub Actions, Jenkins</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
@@ -6096,24 +6096,24 @@
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=52d873bb7fc420f0</t>
+          <t>https://www.indeed.com/viewjob?jk=0245dcafa3f48258</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>Junior/Mid Software Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Function Health</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D163" t="n">
@@ -6121,34 +6121,34 @@
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, GCP, Hadoop, Spark, Scala, Kafka, NoSQL, Kubernetes</t>
+          <t>RDS, Databricks, BigQuery, Spark, Kafka, Snowflake, ELT, dbt, MLOps, Terraform</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d87ecb6d60b0f54d</t>
+          <t>https://www.indeed.com/viewjob?jk=8d332f2047edfa45</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Azure Data Engineer</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>KeHE Distributors</t>
+          <t>Orion Innovation</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Naperville, IL, US USA</t>
+          <t>Montvale, NJ, US USA</t>
         </is>
       </c>
       <c r="D164" t="n">
@@ -6156,34 +6156,34 @@
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, Data Modeling, Power BI, Tableau, MLOps</t>
+          <t>Azure, Data Factory, Databricks, Spark, PySpark, Scala, ETL, ELT, Power BI, AKS</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9033c8036c6af9b3</t>
+          <t>https://www.indeed.com/viewjob?jk=334e0bc8c90d3013</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>Data Platform Engineer</t>
+          <t>Backend Software Engineer</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>Hubble Network</t>
+          <t>KorTerra</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Chanhassen, MN, US USA</t>
         </is>
       </c>
       <c r="D165" t="n">
@@ -6191,262 +6191,17 @@
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>Kinesis, Redshift, RDS, Scala, Kafka, Dimensional Modeling, Star Schema, Fact Tables, ETL, dbt</t>
+          <t>Azure, Scala, PostgreSQL, NoSQL, CI/CD, Terraform, Docker, Kubernetes, AKS, Git</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a000c1d1d33d8b12</t>
-        </is>
-      </c>
-    </row>
-    <row r="166">
-      <c r="A166" t="inlineStr">
-        <is>
-          <t>Data &amp; AI Engineer</t>
-        </is>
-      </c>
-      <c r="B166" t="inlineStr">
-        <is>
-          <t>The Carlyle Group</t>
-        </is>
-      </c>
-      <c r="C166" t="inlineStr">
-        <is>
-          <t>Washington, DC, US USA</t>
-        </is>
-      </c>
-      <c r="D166" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E166" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Databricks, Spark, Scala, Snowflake, ELT, dbt, MLflow, CI/CD</t>
-        </is>
-      </c>
-      <c r="F166" t="inlineStr">
-        <is>
-          <t>2026-08-23</t>
-        </is>
-      </c>
-      <c r="G166" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=83876c66e135b993</t>
-        </is>
-      </c>
-    </row>
-    <row r="167">
-      <c r="A167" t="inlineStr">
-        <is>
-          <t>Data &amp; AI Engineer</t>
-        </is>
-      </c>
-      <c r="B167" t="inlineStr">
-        <is>
-          <t>The Carlyle Group</t>
-        </is>
-      </c>
-      <c r="C167" t="inlineStr">
-        <is>
-          <t>New York, NY, US USA</t>
-        </is>
-      </c>
-      <c r="D167" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E167" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Databricks, Spark, Scala, Snowflake, ELT, dbt, MLflow, CI/CD</t>
-        </is>
-      </c>
-      <c r="F167" t="inlineStr">
-        <is>
-          <t>2026-08-23</t>
-        </is>
-      </c>
-      <c r="G167" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=f4924b3389452957</t>
-        </is>
-      </c>
-    </row>
-    <row r="168">
-      <c r="A168" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer</t>
-        </is>
-      </c>
-      <c r="B168" t="inlineStr">
-        <is>
-          <t>Mastercard</t>
-        </is>
-      </c>
-      <c r="C168" t="inlineStr">
-        <is>
-          <t>O'Fallon, MO, US USA</t>
-        </is>
-      </c>
-      <c r="D168" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E168" t="inlineStr">
-        <is>
-          <t>AWS, API Gateway, RDS, Scala, Oracle, PostgreSQL, CI/CD, Jenkins, GitHub Actions, Jenkins</t>
-        </is>
-      </c>
-      <c r="F168" t="inlineStr">
-        <is>
-          <t>2026-09-22</t>
-        </is>
-      </c>
-      <c r="G168" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=0245dcafa3f48258</t>
-        </is>
-      </c>
-    </row>
-    <row r="169">
-      <c r="A169" t="inlineStr">
-        <is>
-          <t>Healthcare Interoperability Engineer</t>
-        </is>
-      </c>
-      <c r="B169" t="inlineStr">
-        <is>
-          <t>MedQuest Imaging</t>
-        </is>
-      </c>
-      <c r="C169" t="inlineStr">
-        <is>
-          <t>Alpharetta, GA, US USA</t>
-        </is>
-      </c>
-      <c r="D169" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E169" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, CI/CD, Azure DevOps, Terraform, Git</t>
-        </is>
-      </c>
-      <c r="F169" t="inlineStr">
-        <is>
-          <t>2026-09-23</t>
-        </is>
-      </c>
-      <c r="G169" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=eeb961148c207be2</t>
-        </is>
-      </c>
-    </row>
-    <row r="170">
-      <c r="A170" t="inlineStr">
-        <is>
-          <t>Data Scientist IV</t>
-        </is>
-      </c>
-      <c r="B170" t="inlineStr">
-        <is>
-          <t>CareSource</t>
-        </is>
-      </c>
-      <c r="C170" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D170" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E170" t="inlineStr">
-        <is>
-          <t>AWS, EMR, RDS, Azure, Databricks, GCP, Scala, Snowflake, Data Modeling, MLOps</t>
-        </is>
-      </c>
-      <c r="F170" t="inlineStr">
-        <is>
-          <t>2026-09-23</t>
-        </is>
-      </c>
-      <c r="G170" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=f79ced955268a69b</t>
-        </is>
-      </c>
-    </row>
-    <row r="171">
-      <c r="A171" t="inlineStr">
-        <is>
-          <t>Data Engineer</t>
-        </is>
-      </c>
-      <c r="B171" t="inlineStr">
-        <is>
-          <t>Function Health</t>
-        </is>
-      </c>
-      <c r="C171" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D171" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E171" t="inlineStr">
-        <is>
-          <t>RDS, Databricks, BigQuery, Spark, Kafka, Snowflake, ELT, dbt, MLOps, Terraform</t>
-        </is>
-      </c>
-      <c r="F171" t="inlineStr">
-        <is>
-          <t>2026-09-22</t>
-        </is>
-      </c>
-      <c r="G171" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=8d332f2047edfa45</t>
-        </is>
-      </c>
-    </row>
-    <row r="172">
-      <c r="A172" t="inlineStr">
-        <is>
-          <t>Engineer, Performance Management</t>
-        </is>
-      </c>
-      <c r="B172" t="inlineStr">
-        <is>
-          <t>The Carlyle Group</t>
-        </is>
-      </c>
-      <c r="C172" t="inlineStr">
-        <is>
-          <t>Washington, DC, US USA</t>
-        </is>
-      </c>
-      <c r="D172" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E172" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, SQL Server, ETL, Power BI, CI/CD, Git</t>
-        </is>
-      </c>
-      <c r="F172" t="inlineStr">
-        <is>
-          <t>2026-09-15</t>
-        </is>
-      </c>
-      <c r="G172" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=9e0346f80c455f7d</t>
+          <t>https://www.indeed.com/viewjob?jk=62838a48fa61a004</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-09-23.xlsx
+++ b/results/job_matches_2026-09-23.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G165"/>
+  <dimension ref="A1:G108"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -853,25 +853,25 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Senior AI Ops / DevOps Engineer</t>
+          <t>Data Engineer 5 - Enterprise Risk Management</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>16.7</v>
+        <v>16</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Splunk, MLOps, MLflow, CI/CD, Jenkins</t>
+          <t>AWS, Glue, EMR, Redshift, RDS, Azure, Databricks, Spark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,14 +881,14 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=040c156b15abd039</t>
+          <t>https://www.indeed.com/viewjob?jk=a45f08af4f7be5f6</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Data Engineer 5 - Enterprise Risk Management</t>
+          <t>Data Engineer 4 - Nexus Products</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -916,14 +916,14 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a45f08af4f7be5f6</t>
+          <t>https://www.indeed.com/viewjob?jk=36fc31dc37d05722</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Data Engineer 4 - Nexus Products</t>
+          <t>Data Engineer 4 - Payment Networks</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -951,14 +951,14 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=36fc31dc37d05722</t>
+          <t>https://www.indeed.com/viewjob?jk=f8d0c3f139798fd9</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Data Engineer 4 - Payment Networks</t>
+          <t>Data Engineer 4 - HR Tech</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -986,14 +986,14 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f8d0c3f139798fd9</t>
+          <t>https://www.indeed.com/viewjob?jk=010f3637940ea854</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Data Engineer 4 - HR Tech</t>
+          <t>Data Engineer 5 (SEO/GEO, AdTech )</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1021,14 +1021,14 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=010f3637940ea854</t>
+          <t>https://www.indeed.com/viewjob?jk=e9a8f6941c1a4549</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Data Engineer 5 (SEO/GEO, AdTech )</t>
+          <t>Data Engineer 4</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1056,7 +1056,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e9a8f6941c1a4549</t>
+          <t>https://www.indeed.com/viewjob?jk=0db4720c664a5a3f</t>
         </is>
       </c>
     </row>
@@ -1091,14 +1091,14 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0db4720c664a5a3f</t>
+          <t>https://www.indeed.com/viewjob?jk=d80c6adab1193eaf</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Data Engineer 4</t>
+          <t>Data Engineer 5 (Enterprise Platforms Technology)</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1108,7 +1108,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1126,14 +1126,14 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d80c6adab1193eaf</t>
+          <t>https://www.indeed.com/viewjob?jk=220dab7fe793042b</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Data Engineer 5 (Enterprise Platforms Technology)</t>
+          <t>Data Engineer 5</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1143,7 +1143,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1161,24 +1161,24 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=220dab7fe793042b</t>
+          <t>https://www.indeed.com/viewjob?jk=3a1e95e5123a2b15</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Data Engineer 5</t>
+          <t>Senior Software Engineer - ai automation medical billing platform</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>Relentless Talent</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1186,34 +1186,34 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Redshift, RDS, Azure, Databricks, Spark, Scala, Snowflake</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3a1e95e5123a2b15</t>
+          <t>https://www.indeed.com/viewjob?jk=69d642c554413fbe</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Junior Infrastructure Engineer</t>
+          <t>Senior Software Engineer - ai automation medical billing platform</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Techsur Solutions</t>
+          <t>Relentless Talent</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Reston, VA, US USA</t>
+          <t>Buffalo, NY, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1221,7 +1221,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Azure, Scala, Splunk, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,24 +1231,24 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1dfb157f527b54b9</t>
+          <t>https://www.indeed.com/viewjob?jk=818c7178aa0280e0</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - ai automation medical billing platform</t>
+          <t>Junior Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Relentless Talent</t>
+          <t>Techsur Solutions</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>Reston, VA, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,7 +1256,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL</t>
+          <t>AWS, S3, IAM, RDS, Azure, Scala, Splunk, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,32 +1266,32 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=69d642c554413fbe</t>
+          <t>https://www.indeed.com/viewjob?jk=1dfb157f527b54b9</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - ai automation medical billing platform</t>
+          <t>Databricks Forward Deployed Engineer (AI/ML)</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Relentless Talent</t>
+          <t>Revstar</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Buffalo, NY, US USA</t>
+          <t>AZ, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, Azure, Databricks, Unity Catalog, GCP, Hadoop</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,24 +1301,24 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=818c7178aa0280e0</t>
+          <t>https://www.indeed.com/viewjob?jk=c58a99eaffa53928</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Data Engineer I, II</t>
+          <t>Databricks Forward Deployed Engineer (AI/ML)</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Moda Health</t>
+          <t>Revstar</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Portland, OR, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,7 +1326,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Redshift, Azure, Data Factory, BigQuery, Scala, Snowflake, SQL Server, Data Modeling, ETL, ELT</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, Azure, Databricks, Unity Catalog, GCP, Hadoop</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,24 +1336,24 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7db50249524e5920</t>
+          <t>https://www.indeed.com/viewjob?jk=471c5127dda2d9df</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Data Analyst / Data Engineer – Python, Automation &amp; AI</t>
+          <t>Databricks Forward Deployed Engineer (AI/ML)</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>iVedha Inc.</t>
+          <t>Revstar</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Toronto, OH, US USA</t>
+          <t>FL, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,7 +1361,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Scala, Snowflake, ETL, ELT</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, Azure, Databricks, Unity Catalog, GCP, Hadoop</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,24 +1371,24 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=94a37fc46cd45ada</t>
+          <t>https://www.indeed.com/viewjob?jk=ec35dbf5b317fd4d</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Senior Data Platfrom Engineer</t>
+          <t>Data Engineer I, II</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Moda Health</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Portland, OR, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,7 +1396,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Delta Live Tables, Spark, PySpark, Scala, Data Modeling</t>
+          <t>Redshift, Azure, Data Factory, BigQuery, Scala, Snowflake, SQL Server, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,24 +1406,24 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bc974eac3e508ce6</t>
+          <t>https://www.indeed.com/viewjob?jk=7db50249524e5920</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Analyst / Data Engineer – Python, Automation &amp; AI</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>iVedha Inc.</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Toronto, OH, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,7 +1431,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Delta Live Tables, Spark, PySpark, Scala, Data Modeling</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Scala, Snowflake, ETL, ELT</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,24 +1441,24 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e85b5d56e27bdfb8</t>
+          <t>https://www.indeed.com/viewjob?jk=94a37fc46cd45ada</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Cloud Engineer</t>
+          <t>Senior Data Platfrom Engineer</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Willdan</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Anaheim, CA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,34 +1466,34 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, Azure, Scala, Amazon QuickSight, CI/CD</t>
+          <t>RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Delta Live Tables, Spark, PySpark, Scala, Data Modeling</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8d1298ac76effc74</t>
+          <t>https://www.indeed.com/viewjob?jk=bc974eac3e508ce6</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>C,C++, Python, Golang Developer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, SQL Server, PostgreSQL, CI/CD</t>
+          <t>RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Delta Live Tables, Spark, PySpark, Scala, Data Modeling</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,32 +1511,32 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=441856af730024e8</t>
+          <t>https://www.indeed.com/viewjob?jk=e85b5d56e27bdfb8</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Back-end Engineer - Data Platforms</t>
+          <t>Cloud Engineer</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Morgan Stanley</t>
+          <t>Willdan</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Anaheim, CA, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Spark, PySpark, Scala, Kafka</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, Azure, Scala, Amazon QuickSight, CI/CD</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,67 +1546,67 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ebb387f8fd246816</t>
+          <t>https://www.indeed.com/viewjob?jk=8d1298ac76effc74</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Database Engineer - onsite</t>
+          <t>C,C++, Python, Golang Developer</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Eccalon</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Detroit, MI, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Azure, BigQuery, Scala, Snowflake, Oracle, SQL Server, Data Modeling, Dimensional Modeling</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, SQL Server, PostgreSQL, CI/CD</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e9489350e98d48c6</t>
+          <t>https://www.indeed.com/viewjob?jk=441856af730024e8</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Forward Deployed Engineer</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>United Utility</t>
+          <t>Nexus One</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Spring, TX, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, BigQuery, Cloud Storage, Scala, Snowflake, Data Modeling</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Hadoop, YARN, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,102 +1616,102 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2c848474306799be</t>
+          <t>https://www.indeed.com/viewjob?jk=0c644fadd3aa330e</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Software Engineer III - Generative AI Technology</t>
+          <t>Back-end Engineer - Data Platforms</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Wayfair</t>
+          <t>Morgan Stanley</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, BigQuery, Scala, PostgreSQL, MongoDB, MLflow, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Spark, PySpark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dea1b605e8c5ec18</t>
+          <t>https://www.indeed.com/viewjob?jk=ebb387f8fd246816</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Data Engineer (Oracle Apps)</t>
+          <t>Database Engineer - onsite</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Fidelity TalentSource</t>
+          <t>Eccalon</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Durham, NC, US USA</t>
+          <t>Detroit, MI, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>13.2</v>
+        <v>14.6</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, Oracle, MongoDB, NoSQL, ETL</t>
+          <t>Redshift, RDS, Azure, BigQuery, Scala, Snowflake, Oracle, SQL Server, Data Modeling, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c788224995fc1529</t>
+          <t>https://www.indeed.com/viewjob?jk=e9489350e98d48c6</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer (MLOPS)</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>The Coca-Cola Company</t>
+          <t>FMNE Insurance Company</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Lincoln, NE, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Medallion Architecture, GCP, Vertex AI, Scala, MLOps, CI/CD, GitHub Actions</t>
+          <t>RDS, Azure, Data Factory, Databricks, Scala, SQL Server, Data Modeling, Dimensional Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,32 +1721,32 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8551311899e9bc7c</t>
+          <t>https://www.indeed.com/viewjob?jk=ee685373a5be1de3</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Product Software Engineer II</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>United Utility</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Spring, TX, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, S3, ECS, Databricks, Spark, Scala, CI/CD, Jenkins</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, BigQuery, Cloud Storage, Scala, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,59 +1756,59 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5fd9ded3cfb927d6</t>
+          <t>https://www.indeed.com/viewjob?jk=2c848474306799be</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - LoopNet</t>
+          <t>Software Engineer III - Generative AI Technology</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>CoStar Group</t>
+          <t>Wayfair</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Irvine, CA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, S3, SQS, Databricks, BigQuery, Scala, Kafka, Snowflake, MySQL, DynamoDB</t>
+          <t>AWS, Azure, GCP, BigQuery, Scala, PostgreSQL, MongoDB, MLflow, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=625a58dd59856504</t>
+          <t>https://www.indeed.com/viewjob?jk=dea1b605e8c5ec18</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Senior Machine Learning Engineer (MLOPS)</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Imperial Brady</t>
+          <t>The Coca-Cola Company</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,42 +1816,42 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Medallion Architecture, Spark, PySpark, Scala, Data Modeling, Dimensional Modeling</t>
+          <t>AWS, RDS, Azure, Medallion Architecture, GCP, Vertex AI, Scala, MLOps, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=49e6c0c32c4bdcc7</t>
+          <t>https://www.indeed.com/viewjob?jk=8551311899e9bc7c</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Senior Platform Engineer, Growth Product Engineering</t>
+          <t>Product Software Engineer II</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Samsara</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>California City, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, Lambda, ECS, IAM, RDS, Databricks, CI/CD, GitHub Actions, Terraform, Docker</t>
+          <t>AWS, EMR, Lambda, S3, ECS, Databricks, Spark, Scala, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,67 +1861,67 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6566d58d441eeee5</t>
+          <t>https://www.indeed.com/viewjob?jk=5fd9ded3cfb927d6</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Senior Cloud / AWS Infrastructure Engineer</t>
+          <t>Data Engineer (Oracle Apps)</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Reflex Media Inc</t>
+          <t>Fidelity TalentSource</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Durham, NC, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, S3, ECS, IAM, RDS, PostgreSQL, MySQL, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, Oracle, MongoDB, NoSQL, ETL</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=901aac12afba9b93</t>
+          <t>https://www.indeed.com/viewjob?jk=c788224995fc1529</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Specialist Solutions Architect - Cloud Infrastructure &amp; AWS Platform</t>
+          <t>Senior Software Engineer - LoopNet</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>CoStar Group</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Irvine, CA, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Databricks, Unity Catalog, Scala, Snowflake, Terraform, AWS CloudFormation</t>
+          <t>AWS, S3, SQS, Databricks, BigQuery, Scala, Kafka, Snowflake, MySQL, DynamoDB</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,24 +1931,24 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ac14888eb4824ae2</t>
+          <t>https://www.indeed.com/viewjob?jk=625a58dd59856504</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Data Platform Architect</t>
+          <t>Senior Platform Engineer, Growth Product Engineering</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Samsara</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>California City, CA, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,7 +1956,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, Unity Catalog, GCP, BigQuery, Spark, Scala</t>
+          <t>AWS, Lambda, ECS, IAM, RDS, Databricks, CI/CD, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,24 +1966,24 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d90b3504b0804f94</t>
+          <t>https://www.indeed.com/viewjob?jk=6566d58d441eeee5</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Enterprise Architect - Data Platform</t>
+          <t>Senior Cloud / AWS Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Johnson Controls</t>
+          <t>Reflex Media Inc</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Milwaukee, WI, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,34 +1991,34 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Spark, Scala, Kafka, Snowflake, Data Modeling</t>
+          <t>AWS, Lambda, Redshift, S3, ECS, IAM, RDS, PostgreSQL, MySQL, CI/CD</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d42707fbe5923515</t>
+          <t>https://www.indeed.com/viewjob?jk=901aac12afba9b93</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Forward Deployed Engineer (AWS)</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Exostar</t>
+          <t>Revstar</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Herndon, VA, US USA</t>
+          <t>AZ, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,7 +2026,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Scala, SQL Server, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, API Gateway, ECS, IAM, RDS, Scala</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,24 +2036,24 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ca5e90ebcac7315c</t>
+          <t>https://www.indeed.com/viewjob?jk=65da8aaf4011e226</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Sr Implementation Consultant</t>
+          <t>Forward Deployed Engineer (AWS)</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Cotiviti</t>
+          <t>Revstar</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>FL, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2061,34 +2061,34 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, Glue, ECS, RDS, Azure, Oracle, SQL Server, Data Modeling, ETL, Talend</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, API Gateway, ECS, IAM, RDS, Scala</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=feec9157e828c7c5</t>
+          <t>https://www.indeed.com/viewjob?jk=ada06b5a2ee25a8b</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Azure Solutions Architect - Presales</t>
+          <t>Forward Deployed Engineer (AWS)</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>TTEC Digital</t>
+          <t>Revstar</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2096,34 +2096,34 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Synapse Analytics, Databricks, Scala, ETL, Power BI, Azure DevOps, Terraform, AKS</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, API Gateway, ECS, IAM, RDS, Scala</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9d1ac466d0b2792d</t>
+          <t>https://www.indeed.com/viewjob?jk=419115b4b37379d9</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>BI Engineer (Data Analyst)</t>
+          <t>Specialist Solutions Architect - Cloud Infrastructure &amp; AWS Platform</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Apply</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>AR, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,7 +2131,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Scala, Snowflake, Data Modeling, dbt</t>
+          <t>AWS, IAM, RDS, Azure, Databricks, Unity Catalog, Scala, Snowflake, Terraform, AWS CloudFormation</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,24 +2141,24 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7f4074f2837c770f</t>
+          <t>https://www.indeed.com/viewjob?jk=ac14888eb4824ae2</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Full Stack Engineer 4 (Python, AWS, AI, Snowflake, Databricks)</t>
+          <t>Data Platform Architect</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,7 +2166,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Snowflake, NoSQL, CI/CD, Docker</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, Unity Catalog, GCP, BigQuery, Spark, Scala</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,24 +2176,24 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2d2e1578e6815ef7</t>
+          <t>https://www.indeed.com/viewjob?jk=d90b3504b0804f94</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Software Engineer - Remote</t>
+          <t>Enterprise Architect - Data Platform</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Johnson Controls</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>Milwaukee, WI, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,7 +2201,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Dask, Splunk, CI/CD</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Spark, Scala, Kafka, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,24 +2211,24 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=29fa962c43112ed2</t>
+          <t>https://www.indeed.com/viewjob?jk=d42707fbe5923515</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Software Development Engineer II</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>GM Financial</t>
+          <t>Exostar</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Arlington, TX, US USA</t>
+          <t>Herndon, VA, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,34 +2236,34 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Azure, Scala, Oracle, SQL Server, NoSQL, Jenkins, Azure DevOps, Maven, Terraform, Docker</t>
+          <t>AWS, S3, RDS, Azure, Scala, SQL Server, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=77c13363e54e5087</t>
+          <t>https://www.indeed.com/viewjob?jk=ca5e90ebcac7315c</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Data Analyst - ERP &amp; Master Data</t>
+          <t>Sr Implementation Consultant</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>TransTech Group</t>
+          <t>Cotiviti</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,7 +2271,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Medallion Architecture, Dataflow, Spark, PySpark, Scala</t>
+          <t>AWS, Glue, ECS, RDS, Azure, Oracle, SQL Server, Data Modeling, ETL, Talend</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,24 +2281,24 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=49c2343d736f4c5c</t>
+          <t>https://www.indeed.com/viewjob?jk=feec9157e828c7c5</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Full-Stack Engineer 4 (Java, Spring, DynamoDB, S3, GraphQL, GenAI)</t>
+          <t>Azure Solutions Architect - Presales</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>TTEC Digital</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,34 +2306,34 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, DynamoDB, NoSQL, CI/CD, Docker</t>
+          <t>Azure, Data Factory, Synapse Analytics, Databricks, Scala, ETL, Power BI, Azure DevOps, Terraform, AKS</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=30dd4b0534b4aca9</t>
+          <t>https://www.indeed.com/viewjob?jk=9d1ac466d0b2792d</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Full-Stack Engineer 4 (Java, Spring, DynamoDB, S3, GraphQL, GenAL)</t>
+          <t>BI Engineer (Data Analyst)</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>Apply</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>AR, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,7 +2341,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, DynamoDB, NoSQL, CI/CD, Docker</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Scala, Snowflake, Data Modeling, dbt</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,32 +2351,32 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3e502713d51d0a40</t>
+          <t>https://www.indeed.com/viewjob?jk=7f4074f2837c770f</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>AI Data Engineer - University Students - QuantumBlack, AI by McKinsey</t>
+          <t>Full Stack Engineer 4 (Python, AWS, AI, Snowflake, Databricks)</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>McKinsey &amp; Company</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, BigQuery, Spark, Scala, Snowflake, dbt, MLOps</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Snowflake, NoSQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,67 +2386,67 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3c376f7a6c4f6eae</t>
+          <t>https://www.indeed.com/viewjob?jk=2d2e1578e6815ef7</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Software Engineer - Remote</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Pika</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, Redshift, GCP, BigQuery, Scala, Kafka, Snowflake, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Dask, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=126cb889e15ed9cd</t>
+          <t>https://www.indeed.com/viewjob?jk=29fa962c43112ed2</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Software Development Engineer II</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Hollstadt Consulting</t>
+          <t>GM Financial</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>MN, US USA</t>
+          <t>Arlington, TX, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>S3, IAM, RDS, Azure, Google Cloud Platform, GCP, Cloud Storage, Scala, CI/CD, Azure DevOps</t>
+          <t>Azure, Scala, Oracle, SQL Server, NoSQL, Jenkins, Azure DevOps, Maven, Terraform, Docker</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,32 +2456,32 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9488041a67901dc1</t>
+          <t>https://www.indeed.com/viewjob?jk=77c13363e54e5087</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Sr Data Engineer II</t>
+          <t>Data Analyst - ERP &amp; Master Data</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>American Express</t>
+          <t>TransTech Group</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, RDS, HBase, Spark, Scala, Kafka, Cassandra, NoSQL, MLOps, CI/CD</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Medallion Architecture, Dataflow, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,94 +2491,94 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a9b4607cbdf4a3d4</t>
+          <t>https://www.indeed.com/viewjob?jk=49c2343d736f4c5c</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Full-Stack Engineer 4 (Java, Spring, DynamoDB, S3, GraphQL, GenAI)</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Community Choice Credit Union</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Warren, MI, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Scala, Snowflake, SQL Server, Data Modeling, ETL, ELT, Power BI</t>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, DynamoDB, NoSQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=21899fbf482a9cd2</t>
+          <t>https://www.indeed.com/viewjob?jk=30dd4b0534b4aca9</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Full-Stack Engineer 4 (Java, Spring, DynamoDB, S3, GraphQL, GenAL)</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Community Choice Credit Union</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Jackson, MI, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Scala, Snowflake, SQL Server, Data Modeling, ETL, ELT, Power BI</t>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, DynamoDB, NoSQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9457f2c72938dbd5</t>
+          <t>https://www.indeed.com/viewjob?jk=3e502713d51d0a40</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Sr Data Engineer II</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Community Choice Credit Union</t>
+          <t>American Express</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Holland, MI, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,34 +2586,34 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Scala, Snowflake, SQL Server, Data Modeling, ETL, ELT, Power BI</t>
+          <t>AWS, RDS, HBase, Spark, Scala, Kafka, Cassandra, NoSQL, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6f79614628dc966f</t>
+          <t>https://www.indeed.com/viewjob?jk=a9b4607cbdf4a3d4</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Sr. Data Integration Engineer</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Community Choice Credit Union</t>
+          <t>SPS Health</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Farmington Hills, MI, US USA</t>
+          <t>Milwaukee, WI, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2621,34 +2621,34 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Scala, Snowflake, SQL Server, Data Modeling, ETL, ELT, Power BI</t>
+          <t>AWS, RDS, Azure, Data Factory, Scala, SQL Server, Dimensional Modeling, CI/CD, Git, Python</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fc4be70d8a478d8a</t>
+          <t>https://www.indeed.com/viewjob?jk=26332ff2923820d1</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>AI Data Engineer - University Students - QuantumBlack, AI by McKinsey</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Community Choice Credit Union</t>
+          <t>McKinsey &amp; Company</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Jackson, MI, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,34 +2656,34 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Scala, Snowflake, SQL Server, Data Modeling, ETL, ELT, Power BI</t>
+          <t>AWS, Azure, Databricks, GCP, BigQuery, Spark, Scala, Snowflake, dbt, MLOps</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dad209d8bad2edfe</t>
+          <t>https://www.indeed.com/viewjob?jk=3c376f7a6c4f6eae</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>ONTIC TECHNOLOGIES</t>
+          <t>Pika</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,34 +2691,34 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, GCP, Scala, Kafka, MongoDB, CI/CD, Jenkins, Terraform</t>
+          <t>AWS, Kinesis, Redshift, GCP, BigQuery, Scala, Kafka, Snowflake, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7300772b168034de</t>
+          <t>https://www.indeed.com/viewjob?jk=126cb889e15ed9cd</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Senior Backend Developer – Python</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Hollstadt Consulting</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>MN, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,34 +2726,34 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, Glue, S3, RDS, Scala, Oracle, SQL Server, PostgreSQL, DynamoDB, CI/CD</t>
+          <t>S3, IAM, RDS, Azure, Google Cloud Platform, GCP, Cloud Storage, Scala, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=65b0c92c185362f0</t>
+          <t>https://www.indeed.com/viewjob?jk=9488041a67901dc1</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Intentsify</t>
+          <t>Community Choice Credit Union</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Warren, MI, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2761,34 +2761,34 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, S3, SQS, SNS, IAM, Snowflake, ETL, ELT, CI/CD, Terraform</t>
+          <t>RDS, Azure, Data Factory, Scala, Snowflake, SQL Server, Data Modeling, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6d89a533339b416c</t>
+          <t>https://www.indeed.com/viewjob?jk=21899fbf482a9cd2</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Consultant, Data &amp; Analytics, NA</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>The Coca-Cola Company</t>
+          <t>Community Choice Credit Union</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Jackson, MI, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,217 +2796,217 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Scala, ETL, ELT, Power BI, Tableau, Git</t>
+          <t>RDS, Azure, Data Factory, Scala, Snowflake, SQL Server, Data Modeling, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=df7e6baa7a7dd0a0</t>
+          <t>https://www.indeed.com/viewjob?jk=9457f2c72938dbd5</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Cloud Platform Engineering</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>MariaDB plc</t>
+          <t>Community Choice Credit Union</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>VA, US USA</t>
+          <t>Holland, MI, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, MySQL, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>RDS, Azure, Data Factory, Scala, Snowflake, SQL Server, Data Modeling, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e683398c349f7a6d</t>
+          <t>https://www.indeed.com/viewjob?jk=6f79614628dc966f</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>AMD</t>
+          <t>Community Choice Credit Union</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Farmington Hills, MI, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Medallion Architecture, Spark, PySpark, Snowflake, dbt, Power BI</t>
+          <t>RDS, Azure, Data Factory, Scala, Snowflake, SQL Server, Data Modeling, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9724e994419d2473</t>
+          <t>https://www.indeed.com/viewjob?jk=fc4be70d8a478d8a</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>AWS Workspaces Migration Architect</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>WellSky</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Overland Park, KS, US USA</t>
+          <t>Des Moines, IA, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>RDS, GCP, BigQuery, Scala, SQL Server, Data Modeling, ETL, ELT, dbt, Tableau</t>
+          <t>AWS, IAM, RDS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, AWS CodePipeline, Azure DevOps</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1d0888bf081a07cc</t>
+          <t>https://www.indeed.com/viewjob?jk=1680648104527855</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Data Engineer II - AWS/PySpark/ETL</t>
+          <t>AWS Workspaces Migration Architect</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Des Moines, IA, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Spark, PySpark, Scala, Snowflake, ETL, CI/CD, Airflow</t>
+          <t>AWS, IAM, RDS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, AWS CodePipeline, Azure DevOps</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aa1cc23a36ed4493</t>
+          <t>https://www.indeed.com/viewjob?jk=c6c43c1e7a2bb253</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior DevOps Engineer</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Dropbox</t>
+          <t>ONTIC TECHNOLOGIES</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Kinesis, RDS, Databricks, Medallion Architecture, Spark, Scala, Kafka, Data Modeling, Airflow, Python</t>
+          <t>AWS, IAM, RDS, GCP, Scala, Kafka, MongoDB, CI/CD, Jenkins, Terraform</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=43e37e262d8bc84b</t>
+          <t>https://www.indeed.com/viewjob?jk=7300772b168034de</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Full-stack Engineer 5 (Nodejs/Go/Angularjs)</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>Intentsify</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
+          <t>AWS, S3, SQS, SNS, IAM, Snowflake, ETL, ELT, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3016,84 +3016,84 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9813442a220867be</t>
+          <t>https://www.indeed.com/viewjob?jk=6d89a533339b416c</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Full-stack Engineer 4 - RiskTech</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>Wiliot</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
+          <t>AWS, Azure, Databricks, GCP, Spark, Scala, PostgreSQL, MongoDB, DynamoDB, NoSQL</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f2960b2498873f28</t>
+          <t>https://www.indeed.com/viewjob?jk=5308ad0d41e6f61f</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Full-stack Engineer 4 (Golang, Python, Java, AWS)</t>
+          <t>Software Engineering Co-op (Cloud)</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>Sonos</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
+          <t>AWS, API Gateway, RDS, Tableau, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=da278457dd975c3f</t>
+          <t>https://www.indeed.com/viewjob?jk=2ea49302adcd1e9c</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Full-stack Engineer 4</t>
+          <t>Full-stack Engineer 5 (Nodejs/Go/Angularjs)</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -3121,14 +3121,14 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=18716e78985d34c6</t>
+          <t>https://www.indeed.com/viewjob?jk=9813442a220867be</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Full-stack Engineer 4 (Go, AWS)</t>
+          <t>Full-stack Engineer 4 - RiskTech</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -3156,24 +3156,24 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6132bb0eb6aaf86d</t>
+          <t>https://www.indeed.com/viewjob?jk=f2960b2498873f28</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Senior Backend Software Engineer</t>
+          <t>Full-stack Engineer 4 (Golang, Python, Java, AWS)</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>KorTerra</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Chanhassen, MN, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3181,34 +3181,34 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, PostgreSQL, NoSQL, CI/CD, Terraform, Docker, Kubernetes, AKS</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0fed605a20e912b9</t>
+          <t>https://www.indeed.com/viewjob?jk=da278457dd975c3f</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Associate Solution Architect with Modernization Experience</t>
+          <t>Full-stack Engineer 4</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3216,7 +3216,7 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -3226,24 +3226,24 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c343a7d6432ffeaa</t>
+          <t>https://www.indeed.com/viewjob?jk=18716e78985d34c6</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Associate Solution Architect with Modernization Experience</t>
+          <t>Full-stack Engineer 4 (Go, AWS)</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Tempe, AZ, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3251,7 +3251,7 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -3261,24 +3261,24 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e60054b9631d7895</t>
+          <t>https://www.indeed.com/viewjob?jk=6132bb0eb6aaf86d</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Associate Solution Architect with Modernization Experience</t>
+          <t>Senior Software Engineer - Cloud Platform Engineering</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>MariaDB plc</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>VA, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3286,34 +3286,34 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Scala, MySQL, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=99aade9079199e44</t>
+          <t>https://www.indeed.com/viewjob?jk=e683398c349f7a6d</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Associate Solution Architect with Modernization Experience</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>AMD</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Las Vegas, NV, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3321,7 +3321,7 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Databricks, Medallion Architecture, Spark, PySpark, Snowflake, dbt, Power BI</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -3331,24 +3331,24 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fb5a4840f3df3c6d</t>
+          <t>https://www.indeed.com/viewjob?jk=9724e994419d2473</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Associate Solution Architect with Modernization Experience</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>WellSky</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Morristown, NJ, US USA</t>
+          <t>Overland Park, KS, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3356,7 +3356,7 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes</t>
+          <t>RDS, GCP, BigQuery, Scala, SQL Server, Data Modeling, ETL, ELT, dbt, Tableau</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -3366,24 +3366,24 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=55abd889581cdc48</t>
+          <t>https://www.indeed.com/viewjob?jk=1d0888bf081a07cc</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Associate Solution Architect with Modernization Experience</t>
+          <t>Data Engineer II - AWS/PySpark/ETL</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Detroit, MI, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3391,7 +3391,7 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes</t>
+          <t>AWS, RDS, Databricks, Spark, PySpark, Scala, Snowflake, ETL, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -3401,24 +3401,24 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e3febde783536e21</t>
+          <t>https://www.indeed.com/viewjob?jk=aa1cc23a36ed4493</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Associate Solution Architect with Modernization Experience</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>KorTerra</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Chanhassen, MN, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3426,34 +3426,34 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes</t>
+          <t>RDS, Azure, Scala, PostgreSQL, NoSQL, CI/CD, Terraform, Docker, Kubernetes, AKS</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1be19f91eec7a842</t>
+          <t>https://www.indeed.com/viewjob?jk=fb4fc48fd252444e</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Associate Solution Architect with Modernization Experience</t>
+          <t>Senior Backend Software Engineer</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>KorTerra</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Chanhassen, MN, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3461,34 +3461,34 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes</t>
+          <t>RDS, Azure, Scala, PostgreSQL, NoSQL, CI/CD, Terraform, Docker, Kubernetes, AKS</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7698c96689f48a9e</t>
+          <t>https://www.indeed.com/viewjob?jk=0fed605a20e912b9</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Associate Solution Architect with Modernization Experience</t>
+          <t>Senior Full Stack Engineer, Agentic AI Platform</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>NY, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3496,34 +3496,34 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Databricks, BigQuery, Scala, MongoDB, ELT, CI/CD, Kubernetes</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d2e1386f9d607f38</t>
+          <t>https://www.indeed.com/viewjob?jk=7b030b41dfd686f3</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Associate Solution Architect with Modernization Experience</t>
+          <t>Sr Technical Analyst/Prog Ent App</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Avangrid</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Orange, CT, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3531,7 +3531,7 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, ETL, Azure DevOps, Git</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -3541,24 +3541,24 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2f2ca862816ed069</t>
+          <t>https://www.indeed.com/viewjob?jk=4ea1b275b8152311</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Associate Solution Architect with Modernization Experience</t>
+          <t>Full Stack Ad Tech Developer</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>The Hearst Corporation</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3566,7 +3566,7 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes</t>
+          <t>AWS, Redshift, Google Cloud Platform, BigQuery, Scala, ETL, Tableau, CI/CD, Git, Python</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -3576,24 +3576,24 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a40909cafc968d82</t>
+          <t>https://www.indeed.com/viewjob?jk=e8cf1f61c24a8358</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Associate Solution Architect with Modernization Experience</t>
+          <t>Full-stack Engineer 4 (IC)</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -3601,29 +3601,29 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=124344ebd08b7526</t>
+          <t>https://www.indeed.com/viewjob?jk=4620494dca257198</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Associate Solution Architect with Modernization Experience</t>
+          <t>Full-stack Engineer 4 (IC)</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
@@ -3636,34 +3636,34 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f0ef6c1eb38b0db9</t>
+          <t>https://www.indeed.com/viewjob?jk=6b1bed8feba6b917</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Associate Solution Architect with Modernization Experience</t>
+          <t>Full-stack Engineer 4</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
@@ -3671,34 +3671,34 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b780dcc242beb567</t>
+          <t>https://www.indeed.com/viewjob?jk=8e194fdfb9b8dbe3</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Associate Solution Architect with Modernization Experience</t>
+          <t>Full-Stack Engineer 4 (Python, AWS, Network Automation)</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
@@ -3706,42 +3706,42 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a03180188c81f9bf</t>
+          <t>https://www.indeed.com/viewjob?jk=a77780c738e44a57</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Associate Solution Architect with Modernization Experience</t>
+          <t>Integration Engineer 4</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes</t>
+          <t>AWS, Lambda, Step Functions, RDS, Azure, GCP, Scala, Splunk, Jenkins, Jenkins</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -3751,32 +3751,32 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8a037168850b8fe0</t>
+          <t>https://www.indeed.com/viewjob?jk=52d873bb7fc420f0</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Associate Solution Architect with Modernization Experience</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>KeHE Distributors</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Naperville, IL, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, Data Modeling, Power BI, Tableau, MLOps</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
@@ -3786,32 +3786,32 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=45cd4b8d959d97ab</t>
+          <t>https://www.indeed.com/viewjob?jk=9033c8036c6af9b3</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Associate Solution Architect with Modernization Experience</t>
+          <t>Data Platform Engineer</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Hubble Network</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes</t>
+          <t>Kinesis, Redshift, RDS, Scala, Kafka, Dimensional Modeling, Star Schema, Fact Tables, ETL, dbt</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
@@ -3821,137 +3821,137 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=52080037fabe4cb1</t>
+          <t>https://www.indeed.com/viewjob?jk=a000c1d1d33d8b12</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Associate Solution Architect with Modernization Experience</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Lockheed Martin</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Databricks, Oracle, SQL Server, MySQL, ETL, Tableau, CI/CD</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=69224b4d176dd4a2</t>
+          <t>https://www.indeed.com/viewjob?jk=70671fedd9bf2e0b</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Associate Solution Architect with Modernization Experience</t>
+          <t>Specialist Solutions Architect - Cloud Infrastructure &amp; Azure Platform</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Kansas City, MO, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Scala, Snowflake, Terraform, Azure Monitor, Python</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5ce9dba6d19c8b82</t>
+          <t>https://www.indeed.com/viewjob?jk=24b4e0a029b86ac2</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Associate Solution Architect with Modernization Experience</t>
+          <t>Senior Full Stack Software Engineer (Java)</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D100" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes</t>
+          <t>AWS, Azure, GCP, Kafka, Oracle, SQL Server, PostgreSQL, MySQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7c5344293aa5ed77</t>
+          <t>https://www.indeed.com/viewjob?jk=e58be4fcea83450d</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Associate Solution Architect with Modernization Experience</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Mastercard</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>O'Fallon, MO, US USA</t>
         </is>
       </c>
       <c r="D101" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes</t>
+          <t>AWS, API Gateway, RDS, Scala, Oracle, PostgreSQL, CI/CD, Jenkins, GitHub Actions, Jenkins</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
@@ -3961,137 +3961,137 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fea3b3cc46faeb2a</t>
+          <t>https://www.indeed.com/viewjob?jk=0245dcafa3f48258</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Associate Solution Architect with Modernization Experience</t>
+          <t>Software Engineer II</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Identity Digital</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Bellevue, WA, US USA</t>
         </is>
       </c>
       <c r="D102" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes</t>
+          <t>AWS, Glue, Lambda, Step Functions, API Gateway, Scala, PostgreSQL, DynamoDB, CI/CD, Git</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c3672ad48951be20</t>
+          <t>https://www.indeed.com/viewjob?jk=7b468d5dbbf0d446</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Associate Solution Architect with Modernization Experience</t>
+          <t>Senior DevOps Engineer - Arena</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>PTC</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>San Mateo, CA, US USA</t>
         </is>
       </c>
       <c r="D103" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes</t>
+          <t>AWS, RDS, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c45dff0f36a9a356</t>
+          <t>https://www.indeed.com/viewjob?jk=136719f380319c28</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Associate Solution Architect with Modernization Experience</t>
+          <t>Data QA Engineer</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D104" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Databricks, Medallion Architecture, GCP, Spark, PySpark, Snowflake, ETL</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7e91b7a712b7a165</t>
+          <t>https://www.indeed.com/viewjob?jk=2ad09685b76e2f51</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Associate Solution Architect with Modernization Experience</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Function Health</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D105" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes</t>
+          <t>RDS, Databricks, BigQuery, Spark, Kafka, Snowflake, ELT, dbt, MLOps, Terraform</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
@@ -4101,2105 +4101,110 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f3d69f9412407b80</t>
+          <t>https://www.indeed.com/viewjob?jk=8d332f2047edfa45</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Associate Solution Architect with Modernization Experience</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>KorTerra</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Chanhassen, MN, US USA</t>
         </is>
       </c>
       <c r="D106" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes</t>
+          <t>Azure, Scala, PostgreSQL, NoSQL, CI/CD, Terraform, Docker, Kubernetes, AKS, Git</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7d48fbbfaa3d0a97</t>
+          <t>https://www.indeed.com/viewjob?jk=2fd41f8a4a17d7e0</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Associate Solution Architect with Modernization Experience</t>
+          <t>Azure Data Engineer</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Orion Innovation</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Stamford, CT, US USA</t>
+          <t>Montvale, NJ, US USA</t>
         </is>
       </c>
       <c r="D107" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes</t>
+          <t>Azure, Data Factory, Databricks, Spark, PySpark, Scala, ETL, ELT, Power BI, AKS</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c300f1e448116fd7</t>
+          <t>https://www.indeed.com/viewjob?jk=334e0bc8c90d3013</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Associate Solution Architect with Modernization Experience</t>
+          <t>Backend Software Engineer</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>KorTerra</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Sacramento, CA, US USA</t>
+          <t>Chanhassen, MN, US USA</t>
         </is>
       </c>
       <c r="D108" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes</t>
+          <t>Azure, Scala, PostgreSQL, NoSQL, CI/CD, Terraform, Docker, Kubernetes, AKS, Git</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=316adbd72ad7e2e8</t>
-        </is>
-      </c>
-    </row>
-    <row r="109">
-      <c r="A109" t="inlineStr">
-        <is>
-          <t>Associate Solution Architect with Modernization Experience</t>
-        </is>
-      </c>
-      <c r="B109" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C109" t="inlineStr">
-        <is>
-          <t>Costa Mesa, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D109" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E109" t="inlineStr">
-        <is>
-          <t>AWS, Azure, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F109" t="inlineStr">
-        <is>
-          <t>2026-09-22</t>
-        </is>
-      </c>
-      <c r="G109" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=f219232c6b6eef2b</t>
-        </is>
-      </c>
-    </row>
-    <row r="110">
-      <c r="A110" t="inlineStr">
-        <is>
-          <t>Associate Solution Architect with Modernization Experience</t>
-        </is>
-      </c>
-      <c r="B110" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C110" t="inlineStr">
-        <is>
-          <t>San Francisco, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D110" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E110" t="inlineStr">
-        <is>
-          <t>AWS, Azure, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F110" t="inlineStr">
-        <is>
-          <t>2026-09-22</t>
-        </is>
-      </c>
-      <c r="G110" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=0bb31aa937d723cd</t>
-        </is>
-      </c>
-    </row>
-    <row r="111">
-      <c r="A111" t="inlineStr">
-        <is>
-          <t>Associate Solution Architect with Modernization Experience</t>
-        </is>
-      </c>
-      <c r="B111" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C111" t="inlineStr">
-        <is>
-          <t>Hartford, CT, US USA</t>
-        </is>
-      </c>
-      <c r="D111" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E111" t="inlineStr">
-        <is>
-          <t>AWS, Azure, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F111" t="inlineStr">
-        <is>
-          <t>2026-09-22</t>
-        </is>
-      </c>
-      <c r="G111" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=884c614c785d6835</t>
-        </is>
-      </c>
-    </row>
-    <row r="112">
-      <c r="A112" t="inlineStr">
-        <is>
-          <t>Associate Solution Architect with Modernization Experience</t>
-        </is>
-      </c>
-      <c r="B112" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C112" t="inlineStr">
-        <is>
-          <t>San Jose, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D112" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E112" t="inlineStr">
-        <is>
-          <t>AWS, Azure, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F112" t="inlineStr">
-        <is>
-          <t>2026-09-22</t>
-        </is>
-      </c>
-      <c r="G112" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=ecedaabbce0a0b5b</t>
-        </is>
-      </c>
-    </row>
-    <row r="113">
-      <c r="A113" t="inlineStr">
-        <is>
-          <t>Associate Solution Architect with Modernization Experience</t>
-        </is>
-      </c>
-      <c r="B113" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C113" t="inlineStr">
-        <is>
-          <t>Denver, CO, US USA</t>
-        </is>
-      </c>
-      <c r="D113" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E113" t="inlineStr">
-        <is>
-          <t>AWS, Azure, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F113" t="inlineStr">
-        <is>
-          <t>2026-09-22</t>
-        </is>
-      </c>
-      <c r="G113" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=eea12c90a4a047af</t>
-        </is>
-      </c>
-    </row>
-    <row r="114">
-      <c r="A114" t="inlineStr">
-        <is>
-          <t>Associate Solution Architect with Modernization Experience</t>
-        </is>
-      </c>
-      <c r="B114" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C114" t="inlineStr">
-        <is>
-          <t>Chicago, IL, US USA</t>
-        </is>
-      </c>
-      <c r="D114" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E114" t="inlineStr">
-        <is>
-          <t>AWS, Azure, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F114" t="inlineStr">
-        <is>
-          <t>2026-09-22</t>
-        </is>
-      </c>
-      <c r="G114" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=28b6e9e7e6b5c6aa</t>
-        </is>
-      </c>
-    </row>
-    <row r="115">
-      <c r="A115" t="inlineStr">
-        <is>
-          <t>Associate Solution Architect with Modernization Experience</t>
-        </is>
-      </c>
-      <c r="B115" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C115" t="inlineStr">
-        <is>
-          <t>Miami, FL, US USA</t>
-        </is>
-      </c>
-      <c r="D115" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E115" t="inlineStr">
-        <is>
-          <t>AWS, Azure, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F115" t="inlineStr">
-        <is>
-          <t>2026-09-22</t>
-        </is>
-      </c>
-      <c r="G115" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=2c0e09d9843111bd</t>
-        </is>
-      </c>
-    </row>
-    <row r="116">
-      <c r="A116" t="inlineStr">
-        <is>
-          <t>Associate Solution Architect with Modernization Experience</t>
-        </is>
-      </c>
-      <c r="B116" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C116" t="inlineStr">
-        <is>
-          <t>Los Angeles, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D116" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E116" t="inlineStr">
-        <is>
-          <t>AWS, Azure, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F116" t="inlineStr">
-        <is>
-          <t>2026-09-22</t>
-        </is>
-      </c>
-      <c r="G116" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=3b10af7d10426fa4</t>
-        </is>
-      </c>
-    </row>
-    <row r="117">
-      <c r="A117" t="inlineStr">
-        <is>
-          <t>Sr Technical Analyst/Prog Ent App</t>
-        </is>
-      </c>
-      <c r="B117" t="inlineStr">
-        <is>
-          <t>Avangrid</t>
-        </is>
-      </c>
-      <c r="C117" t="inlineStr">
-        <is>
-          <t>Orange, CT, US USA</t>
-        </is>
-      </c>
-      <c r="D117" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E117" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, ETL, Azure DevOps, Git</t>
-        </is>
-      </c>
-      <c r="F117" t="inlineStr">
-        <is>
-          <t>2026-09-22</t>
-        </is>
-      </c>
-      <c r="G117" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=4ea1b275b8152311</t>
-        </is>
-      </c>
-    </row>
-    <row r="118">
-      <c r="A118" t="inlineStr">
-        <is>
-          <t>Full Stack Ad Tech Developer</t>
-        </is>
-      </c>
-      <c r="B118" t="inlineStr">
-        <is>
-          <t>The Hearst Corporation</t>
-        </is>
-      </c>
-      <c r="C118" t="inlineStr">
-        <is>
-          <t>New York, NY, US USA</t>
-        </is>
-      </c>
-      <c r="D118" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E118" t="inlineStr">
-        <is>
-          <t>AWS, Redshift, Google Cloud Platform, BigQuery, Scala, ETL, Tableau, CI/CD, Git, Python</t>
-        </is>
-      </c>
-      <c r="F118" t="inlineStr">
-        <is>
-          <t>2026-09-22</t>
-        </is>
-      </c>
-      <c r="G118" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=e8cf1f61c24a8358</t>
-        </is>
-      </c>
-    </row>
-    <row r="119">
-      <c r="A119" t="inlineStr">
-        <is>
-          <t>Full-stack Engineer 4 (IC)</t>
-        </is>
-      </c>
-      <c r="B119" t="inlineStr">
-        <is>
-          <t>Capital One</t>
-        </is>
-      </c>
-      <c r="C119" t="inlineStr">
-        <is>
-          <t>San Jose, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D119" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E119" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
-        </is>
-      </c>
-      <c r="F119" t="inlineStr">
-        <is>
-          <t>2026-09-23</t>
-        </is>
-      </c>
-      <c r="G119" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=4620494dca257198</t>
-        </is>
-      </c>
-    </row>
-    <row r="120">
-      <c r="A120" t="inlineStr">
-        <is>
-          <t>Full-stack Engineer 4 (IC)</t>
-        </is>
-      </c>
-      <c r="B120" t="inlineStr">
-        <is>
-          <t>Capital One</t>
-        </is>
-      </c>
-      <c r="C120" t="inlineStr">
-        <is>
-          <t>McLean, VA, US USA</t>
-        </is>
-      </c>
-      <c r="D120" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E120" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
-        </is>
-      </c>
-      <c r="F120" t="inlineStr">
-        <is>
-          <t>2026-09-23</t>
-        </is>
-      </c>
-      <c r="G120" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=6b1bed8feba6b917</t>
-        </is>
-      </c>
-    </row>
-    <row r="121">
-      <c r="A121" t="inlineStr">
-        <is>
-          <t>Full-stack Engineer 4</t>
-        </is>
-      </c>
-      <c r="B121" t="inlineStr">
-        <is>
-          <t>Capital One</t>
-        </is>
-      </c>
-      <c r="C121" t="inlineStr">
-        <is>
-          <t>McLean, VA, US USA</t>
-        </is>
-      </c>
-      <c r="D121" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E121" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
-        </is>
-      </c>
-      <c r="F121" t="inlineStr">
-        <is>
-          <t>2026-09-23</t>
-        </is>
-      </c>
-      <c r="G121" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=8e194fdfb9b8dbe3</t>
-        </is>
-      </c>
-    </row>
-    <row r="122">
-      <c r="A122" t="inlineStr">
-        <is>
-          <t>Full-Stack Engineer 4 (Python, AWS, Network Automation)</t>
-        </is>
-      </c>
-      <c r="B122" t="inlineStr">
-        <is>
-          <t>Capital One</t>
-        </is>
-      </c>
-      <c r="C122" t="inlineStr">
-        <is>
-          <t>McLean, VA, US USA</t>
-        </is>
-      </c>
-      <c r="D122" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E122" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
-        </is>
-      </c>
-      <c r="F122" t="inlineStr">
-        <is>
-          <t>2026-09-23</t>
-        </is>
-      </c>
-      <c r="G122" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=a77780c738e44a57</t>
-        </is>
-      </c>
-    </row>
-    <row r="123">
-      <c r="A123" t="inlineStr">
-        <is>
-          <t>Full-stack Engineer 5 (Go, TypeScript and Angular)</t>
-        </is>
-      </c>
-      <c r="B123" t="inlineStr">
-        <is>
-          <t>Capital One</t>
-        </is>
-      </c>
-      <c r="C123" t="inlineStr">
-        <is>
-          <t>Chicago, IL, US USA</t>
-        </is>
-      </c>
-      <c r="D123" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E123" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
-        </is>
-      </c>
-      <c r="F123" t="inlineStr">
-        <is>
-          <t>2026-09-22</t>
-        </is>
-      </c>
-      <c r="G123" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=81ff3ef325447a98</t>
-        </is>
-      </c>
-    </row>
-    <row r="124">
-      <c r="A124" t="inlineStr">
-        <is>
-          <t>Full-stack Engineer 4</t>
-        </is>
-      </c>
-      <c r="B124" t="inlineStr">
-        <is>
-          <t>Capital One</t>
-        </is>
-      </c>
-      <c r="C124" t="inlineStr">
-        <is>
-          <t>McLean, VA, US USA</t>
-        </is>
-      </c>
-      <c r="D124" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E124" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
-        </is>
-      </c>
-      <c r="F124" t="inlineStr">
-        <is>
-          <t>2026-09-22</t>
-        </is>
-      </c>
-      <c r="G124" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=70843ae9e366dd5b</t>
-        </is>
-      </c>
-    </row>
-    <row r="125">
-      <c r="A125" t="inlineStr">
-        <is>
-          <t>Full - Stack Engineer 5 (Remote - Eligible)</t>
-        </is>
-      </c>
-      <c r="B125" t="inlineStr">
-        <is>
-          <t>Capital One</t>
-        </is>
-      </c>
-      <c r="C125" t="inlineStr">
-        <is>
-          <t>McLean, VA, US USA</t>
-        </is>
-      </c>
-      <c r="D125" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E125" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
-        </is>
-      </c>
-      <c r="F125" t="inlineStr">
-        <is>
-          <t>2026-09-22</t>
-        </is>
-      </c>
-      <c r="G125" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=877ad6c20024fb1a</t>
-        </is>
-      </c>
-    </row>
-    <row r="126">
-      <c r="A126" t="inlineStr">
-        <is>
-          <t>Full-stack Engineer 4</t>
-        </is>
-      </c>
-      <c r="B126" t="inlineStr">
-        <is>
-          <t>Capital One</t>
-        </is>
-      </c>
-      <c r="C126" t="inlineStr">
-        <is>
-          <t>Plano, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D126" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E126" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
-        </is>
-      </c>
-      <c r="F126" t="inlineStr">
-        <is>
-          <t>2026-09-22</t>
-        </is>
-      </c>
-      <c r="G126" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=6979868bb95d63f0</t>
-        </is>
-      </c>
-    </row>
-    <row r="127">
-      <c r="A127" t="inlineStr">
-        <is>
-          <t>Full Stack Engineer 5</t>
-        </is>
-      </c>
-      <c r="B127" t="inlineStr">
-        <is>
-          <t>Capital One</t>
-        </is>
-      </c>
-      <c r="C127" t="inlineStr">
-        <is>
-          <t>McLean, VA, US USA</t>
-        </is>
-      </c>
-      <c r="D127" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E127" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
-        </is>
-      </c>
-      <c r="F127" t="inlineStr">
-        <is>
-          <t>2026-09-22</t>
-        </is>
-      </c>
-      <c r="G127" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=b743b91aec079a75</t>
-        </is>
-      </c>
-    </row>
-    <row r="128">
-      <c r="A128" t="inlineStr">
-        <is>
-          <t>Full Stack Engineer 4</t>
-        </is>
-      </c>
-      <c r="B128" t="inlineStr">
-        <is>
-          <t>Capital One</t>
-        </is>
-      </c>
-      <c r="C128" t="inlineStr">
-        <is>
-          <t>McLean, VA, US USA</t>
-        </is>
-      </c>
-      <c r="D128" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E128" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
-        </is>
-      </c>
-      <c r="F128" t="inlineStr">
-        <is>
-          <t>2026-09-22</t>
-        </is>
-      </c>
-      <c r="G128" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=3fb66ff5f4ef065f</t>
-        </is>
-      </c>
-    </row>
-    <row r="129">
-      <c r="A129" t="inlineStr">
-        <is>
-          <t>Full-stack Engineer 4 (Python, Java)</t>
-        </is>
-      </c>
-      <c r="B129" t="inlineStr">
-        <is>
-          <t>Capital One</t>
-        </is>
-      </c>
-      <c r="C129" t="inlineStr">
-        <is>
-          <t>Richmond, VA, US USA</t>
-        </is>
-      </c>
-      <c r="D129" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E129" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
-        </is>
-      </c>
-      <c r="F129" t="inlineStr">
-        <is>
-          <t>2026-09-22</t>
-        </is>
-      </c>
-      <c r="G129" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=c9046de91e154d69</t>
-        </is>
-      </c>
-    </row>
-    <row r="130">
-      <c r="A130" t="inlineStr">
-        <is>
-          <t>Full-stack Engineer 5 ( Python, AWS)</t>
-        </is>
-      </c>
-      <c r="B130" t="inlineStr">
-        <is>
-          <t>Capital One</t>
-        </is>
-      </c>
-      <c r="C130" t="inlineStr">
-        <is>
-          <t>McLean, VA, US USA</t>
-        </is>
-      </c>
-      <c r="D130" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E130" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
-        </is>
-      </c>
-      <c r="F130" t="inlineStr">
-        <is>
-          <t>2026-09-22</t>
-        </is>
-      </c>
-      <c r="G130" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=5e4de127a7227d81</t>
-        </is>
-      </c>
-    </row>
-    <row r="131">
-      <c r="A131" t="inlineStr">
-        <is>
-          <t>Full-stack Engineer 5 (Golang, Java, AWS)</t>
-        </is>
-      </c>
-      <c r="B131" t="inlineStr">
-        <is>
-          <t>Capital One</t>
-        </is>
-      </c>
-      <c r="C131" t="inlineStr">
-        <is>
-          <t>Chicago, IL, US USA</t>
-        </is>
-      </c>
-      <c r="D131" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E131" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
-        </is>
-      </c>
-      <c r="F131" t="inlineStr">
-        <is>
-          <t>2026-09-22</t>
-        </is>
-      </c>
-      <c r="G131" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=f3a9ee8f682a9c78</t>
-        </is>
-      </c>
-    </row>
-    <row r="132">
-      <c r="A132" t="inlineStr">
-        <is>
-          <t>Full-stack Engineer 4 - Intelligent Foundations and Experiences (IFX)</t>
-        </is>
-      </c>
-      <c r="B132" t="inlineStr">
-        <is>
-          <t>Capital One</t>
-        </is>
-      </c>
-      <c r="C132" t="inlineStr">
-        <is>
-          <t>McLean, VA, US USA</t>
-        </is>
-      </c>
-      <c r="D132" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E132" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
-        </is>
-      </c>
-      <c r="F132" t="inlineStr">
-        <is>
-          <t>2026-09-22</t>
-        </is>
-      </c>
-      <c r="G132" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=6faf5ca1640fcd31</t>
-        </is>
-      </c>
-    </row>
-    <row r="133">
-      <c r="A133" t="inlineStr">
-        <is>
-          <t>Full-stack Engineer 4 - Intelligent Foundations and Experiences (IFX)</t>
-        </is>
-      </c>
-      <c r="B133" t="inlineStr">
-        <is>
-          <t>Capital One</t>
-        </is>
-      </c>
-      <c r="C133" t="inlineStr">
-        <is>
-          <t>New York, NY, US USA</t>
-        </is>
-      </c>
-      <c r="D133" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E133" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
-        </is>
-      </c>
-      <c r="F133" t="inlineStr">
-        <is>
-          <t>2026-09-22</t>
-        </is>
-      </c>
-      <c r="G133" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=42133a298638cb9b</t>
-        </is>
-      </c>
-    </row>
-    <row r="134">
-      <c r="A134" t="inlineStr">
-        <is>
-          <t>Full-stack Engineer 5</t>
-        </is>
-      </c>
-      <c r="B134" t="inlineStr">
-        <is>
-          <t>Capital One</t>
-        </is>
-      </c>
-      <c r="C134" t="inlineStr">
-        <is>
-          <t>McLean, VA, US USA</t>
-        </is>
-      </c>
-      <c r="D134" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E134" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
-        </is>
-      </c>
-      <c r="F134" t="inlineStr">
-        <is>
-          <t>2026-09-22</t>
-        </is>
-      </c>
-      <c r="G134" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=a708182f9a1da64d</t>
-        </is>
-      </c>
-    </row>
-    <row r="135">
-      <c r="A135" t="inlineStr">
-        <is>
-          <t>Full-stack Engineer 4 - Intelligent Foundations and Experiences (IFX)</t>
-        </is>
-      </c>
-      <c r="B135" t="inlineStr">
-        <is>
-          <t>Capital One</t>
-        </is>
-      </c>
-      <c r="C135" t="inlineStr">
-        <is>
-          <t>New York, NY, US USA</t>
-        </is>
-      </c>
-      <c r="D135" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E135" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
-        </is>
-      </c>
-      <c r="F135" t="inlineStr">
-        <is>
-          <t>2026-09-22</t>
-        </is>
-      </c>
-      <c r="G135" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=76c8a5b4fcc58505</t>
-        </is>
-      </c>
-    </row>
-    <row r="136">
-      <c r="A136" t="inlineStr">
-        <is>
-          <t>Full-stack Engineer 5 - Shopping (Remote-Eligible)</t>
-        </is>
-      </c>
-      <c r="B136" t="inlineStr">
-        <is>
-          <t>Capital One</t>
-        </is>
-      </c>
-      <c r="C136" t="inlineStr">
-        <is>
-          <t>McLean, VA, US USA</t>
-        </is>
-      </c>
-      <c r="D136" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E136" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
-        </is>
-      </c>
-      <c r="F136" t="inlineStr">
-        <is>
-          <t>2026-09-22</t>
-        </is>
-      </c>
-      <c r="G136" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=419688dc0cbfaf98</t>
-        </is>
-      </c>
-    </row>
-    <row r="137">
-      <c r="A137" t="inlineStr">
-        <is>
-          <t>Full-stack Engineer 5 (Java, Scala, AWS)</t>
-        </is>
-      </c>
-      <c r="B137" t="inlineStr">
-        <is>
-          <t>Capital One</t>
-        </is>
-      </c>
-      <c r="C137" t="inlineStr">
-        <is>
-          <t>McLean, VA, US USA</t>
-        </is>
-      </c>
-      <c r="D137" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E137" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
-        </is>
-      </c>
-      <c r="F137" t="inlineStr">
-        <is>
-          <t>2026-09-22</t>
-        </is>
-      </c>
-      <c r="G137" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=c997daa05db4e0c7</t>
-        </is>
-      </c>
-    </row>
-    <row r="138">
-      <c r="A138" t="inlineStr">
-        <is>
-          <t>Full Stack Engineer 4 (Go, AWS)</t>
-        </is>
-      </c>
-      <c r="B138" t="inlineStr">
-        <is>
-          <t>Capital One</t>
-        </is>
-      </c>
-      <c r="C138" t="inlineStr">
-        <is>
-          <t>McLean, VA, US USA</t>
-        </is>
-      </c>
-      <c r="D138" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E138" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
-        </is>
-      </c>
-      <c r="F138" t="inlineStr">
-        <is>
-          <t>2026-09-22</t>
-        </is>
-      </c>
-      <c r="G138" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=6a9874c783fb4a03</t>
-        </is>
-      </c>
-    </row>
-    <row r="139">
-      <c r="A139" t="inlineStr">
-        <is>
-          <t>Full-stack Engineer 4</t>
-        </is>
-      </c>
-      <c r="B139" t="inlineStr">
-        <is>
-          <t>Capital One</t>
-        </is>
-      </c>
-      <c r="C139" t="inlineStr">
-        <is>
-          <t>McLean, VA, US USA</t>
-        </is>
-      </c>
-      <c r="D139" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E139" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
-        </is>
-      </c>
-      <c r="F139" t="inlineStr">
-        <is>
-          <t>2026-09-22</t>
-        </is>
-      </c>
-      <c r="G139" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=1f96da918db85a2a</t>
-        </is>
-      </c>
-    </row>
-    <row r="140">
-      <c r="A140" t="inlineStr">
-        <is>
-          <t>Full-stack Engineer 4 (Java, Scala, AWS)</t>
-        </is>
-      </c>
-      <c r="B140" t="inlineStr">
-        <is>
-          <t>Capital One</t>
-        </is>
-      </c>
-      <c r="C140" t="inlineStr">
-        <is>
-          <t>New York, NY, US USA</t>
-        </is>
-      </c>
-      <c r="D140" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E140" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
-        </is>
-      </c>
-      <c r="F140" t="inlineStr">
-        <is>
-          <t>2026-09-22</t>
-        </is>
-      </c>
-      <c r="G140" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=b9e0187cbe4c2e40</t>
-        </is>
-      </c>
-    </row>
-    <row r="141">
-      <c r="A141" t="inlineStr">
-        <is>
-          <t>Full-stack Engineer 4</t>
-        </is>
-      </c>
-      <c r="B141" t="inlineStr">
-        <is>
-          <t>Capital One</t>
-        </is>
-      </c>
-      <c r="C141" t="inlineStr">
-        <is>
-          <t>McLean, VA, US USA</t>
-        </is>
-      </c>
-      <c r="D141" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E141" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
-        </is>
-      </c>
-      <c r="F141" t="inlineStr">
-        <is>
-          <t>2026-09-22</t>
-        </is>
-      </c>
-      <c r="G141" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=900df92ddc778d5f</t>
-        </is>
-      </c>
-    </row>
-    <row r="142">
-      <c r="A142" t="inlineStr">
-        <is>
-          <t>Full-stack Engineer 4 (JavaScript, React)</t>
-        </is>
-      </c>
-      <c r="B142" t="inlineStr">
-        <is>
-          <t>Capital One</t>
-        </is>
-      </c>
-      <c r="C142" t="inlineStr">
-        <is>
-          <t>Chicago, IL, US USA</t>
-        </is>
-      </c>
-      <c r="D142" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E142" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
-        </is>
-      </c>
-      <c r="F142" t="inlineStr">
-        <is>
-          <t>2026-09-22</t>
-        </is>
-      </c>
-      <c r="G142" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=e7c346fa6453ffb9</t>
-        </is>
-      </c>
-    </row>
-    <row r="143">
-      <c r="A143" t="inlineStr">
-        <is>
-          <t>Full-stack Engineer 5 (Go/Java, Angular, AWS)</t>
-        </is>
-      </c>
-      <c r="B143" t="inlineStr">
-        <is>
-          <t>Capital One</t>
-        </is>
-      </c>
-      <c r="C143" t="inlineStr">
-        <is>
-          <t>Chicago, IL, US USA</t>
-        </is>
-      </c>
-      <c r="D143" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E143" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
-        </is>
-      </c>
-      <c r="F143" t="inlineStr">
-        <is>
-          <t>2026-09-22</t>
-        </is>
-      </c>
-      <c r="G143" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=c039bc465260bc95</t>
-        </is>
-      </c>
-    </row>
-    <row r="144">
-      <c r="A144" t="inlineStr">
-        <is>
-          <t>Full-stack Engineer 4</t>
-        </is>
-      </c>
-      <c r="B144" t="inlineStr">
-        <is>
-          <t>Capital One</t>
-        </is>
-      </c>
-      <c r="C144" t="inlineStr">
-        <is>
-          <t>Richmond, VA, US USA</t>
-        </is>
-      </c>
-      <c r="D144" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E144" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
-        </is>
-      </c>
-      <c r="F144" t="inlineStr">
-        <is>
-          <t>2026-09-22</t>
-        </is>
-      </c>
-      <c r="G144" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=54e236865193f8a0</t>
-        </is>
-      </c>
-    </row>
-    <row r="145">
-      <c r="A145" t="inlineStr">
-        <is>
-          <t>Full-stack Engineer 4</t>
-        </is>
-      </c>
-      <c r="B145" t="inlineStr">
-        <is>
-          <t>Capital One</t>
-        </is>
-      </c>
-      <c r="C145" t="inlineStr">
-        <is>
-          <t>McLean, VA, US USA</t>
-        </is>
-      </c>
-      <c r="D145" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E145" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
-        </is>
-      </c>
-      <c r="F145" t="inlineStr">
-        <is>
-          <t>2026-09-22</t>
-        </is>
-      </c>
-      <c r="G145" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=b667ebd325202576</t>
-        </is>
-      </c>
-    </row>
-    <row r="146">
-      <c r="A146" t="inlineStr">
-        <is>
-          <t>Full-stack Engineer 5 (Golang, AWS)</t>
-        </is>
-      </c>
-      <c r="B146" t="inlineStr">
-        <is>
-          <t>Capital One</t>
-        </is>
-      </c>
-      <c r="C146" t="inlineStr">
-        <is>
-          <t>McLean, VA, US USA</t>
-        </is>
-      </c>
-      <c r="D146" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E146" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
-        </is>
-      </c>
-      <c r="F146" t="inlineStr">
-        <is>
-          <t>2026-09-22</t>
-        </is>
-      </c>
-      <c r="G146" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=672e371e8fd60859</t>
-        </is>
-      </c>
-    </row>
-    <row r="147">
-      <c r="A147" t="inlineStr">
-        <is>
-          <t>Full-stack Engineer 4 (React, TypeScript, AWS)</t>
-        </is>
-      </c>
-      <c r="B147" t="inlineStr">
-        <is>
-          <t>Capital One</t>
-        </is>
-      </c>
-      <c r="C147" t="inlineStr">
-        <is>
-          <t>McLean, VA, US USA</t>
-        </is>
-      </c>
-      <c r="D147" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E147" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
-        </is>
-      </c>
-      <c r="F147" t="inlineStr">
-        <is>
-          <t>2026-09-22</t>
-        </is>
-      </c>
-      <c r="G147" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=346a7f081a67b46c</t>
-        </is>
-      </c>
-    </row>
-    <row r="148">
-      <c r="A148" t="inlineStr">
-        <is>
-          <t>Full-stack Engineer 4</t>
-        </is>
-      </c>
-      <c r="B148" t="inlineStr">
-        <is>
-          <t>Capital One</t>
-        </is>
-      </c>
-      <c r="C148" t="inlineStr">
-        <is>
-          <t>McLean, VA, US USA</t>
-        </is>
-      </c>
-      <c r="D148" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E148" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
-        </is>
-      </c>
-      <c r="F148" t="inlineStr">
-        <is>
-          <t>2026-09-22</t>
-        </is>
-      </c>
-      <c r="G148" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=7b21934bf2433e6a</t>
-        </is>
-      </c>
-    </row>
-    <row r="149">
-      <c r="A149" t="inlineStr">
-        <is>
-          <t>Full-stack Engineer 4 (Scala, React, AWS)</t>
-        </is>
-      </c>
-      <c r="B149" t="inlineStr">
-        <is>
-          <t>Capital One</t>
-        </is>
-      </c>
-      <c r="C149" t="inlineStr">
-        <is>
-          <t>New York, NY, US USA</t>
-        </is>
-      </c>
-      <c r="D149" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E149" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
-        </is>
-      </c>
-      <c r="F149" t="inlineStr">
-        <is>
-          <t>2026-09-22</t>
-        </is>
-      </c>
-      <c r="G149" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=2af3b2e528eb8c47</t>
-        </is>
-      </c>
-    </row>
-    <row r="150">
-      <c r="A150" t="inlineStr">
-        <is>
-          <t>Full-stack Engineer 4 (Scala, React, AWS)</t>
-        </is>
-      </c>
-      <c r="B150" t="inlineStr">
-        <is>
-          <t>Capital One</t>
-        </is>
-      </c>
-      <c r="C150" t="inlineStr">
-        <is>
-          <t>New York, NY, US USA</t>
-        </is>
-      </c>
-      <c r="D150" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E150" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
-        </is>
-      </c>
-      <c r="F150" t="inlineStr">
-        <is>
-          <t>2026-09-22</t>
-        </is>
-      </c>
-      <c r="G150" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=51fd20841ca9c754</t>
-        </is>
-      </c>
-    </row>
-    <row r="151">
-      <c r="A151" t="inlineStr">
-        <is>
-          <t>Full-stack Engineer 4</t>
-        </is>
-      </c>
-      <c r="B151" t="inlineStr">
-        <is>
-          <t>Capital One</t>
-        </is>
-      </c>
-      <c r="C151" t="inlineStr">
-        <is>
-          <t>McLean, VA, US USA</t>
-        </is>
-      </c>
-      <c r="D151" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E151" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
-        </is>
-      </c>
-      <c r="F151" t="inlineStr">
-        <is>
-          <t>2026-09-22</t>
-        </is>
-      </c>
-      <c r="G151" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=619531dae358928f</t>
-        </is>
-      </c>
-    </row>
-    <row r="152">
-      <c r="A152" t="inlineStr">
-        <is>
-          <t>Full-stack Engineer 4 (Python, AWS)</t>
-        </is>
-      </c>
-      <c r="B152" t="inlineStr">
-        <is>
-          <t>Capital One</t>
-        </is>
-      </c>
-      <c r="C152" t="inlineStr">
-        <is>
-          <t>McLean, VA, US USA</t>
-        </is>
-      </c>
-      <c r="D152" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E152" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
-        </is>
-      </c>
-      <c r="F152" t="inlineStr">
-        <is>
-          <t>2026-09-22</t>
-        </is>
-      </c>
-      <c r="G152" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=8e4eaf7eaa027bbb</t>
-        </is>
-      </c>
-    </row>
-    <row r="153">
-      <c r="A153" t="inlineStr">
-        <is>
-          <t>Full-stack Engineer 4 (GoLang)</t>
-        </is>
-      </c>
-      <c r="B153" t="inlineStr">
-        <is>
-          <t>Capital One</t>
-        </is>
-      </c>
-      <c r="C153" t="inlineStr">
-        <is>
-          <t>Chicago, IL, US USA</t>
-        </is>
-      </c>
-      <c r="D153" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E153" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
-        </is>
-      </c>
-      <c r="F153" t="inlineStr">
-        <is>
-          <t>2026-09-22</t>
-        </is>
-      </c>
-      <c r="G153" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=b7c24e0e87f3fc42</t>
-        </is>
-      </c>
-    </row>
-    <row r="154">
-      <c r="A154" t="inlineStr">
-        <is>
-          <t>Full-Stack Engineer 4 (Automation Quality Engineer)</t>
-        </is>
-      </c>
-      <c r="B154" t="inlineStr">
-        <is>
-          <t>Capital One</t>
-        </is>
-      </c>
-      <c r="C154" t="inlineStr">
-        <is>
-          <t>Riverwoods, IL, US USA</t>
-        </is>
-      </c>
-      <c r="D154" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E154" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
-        </is>
-      </c>
-      <c r="F154" t="inlineStr">
-        <is>
-          <t>2026-09-22</t>
-        </is>
-      </c>
-      <c r="G154" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=2acd23b24043f205</t>
-        </is>
-      </c>
-    </row>
-    <row r="155">
-      <c r="A155" t="inlineStr">
-        <is>
-          <t>Full-stack Engineer 4 - Shopping (Remote-Eligible)</t>
-        </is>
-      </c>
-      <c r="B155" t="inlineStr">
-        <is>
-          <t>Capital One</t>
-        </is>
-      </c>
-      <c r="C155" t="inlineStr">
-        <is>
-          <t>McLean, VA, US USA</t>
-        </is>
-      </c>
-      <c r="D155" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E155" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
-        </is>
-      </c>
-      <c r="F155" t="inlineStr">
-        <is>
-          <t>2026-09-22</t>
-        </is>
-      </c>
-      <c r="G155" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=f87b328e958cbb63</t>
-        </is>
-      </c>
-    </row>
-    <row r="156">
-      <c r="A156" t="inlineStr">
-        <is>
-          <t>Data Engineer</t>
-        </is>
-      </c>
-      <c r="B156" t="inlineStr">
-        <is>
-          <t>KeHE Distributors</t>
-        </is>
-      </c>
-      <c r="C156" t="inlineStr">
-        <is>
-          <t>Naperville, IL, US USA</t>
-        </is>
-      </c>
-      <c r="D156" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E156" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, Data Modeling, Power BI, Tableau, MLOps</t>
-        </is>
-      </c>
-      <c r="F156" t="inlineStr">
-        <is>
-          <t>2026-09-22</t>
-        </is>
-      </c>
-      <c r="G156" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=9033c8036c6af9b3</t>
-        </is>
-      </c>
-    </row>
-    <row r="157">
-      <c r="A157" t="inlineStr">
-        <is>
-          <t>Data Platform Engineer</t>
-        </is>
-      </c>
-      <c r="B157" t="inlineStr">
-        <is>
-          <t>Hubble Network</t>
-        </is>
-      </c>
-      <c r="C157" t="inlineStr">
-        <is>
-          <t>San Francisco, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D157" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E157" t="inlineStr">
-        <is>
-          <t>Kinesis, Redshift, RDS, Scala, Kafka, Dimensional Modeling, Star Schema, Fact Tables, ETL, dbt</t>
-        </is>
-      </c>
-      <c r="F157" t="inlineStr">
-        <is>
-          <t>2026-09-22</t>
-        </is>
-      </c>
-      <c r="G157" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=a000c1d1d33d8b12</t>
-        </is>
-      </c>
-    </row>
-    <row r="158">
-      <c r="A158" t="inlineStr">
-        <is>
-          <t>Senior Data Engineer</t>
-        </is>
-      </c>
-      <c r="B158" t="inlineStr">
-        <is>
-          <t>Lockheed Martin</t>
-        </is>
-      </c>
-      <c r="C158" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D158" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E158" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Databricks, Oracle, SQL Server, MySQL, ETL, Tableau, CI/CD</t>
-        </is>
-      </c>
-      <c r="F158" t="inlineStr">
-        <is>
-          <t>2026-09-02</t>
-        </is>
-      </c>
-      <c r="G158" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=70671fedd9bf2e0b</t>
-        </is>
-      </c>
-    </row>
-    <row r="159">
-      <c r="A159" t="inlineStr">
-        <is>
-          <t>Integration Engineer 4</t>
-        </is>
-      </c>
-      <c r="B159" t="inlineStr">
-        <is>
-          <t>Capital One</t>
-        </is>
-      </c>
-      <c r="C159" t="inlineStr">
-        <is>
-          <t>McLean, VA, US USA</t>
-        </is>
-      </c>
-      <c r="D159" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E159" t="inlineStr">
-        <is>
-          <t>AWS, Lambda, Step Functions, RDS, Azure, GCP, Scala, Splunk, Jenkins, Jenkins</t>
-        </is>
-      </c>
-      <c r="F159" t="inlineStr">
-        <is>
-          <t>2026-09-22</t>
-        </is>
-      </c>
-      <c r="G159" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=52d873bb7fc420f0</t>
-        </is>
-      </c>
-    </row>
-    <row r="160">
-      <c r="A160" t="inlineStr">
-        <is>
-          <t>Specialist Solutions Architect - Cloud Infrastructure &amp; Azure Platform</t>
-        </is>
-      </c>
-      <c r="B160" t="inlineStr">
-        <is>
-          <t>Databricks</t>
-        </is>
-      </c>
-      <c r="C160" t="inlineStr">
-        <is>
-          <t>US USA</t>
-        </is>
-      </c>
-      <c r="D160" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E160" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Scala, Snowflake, Terraform, Azure Monitor, Python</t>
-        </is>
-      </c>
-      <c r="F160" t="inlineStr">
-        <is>
-          <t>2026-09-23</t>
-        </is>
-      </c>
-      <c r="G160" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=24b4e0a029b86ac2</t>
-        </is>
-      </c>
-    </row>
-    <row r="161">
-      <c r="A161" t="inlineStr">
-        <is>
-          <t>Senior Full Stack Software Engineer (Java)</t>
-        </is>
-      </c>
-      <c r="B161" t="inlineStr">
-        <is>
-          <t>BV Teck</t>
-        </is>
-      </c>
-      <c r="C161" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D161" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E161" t="inlineStr">
-        <is>
-          <t>AWS, Azure, GCP, Kafka, Oracle, SQL Server, PostgreSQL, MySQL, CI/CD, Docker</t>
-        </is>
-      </c>
-      <c r="F161" t="inlineStr">
-        <is>
-          <t>2026-09-23</t>
-        </is>
-      </c>
-      <c r="G161" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=e58be4fcea83450d</t>
-        </is>
-      </c>
-    </row>
-    <row r="162">
-      <c r="A162" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer</t>
-        </is>
-      </c>
-      <c r="B162" t="inlineStr">
-        <is>
-          <t>Mastercard</t>
-        </is>
-      </c>
-      <c r="C162" t="inlineStr">
-        <is>
-          <t>O'Fallon, MO, US USA</t>
-        </is>
-      </c>
-      <c r="D162" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E162" t="inlineStr">
-        <is>
-          <t>AWS, API Gateway, RDS, Scala, Oracle, PostgreSQL, CI/CD, Jenkins, GitHub Actions, Jenkins</t>
-        </is>
-      </c>
-      <c r="F162" t="inlineStr">
-        <is>
-          <t>2026-09-22</t>
-        </is>
-      </c>
-      <c r="G162" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=0245dcafa3f48258</t>
-        </is>
-      </c>
-    </row>
-    <row r="163">
-      <c r="A163" t="inlineStr">
-        <is>
-          <t>Data Engineer</t>
-        </is>
-      </c>
-      <c r="B163" t="inlineStr">
-        <is>
-          <t>Function Health</t>
-        </is>
-      </c>
-      <c r="C163" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D163" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E163" t="inlineStr">
-        <is>
-          <t>RDS, Databricks, BigQuery, Spark, Kafka, Snowflake, ELT, dbt, MLOps, Terraform</t>
-        </is>
-      </c>
-      <c r="F163" t="inlineStr">
-        <is>
-          <t>2026-09-22</t>
-        </is>
-      </c>
-      <c r="G163" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=8d332f2047edfa45</t>
-        </is>
-      </c>
-    </row>
-    <row r="164">
-      <c r="A164" t="inlineStr">
-        <is>
-          <t>Azure Data Engineer</t>
-        </is>
-      </c>
-      <c r="B164" t="inlineStr">
-        <is>
-          <t>Orion Innovation</t>
-        </is>
-      </c>
-      <c r="C164" t="inlineStr">
-        <is>
-          <t>Montvale, NJ, US USA</t>
-        </is>
-      </c>
-      <c r="D164" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E164" t="inlineStr">
-        <is>
-          <t>Azure, Data Factory, Databricks, Spark, PySpark, Scala, ETL, ELT, Power BI, AKS</t>
-        </is>
-      </c>
-      <c r="F164" t="inlineStr">
-        <is>
-          <t>2026-09-23</t>
-        </is>
-      </c>
-      <c r="G164" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=334e0bc8c90d3013</t>
-        </is>
-      </c>
-    </row>
-    <row r="165">
-      <c r="A165" t="inlineStr">
-        <is>
-          <t>Backend Software Engineer</t>
-        </is>
-      </c>
-      <c r="B165" t="inlineStr">
-        <is>
-          <t>KorTerra</t>
-        </is>
-      </c>
-      <c r="C165" t="inlineStr">
-        <is>
-          <t>Chanhassen, MN, US USA</t>
-        </is>
-      </c>
-      <c r="D165" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E165" t="inlineStr">
-        <is>
-          <t>Azure, Scala, PostgreSQL, NoSQL, CI/CD, Terraform, Docker, Kubernetes, AKS, Git</t>
-        </is>
-      </c>
-      <c r="F165" t="inlineStr">
-        <is>
-          <t>2026-09-23</t>
-        </is>
-      </c>
-      <c r="G165" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=62838a48fa61a004</t>
         </is>
